--- a/Data/Corrections_Log.xlsx
+++ b/Data/Corrections_Log.xlsx
@@ -6363,7 +6363,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6381,12 +6381,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -6433,7 +6427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6449,9 +6443,6 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -6770,19 +6761,19 @@
   <dimension ref="A1:M694"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="15.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="15.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -6839,7 +6830,7 @@
       <c r="D2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="4">
         <v>8198</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -6880,7 +6871,7 @@
       <c r="D3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>85864</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -6889,7 +6880,7 @@
       <c r="G3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>0.857</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -6921,7 +6912,7 @@
       <c r="D4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>46156</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -6962,7 +6953,7 @@
       <c r="D5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>105470</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -7001,7 +6992,7 @@
       <c r="D6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>28396</v>
       </c>
       <c r="F6" s="5" t="s">
@@ -7042,7 +7033,7 @@
       <c r="D7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>131789</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -7083,7 +7074,7 @@
       <c r="D8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>37838</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -7092,7 +7083,7 @@
       <c r="G8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>0.857</v>
       </c>
       <c r="I8" s="5" t="s">
@@ -7124,7 +7115,7 @@
       <c r="D9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>25557</v>
       </c>
       <c r="F9" s="5" t="s">
@@ -7165,7 +7156,7 @@
       <c r="D10" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>40680</v>
       </c>
       <c r="F10" s="5" t="s">
@@ -7174,7 +7165,7 @@
       <c r="G10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>0.733</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -7206,7 +7197,7 @@
       <c r="D11" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <v>79422</v>
       </c>
       <c r="F11" s="5" t="s">
@@ -7247,7 +7238,7 @@
       <c r="D12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>41982</v>
       </c>
       <c r="F12" s="5" t="s">
@@ -7288,7 +7279,7 @@
       <c r="D13" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>44501</v>
       </c>
       <c r="F13" s="5" t="s">
@@ -7329,7 +7320,7 @@
       <c r="D14" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="4">
         <v>27992</v>
       </c>
       <c r="F14" s="5" t="s">
@@ -7370,7 +7361,7 @@
       <c r="D15" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <v>38253</v>
       </c>
       <c r="F15" s="5" t="s">
@@ -7379,7 +7370,7 @@
       <c r="G15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>0.733</v>
       </c>
       <c r="I15" s="5" t="s">
@@ -7411,7 +7402,7 @@
       <c r="D16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="4">
         <v>31909</v>
       </c>
       <c r="F16" s="5" t="s">
@@ -7452,7 +7443,7 @@
       <c r="D17" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="4">
         <v>16306</v>
       </c>
       <c r="F17" s="5" t="s">
@@ -7493,7 +7484,7 @@
       <c r="D18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="4">
         <v>200512</v>
       </c>
       <c r="F18" s="5" t="s">
@@ -7502,7 +7493,7 @@
       <c r="G18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="6">
         <v>0.857</v>
       </c>
       <c r="I18" s="5" t="s">
@@ -7534,7 +7525,7 @@
       <c r="D19" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="4">
         <v>164770</v>
       </c>
       <c r="F19" s="5" t="s">
@@ -7575,7 +7566,7 @@
       <c r="D20" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="4">
         <v>148455</v>
       </c>
       <c r="F20" s="5" t="s">
@@ -7584,7 +7575,7 @@
       <c r="G20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>0.857</v>
       </c>
       <c r="I20" s="5" t="s">
@@ -7616,7 +7607,7 @@
       <c r="D21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="4">
         <v>45314</v>
       </c>
       <c r="F21" s="5" t="s">
@@ -7657,7 +7648,7 @@
       <c r="D22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="4">
         <v>104752</v>
       </c>
       <c r="F22" s="5" t="s">
@@ -7698,7 +7689,7 @@
       <c r="D23" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="4">
         <v>7935</v>
       </c>
       <c r="F23" s="5" t="s">
@@ -7707,7 +7698,7 @@
       <c r="G23" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="6">
         <v>0.824</v>
       </c>
       <c r="I23" s="5" t="s">
@@ -7739,7 +7730,7 @@
       <c r="D24" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="4">
         <v>79960</v>
       </c>
       <c r="F24" s="5" t="s">
@@ -7748,7 +7739,7 @@
       <c r="G24" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="6">
         <v>0.842</v>
       </c>
       <c r="I24" s="5" t="s">
@@ -7780,7 +7771,7 @@
       <c r="D25" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="4">
         <v>161056</v>
       </c>
       <c r="F25" s="5" t="s">
@@ -7789,7 +7780,7 @@
       <c r="G25" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="6">
         <v>0.733</v>
       </c>
       <c r="I25" s="5" t="s">
@@ -7821,7 +7812,7 @@
       <c r="D26" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="4">
         <v>44352</v>
       </c>
       <c r="F26" s="5" t="s">
@@ -7830,7 +7821,7 @@
       <c r="G26" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="6">
         <v>0.857</v>
       </c>
       <c r="I26" s="5" t="s">
@@ -7862,7 +7853,7 @@
       <c r="D27" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="4">
         <v>3333</v>
       </c>
       <c r="F27" s="5" t="s">
@@ -7871,7 +7862,7 @@
       <c r="G27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>0.857</v>
       </c>
       <c r="I27" s="5" t="s">
@@ -7903,7 +7894,7 @@
       <c r="D28" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="4">
         <v>61651</v>
       </c>
       <c r="F28" s="5" t="s">
@@ -7912,7 +7903,7 @@
       <c r="G28" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="6">
         <v>0.857</v>
       </c>
       <c r="I28" s="5" t="s">
@@ -7944,7 +7935,7 @@
       <c r="D29" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="4">
         <v>49499</v>
       </c>
       <c r="F29" s="5" t="s">
@@ -7953,7 +7944,7 @@
       <c r="G29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="6">
         <v>0.857</v>
       </c>
       <c r="I29" s="5" t="s">
@@ -7985,7 +7976,7 @@
       <c r="D30" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="4">
         <v>68864</v>
       </c>
       <c r="F30" s="5" t="s">
@@ -8026,7 +8017,7 @@
       <c r="D31" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="4">
         <v>39153</v>
       </c>
       <c r="F31" s="5" t="s">
@@ -8035,7 +8026,7 @@
       <c r="G31" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="6">
         <v>0.842</v>
       </c>
       <c r="I31" s="5" t="s">
@@ -8067,7 +8058,7 @@
       <c r="D32" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="4">
         <v>314353</v>
       </c>
       <c r="F32" s="5" t="s">
@@ -8076,7 +8067,7 @@
       <c r="G32" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="6">
         <v>0.857</v>
       </c>
       <c r="I32" s="5" t="s">
@@ -8108,7 +8099,7 @@
       <c r="D33" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="4">
         <v>182904</v>
       </c>
       <c r="F33" s="5" t="s">
@@ -8117,7 +8108,7 @@
       <c r="G33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="6">
         <v>0.824</v>
       </c>
       <c r="I33" s="5" t="s">
@@ -8149,7 +8140,7 @@
       <c r="D34" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="4">
         <v>126540</v>
       </c>
       <c r="F34" s="5" t="s">
@@ -8158,7 +8149,7 @@
       <c r="G34" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="6">
         <v>0.857</v>
       </c>
       <c r="I34" s="5" t="s">
@@ -8190,7 +8181,7 @@
       <c r="D35" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="4">
         <v>5023</v>
       </c>
       <c r="F35" s="5" t="s">
@@ -8199,7 +8190,7 @@
       <c r="G35" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="6">
         <v>0.842</v>
       </c>
       <c r="I35" s="5" t="s">
@@ -8231,7 +8222,7 @@
       <c r="D36" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="4">
         <v>238223</v>
       </c>
       <c r="F36" s="5" t="s">
@@ -8272,7 +8263,7 @@
       <c r="D37" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="4">
         <v>74857</v>
       </c>
       <c r="F37" s="5" t="s">
@@ -8281,7 +8272,7 @@
       <c r="G37" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="6">
         <v>0.857</v>
       </c>
       <c r="I37" s="5" t="s">
@@ -8313,7 +8304,7 @@
       <c r="D38" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="4">
         <v>12249</v>
       </c>
       <c r="F38" s="5" t="s">
@@ -8322,7 +8313,7 @@
       <c r="G38" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38" s="6">
         <v>0.824</v>
       </c>
       <c r="I38" s="5" t="s">
@@ -8354,7 +8345,7 @@
       <c r="D39" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="4">
         <v>28003</v>
       </c>
       <c r="F39" s="5" t="s">
@@ -8363,7 +8354,7 @@
       <c r="G39" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="6">
         <v>0.857</v>
       </c>
       <c r="I39" s="5" t="s">
@@ -8395,7 +8386,7 @@
       <c r="D40" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="4">
         <v>88103</v>
       </c>
       <c r="F40" s="5" t="s">
@@ -8404,7 +8395,7 @@
       <c r="G40" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="6">
         <v>0.733</v>
       </c>
       <c r="I40" s="5" t="s">
@@ -8436,7 +8427,7 @@
       <c r="D41" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="4">
         <v>5947</v>
       </c>
       <c r="F41" s="5" t="s">
@@ -8477,7 +8468,7 @@
       <c r="D42" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="4">
         <v>65230</v>
       </c>
       <c r="F42" s="5" t="s">
@@ -8486,7 +8477,7 @@
       <c r="G42" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H42" s="7">
+      <c r="H42" s="6">
         <v>0.857</v>
       </c>
       <c r="I42" s="5" t="s">
@@ -8518,7 +8509,7 @@
       <c r="D43" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="4">
         <v>32467</v>
       </c>
       <c r="F43" s="5" t="s">
@@ -8527,7 +8518,7 @@
       <c r="G43" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H43" s="7">
+      <c r="H43" s="6">
         <v>0.857</v>
       </c>
       <c r="I43" s="5" t="s">
@@ -8559,7 +8550,7 @@
       <c r="D44" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44" s="4">
         <v>74230</v>
       </c>
       <c r="F44" s="5" t="s">
@@ -8568,7 +8559,7 @@
       <c r="G44" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="6">
         <v>0.824</v>
       </c>
       <c r="I44" s="5" t="s">
@@ -8600,7 +8591,7 @@
       <c r="D45" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="4">
         <v>44017</v>
       </c>
       <c r="F45" s="5" t="s">
@@ -8609,7 +8600,7 @@
       <c r="G45" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="6">
         <v>0.733</v>
       </c>
       <c r="I45" s="5" t="s">
@@ -8641,7 +8632,7 @@
       <c r="D46" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="4">
         <v>85288</v>
       </c>
       <c r="F46" s="5" t="s">
@@ -8682,7 +8673,7 @@
       <c r="D47" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="4">
         <v>18944</v>
       </c>
       <c r="F47" s="5" t="s">
@@ -8691,7 +8682,7 @@
       <c r="G47" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H47" s="6">
         <v>0.857</v>
       </c>
       <c r="I47" s="5" t="s">
@@ -8723,7 +8714,7 @@
       <c r="D48" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="4">
         <v>58358</v>
       </c>
       <c r="F48" s="5" t="s">
@@ -8732,7 +8723,7 @@
       <c r="G48" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H48" s="6">
         <v>0.733</v>
       </c>
       <c r="I48" s="5" t="s">
@@ -8764,7 +8755,7 @@
       <c r="D49" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E49" s="4">
         <v>54984</v>
       </c>
       <c r="F49" s="5" t="s">
@@ -8773,7 +8764,7 @@
       <c r="G49" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="6">
         <v>0.2</v>
       </c>
       <c r="I49" s="5" t="s">
@@ -8805,7 +8796,7 @@
       <c r="D50" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E50" s="6">
+      <c r="E50" s="4">
         <v>51346</v>
       </c>
       <c r="F50" s="5" t="s">
@@ -8844,7 +8835,7 @@
       <c r="D51" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51" s="4">
         <v>15951</v>
       </c>
       <c r="F51" s="5" t="s">
@@ -8885,7 +8876,7 @@
       <c r="D52" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="4">
         <v>76028</v>
       </c>
       <c r="F52" s="5" t="s">
@@ -8926,7 +8917,7 @@
       <c r="D53" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53" s="4">
         <v>54781</v>
       </c>
       <c r="F53" s="5" t="s">
@@ -8967,7 +8958,7 @@
       <c r="D54" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E54" s="4">
         <v>181767</v>
       </c>
       <c r="F54" s="5" t="s">
@@ -9008,7 +8999,7 @@
       <c r="D55" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E55" s="4">
         <v>34542</v>
       </c>
       <c r="F55" s="5" t="s">
@@ -9017,7 +9008,7 @@
       <c r="G55" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H55" s="7">
+      <c r="H55" s="6">
         <v>0.556</v>
       </c>
       <c r="I55" s="5" t="s">
@@ -9049,7 +9040,7 @@
       <c r="D56" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E56" s="4">
         <v>341429</v>
       </c>
       <c r="F56" s="5" t="s">
@@ -9058,7 +9049,7 @@
       <c r="G56" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H56" s="7">
+      <c r="H56" s="6">
         <v>0.692</v>
       </c>
       <c r="I56" s="5" t="s">
@@ -9090,7 +9081,7 @@
       <c r="D57" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E57" s="4">
         <v>103427</v>
       </c>
       <c r="F57" s="5" t="s">
@@ -9131,7 +9122,7 @@
       <c r="D58" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E58" s="4">
         <v>120629</v>
       </c>
       <c r="F58" s="5" t="s">
@@ -9172,7 +9163,7 @@
       <c r="D59" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E59" s="4">
         <v>39996</v>
       </c>
       <c r="F59" s="5" t="s">
@@ -9213,7 +9204,7 @@
       <c r="D60" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E60" s="6">
+      <c r="E60" s="4">
         <v>64000</v>
       </c>
       <c r="F60" s="5" t="s">
@@ -9222,7 +9213,7 @@
       <c r="G60" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H60" s="7">
+      <c r="H60" s="6">
         <v>0.556</v>
       </c>
       <c r="I60" s="5" t="s">
@@ -9263,7 +9254,7 @@
       <c r="G61" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H61" s="7">
+      <c r="H61" s="6">
         <v>0.37</v>
       </c>
       <c r="I61" s="5" t="s">
@@ -9295,7 +9286,7 @@
       <c r="D62" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E62" s="4">
         <v>108390</v>
       </c>
       <c r="F62" s="5" t="s">
@@ -9304,7 +9295,7 @@
       <c r="G62" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H62" s="7">
+      <c r="H62" s="6">
         <v>0.824</v>
       </c>
       <c r="I62" s="5" t="s">
@@ -9336,7 +9327,7 @@
       <c r="D63" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E63" s="4">
         <v>75615</v>
       </c>
       <c r="F63" s="5" t="s">
@@ -9345,7 +9336,7 @@
       <c r="G63" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H63" s="7">
+      <c r="H63" s="6">
         <v>0.842</v>
       </c>
       <c r="I63" s="5" t="s">
@@ -9377,7 +9368,7 @@
       <c r="D64" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E64" s="4">
         <v>274839</v>
       </c>
       <c r="F64" s="5" t="s">
@@ -9418,7 +9409,7 @@
       <c r="D65" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E65" s="4">
         <v>130365</v>
       </c>
       <c r="F65" s="5" t="s">
@@ -9459,7 +9450,7 @@
       <c r="D66" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="4">
         <v>57500</v>
       </c>
       <c r="F66" s="5" t="s">
@@ -9468,7 +9459,7 @@
       <c r="G66" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H66" s="7">
+      <c r="H66" s="6">
         <v>0.824</v>
       </c>
       <c r="I66" s="5" t="s">
@@ -9500,7 +9491,7 @@
       <c r="D67" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E67" s="4">
         <v>96341</v>
       </c>
       <c r="F67" s="5" t="s">
@@ -9541,7 +9532,7 @@
       <c r="D68" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E68" s="4">
         <v>93795</v>
       </c>
       <c r="F68" s="5" t="s">
@@ -9582,7 +9573,7 @@
       <c r="D69" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E69" s="6">
+      <c r="E69" s="4">
         <v>124028</v>
       </c>
       <c r="F69" s="5" t="s">
@@ -9623,7 +9614,7 @@
       <c r="D70" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E70" s="6">
+      <c r="E70" s="4">
         <v>45319</v>
       </c>
       <c r="F70" s="5" t="s">
@@ -9632,7 +9623,7 @@
       <c r="G70" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H70" s="7">
+      <c r="H70" s="6">
         <v>0.824</v>
       </c>
       <c r="I70" s="5" t="s">
@@ -9664,7 +9655,7 @@
       <c r="D71" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E71" s="4">
         <v>8806</v>
       </c>
       <c r="F71" s="5" t="s">
@@ -9673,7 +9664,7 @@
       <c r="G71" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H71" s="7">
+      <c r="H71" s="6">
         <v>0.824</v>
       </c>
       <c r="I71" s="5" t="s">
@@ -9705,7 +9696,7 @@
       <c r="D72" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E72" s="4">
         <v>59970</v>
       </c>
       <c r="F72" s="5" t="s">
@@ -9746,7 +9737,7 @@
       <c r="D73" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E73" s="4">
         <v>26267</v>
       </c>
       <c r="F73" s="5" t="s">
@@ -9787,7 +9778,7 @@
       <c r="D74" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="E74" s="6">
+      <c r="E74" s="4">
         <v>48280</v>
       </c>
       <c r="F74" s="5" t="s">
@@ -9837,7 +9828,7 @@
       <c r="G75" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H75" s="7">
+      <c r="H75" s="6">
         <v>0.387</v>
       </c>
       <c r="I75" s="5" t="s">
@@ -9869,7 +9860,7 @@
       <c r="D76" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E76" s="4">
         <v>39728</v>
       </c>
       <c r="F76" s="5" t="s">
@@ -9878,7 +9869,7 @@
       <c r="G76" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H76" s="7">
+      <c r="H76" s="6">
         <v>0.733</v>
       </c>
       <c r="I76" s="5" t="s">
@@ -9910,7 +9901,7 @@
       <c r="D77" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="E77" s="6">
+      <c r="E77" s="4">
         <v>26485</v>
       </c>
       <c r="F77" s="5" t="s">
@@ -9919,7 +9910,7 @@
       <c r="G77" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H77" s="7">
+      <c r="H77" s="6">
         <v>0.733</v>
       </c>
       <c r="I77" s="5" t="s">
@@ -9951,7 +9942,7 @@
       <c r="D78" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="E78" s="6">
+      <c r="E78" s="4">
         <v>182913</v>
       </c>
       <c r="F78" s="5" t="s">
@@ -9992,7 +9983,7 @@
       <c r="D79" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E79" s="4">
         <v>73734</v>
       </c>
       <c r="F79" s="5" t="s">
@@ -10001,7 +9992,7 @@
       <c r="G79" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H79" s="7">
+      <c r="H79" s="6">
         <v>0.824</v>
       </c>
       <c r="I79" s="5" t="s">
@@ -10033,7 +10024,7 @@
       <c r="D80" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E80" s="4">
         <v>68778</v>
       </c>
       <c r="F80" s="5" t="s">
@@ -10074,7 +10065,7 @@
       <c r="D81" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="E81" s="6">
+      <c r="E81" s="4">
         <v>88755</v>
       </c>
       <c r="F81" s="5" t="s">
@@ -10115,7 +10106,7 @@
       <c r="D82" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="E82" s="6">
+      <c r="E82" s="4">
         <v>118850</v>
       </c>
       <c r="F82" s="5" t="s">
@@ -10156,7 +10147,7 @@
       <c r="D83" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="E83" s="6">
+      <c r="E83" s="4">
         <v>206050</v>
       </c>
       <c r="F83" s="5" t="s">
@@ -10165,7 +10156,7 @@
       <c r="G83" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H83" s="7">
+      <c r="H83" s="6">
         <v>0.842</v>
       </c>
       <c r="I83" s="5" t="s">
@@ -10197,7 +10188,7 @@
       <c r="D84" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E84" s="6">
+      <c r="E84" s="4">
         <v>342229</v>
       </c>
       <c r="F84" s="5" t="s">
@@ -10238,7 +10229,7 @@
       <c r="D85" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="E85" s="6">
+      <c r="E85" s="4">
         <v>7109</v>
       </c>
       <c r="F85" s="5" t="s">
@@ -10247,7 +10238,7 @@
       <c r="G85" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H85" s="7">
+      <c r="H85" s="6">
         <v>0.842</v>
       </c>
       <c r="I85" s="5" t="s">
@@ -10279,7 +10270,7 @@
       <c r="D86" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E86" s="6">
+      <c r="E86" s="4">
         <v>192565</v>
       </c>
       <c r="F86" s="5" t="s">
@@ -10320,7 +10311,7 @@
       <c r="D87" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E87" s="4">
         <v>146854</v>
       </c>
       <c r="F87" s="5" t="s">
@@ -10329,7 +10320,7 @@
       <c r="G87" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H87" s="7">
+      <c r="H87" s="6">
         <v>0.824</v>
       </c>
       <c r="I87" s="5" t="s">
@@ -10361,7 +10352,7 @@
       <c r="D88" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="E88" s="6">
+      <c r="E88" s="4">
         <v>166601</v>
       </c>
       <c r="F88" s="5" t="s">
@@ -10370,7 +10361,7 @@
       <c r="G88" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H88" s="7">
+      <c r="H88" s="6">
         <v>0.733</v>
       </c>
       <c r="I88" s="5" t="s">
@@ -10402,7 +10393,7 @@
       <c r="D89" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="E89" s="6">
+      <c r="E89" s="4">
         <v>138927</v>
       </c>
       <c r="F89" s="5" t="s">
@@ -10443,7 +10434,7 @@
       <c r="D90" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="E90" s="6">
+      <c r="E90" s="4">
         <v>186644</v>
       </c>
       <c r="F90" s="5" t="s">
@@ -10452,7 +10443,7 @@
       <c r="G90" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H90" s="7">
+      <c r="H90" s="6">
         <v>0.556</v>
       </c>
       <c r="I90" s="5" t="s">
@@ -10484,7 +10475,7 @@
       <c r="D91" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E91" s="4">
         <v>102558</v>
       </c>
       <c r="F91" s="5" t="s">
@@ -10525,7 +10516,7 @@
       <c r="D92" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="E92" s="6">
+      <c r="E92" s="4">
         <v>69751</v>
       </c>
       <c r="F92" s="5" t="s">
@@ -10534,7 +10525,7 @@
       <c r="G92" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H92" s="7">
+      <c r="H92" s="6">
         <v>0.857</v>
       </c>
       <c r="I92" s="5" t="s">
@@ -10566,7 +10557,7 @@
       <c r="D93" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="E93" s="6">
+      <c r="E93" s="4">
         <v>44162</v>
       </c>
       <c r="F93" s="5" t="s">
@@ -10575,7 +10566,7 @@
       <c r="G93" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H93" s="7">
+      <c r="H93" s="6">
         <v>0.842</v>
       </c>
       <c r="I93" s="5" t="s">
@@ -10607,7 +10598,7 @@
       <c r="D94" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="E94" s="6">
+      <c r="E94" s="4">
         <v>29401</v>
       </c>
       <c r="F94" s="5" t="s">
@@ -10616,7 +10607,7 @@
       <c r="G94" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H94" s="7">
+      <c r="H94" s="6">
         <v>0.842</v>
       </c>
       <c r="I94" s="5" t="s">
@@ -10648,7 +10639,7 @@
       <c r="D95" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="E95" s="6">
+      <c r="E95" s="4">
         <v>68290</v>
       </c>
       <c r="F95" s="5" t="s">
@@ -10689,7 +10680,7 @@
       <c r="D96" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="E96" s="6">
+      <c r="E96" s="4">
         <v>255755</v>
       </c>
       <c r="F96" s="5" t="s">
@@ -10730,7 +10721,7 @@
       <c r="D97" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="E97" s="6">
+      <c r="E97" s="4">
         <v>59246</v>
       </c>
       <c r="F97" s="5" t="s">
@@ -10739,7 +10730,7 @@
       <c r="G97" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H97" s="7">
+      <c r="H97" s="6">
         <v>0.556</v>
       </c>
       <c r="I97" s="5" t="s">
@@ -10771,7 +10762,7 @@
       <c r="D98" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="E98" s="6">
+      <c r="E98" s="4">
         <v>57723</v>
       </c>
       <c r="F98" s="5" t="s">
@@ -10812,7 +10803,7 @@
       <c r="D99" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="E99" s="6">
+      <c r="E99" s="4">
         <v>95424</v>
       </c>
       <c r="F99" s="5" t="s">
@@ -10853,7 +10844,7 @@
       <c r="D100" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E100" s="6">
+      <c r="E100" s="4">
         <v>94922</v>
       </c>
       <c r="F100" s="5" t="s">
@@ -10894,7 +10885,7 @@
       <c r="D101" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="E101" s="6">
+      <c r="E101" s="4">
         <v>29260</v>
       </c>
       <c r="F101" s="5" t="s">
@@ -10903,7 +10894,7 @@
       <c r="G101" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H101" s="7">
+      <c r="H101" s="6">
         <v>0.842</v>
       </c>
       <c r="I101" s="5" t="s">
@@ -10935,7 +10926,7 @@
       <c r="D102" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="E102" s="6">
+      <c r="E102" s="4">
         <v>17965</v>
       </c>
       <c r="F102" s="5" t="s">
@@ -10944,7 +10935,7 @@
       <c r="G102" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H102" s="7">
+      <c r="H102" s="6">
         <v>0.692</v>
       </c>
       <c r="I102" s="5" t="s">
@@ -10976,7 +10967,7 @@
       <c r="D103" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E103" s="6">
+      <c r="E103" s="4">
         <v>227081</v>
       </c>
       <c r="F103" s="5" t="s">
@@ -10985,7 +10976,7 @@
       <c r="G103" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H103" s="7">
+      <c r="H103" s="6">
         <v>0.824</v>
       </c>
       <c r="I103" s="5" t="s">
@@ -11017,7 +11008,7 @@
       <c r="D104" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="E104" s="6">
+      <c r="E104" s="4">
         <v>59016</v>
       </c>
       <c r="F104" s="5" t="s">
@@ -11026,7 +11017,7 @@
       <c r="G104" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H104" s="7">
+      <c r="H104" s="6">
         <v>0.733</v>
       </c>
       <c r="I104" s="5" t="s">
@@ -11058,7 +11049,7 @@
       <c r="D105" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="E105" s="6">
+      <c r="E105" s="4">
         <v>231572</v>
       </c>
       <c r="F105" s="5" t="s">
@@ -11067,7 +11058,7 @@
       <c r="G105" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H105" s="7">
+      <c r="H105" s="6">
         <v>0.857</v>
       </c>
       <c r="I105" s="5" t="s">
@@ -11099,7 +11090,7 @@
       <c r="D106" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="E106" s="6">
+      <c r="E106" s="4">
         <v>7600</v>
       </c>
       <c r="F106" s="5" t="s">
@@ -11108,7 +11099,7 @@
       <c r="G106" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H106" s="7">
+      <c r="H106" s="6">
         <v>0.857</v>
       </c>
       <c r="I106" s="5" t="s">
@@ -11140,7 +11131,7 @@
       <c r="D107" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E107" s="6">
+      <c r="E107" s="4">
         <v>15956</v>
       </c>
       <c r="F107" s="5" t="s">
@@ -11181,7 +11172,7 @@
       <c r="D108" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="E108" s="6">
+      <c r="E108" s="4">
         <v>89222</v>
       </c>
       <c r="F108" s="5" t="s">
@@ -11222,7 +11213,7 @@
       <c r="D109" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="E109" s="6">
+      <c r="E109" s="4">
         <v>175722</v>
       </c>
       <c r="F109" s="5" t="s">
@@ -11231,7 +11222,7 @@
       <c r="G109" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H109" s="7">
+      <c r="H109" s="6">
         <v>0.692</v>
       </c>
       <c r="I109" s="5" t="s">
@@ -11263,7 +11254,7 @@
       <c r="D110" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="E110" s="6">
+      <c r="E110" s="4">
         <v>50202</v>
       </c>
       <c r="F110" s="5" t="s">
@@ -11302,7 +11293,7 @@
       <c r="D111" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="E111" s="6">
+      <c r="E111" s="4">
         <v>60444</v>
       </c>
       <c r="F111" s="5" t="s">
@@ -11311,7 +11302,7 @@
       <c r="G111" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H111" s="7">
+      <c r="H111" s="6">
         <v>0.733</v>
       </c>
       <c r="I111" s="5" t="s">
@@ -11343,7 +11334,7 @@
       <c r="D112" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="E112" s="6">
+      <c r="E112" s="4">
         <v>4188</v>
       </c>
       <c r="F112" s="5" t="s">
@@ -11352,7 +11343,7 @@
       <c r="G112" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H112" s="7">
+      <c r="H112" s="6">
         <v>0.171</v>
       </c>
       <c r="I112" s="5" t="s">
@@ -11384,7 +11375,7 @@
       <c r="D113" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E113" s="4">
         <v>18922</v>
       </c>
       <c r="F113" s="5" t="s">
@@ -11425,7 +11416,7 @@
       <c r="D114" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="E114" s="6">
+      <c r="E114" s="4">
         <v>112515</v>
       </c>
       <c r="F114" s="5" t="s">
@@ -11434,7 +11425,7 @@
       <c r="G114" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H114" s="7">
+      <c r="H114" s="6">
         <v>0.824</v>
       </c>
       <c r="I114" s="5" t="s">
@@ -11466,7 +11457,7 @@
       <c r="D115" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="E115" s="6">
+      <c r="E115" s="4">
         <v>132098</v>
       </c>
       <c r="F115" s="5" t="s">
@@ -11475,7 +11466,7 @@
       <c r="G115" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H115" s="7">
+      <c r="H115" s="6">
         <v>0.692</v>
       </c>
       <c r="I115" s="5" t="s">
@@ -11507,7 +11498,7 @@
       <c r="D116" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="E116" s="6">
+      <c r="E116" s="4">
         <v>58884</v>
       </c>
       <c r="F116" s="5" t="s">
@@ -11548,7 +11539,7 @@
       <c r="D117" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="E117" s="6">
+      <c r="E117" s="4">
         <v>85370</v>
       </c>
       <c r="F117" s="5" t="s">
@@ -11557,7 +11548,7 @@
       <c r="G117" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H117" s="7">
+      <c r="H117" s="6">
         <v>0.857</v>
       </c>
       <c r="I117" s="5" t="s">
@@ -11589,7 +11580,7 @@
       <c r="D118" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="E118" s="6">
+      <c r="E118" s="4">
         <v>159372</v>
       </c>
       <c r="F118" s="5" t="s">
@@ -11630,7 +11621,7 @@
       <c r="D119" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="E119" s="6">
+      <c r="E119" s="4">
         <v>22068</v>
       </c>
       <c r="F119" s="5" t="s">
@@ -11639,7 +11630,7 @@
       <c r="G119" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H119" s="7">
+      <c r="H119" s="6">
         <v>0.733</v>
       </c>
       <c r="I119" s="5" t="s">
@@ -11671,7 +11662,7 @@
       <c r="D120" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="E120" s="6">
+      <c r="E120" s="4">
         <v>60517</v>
       </c>
       <c r="F120" s="5" t="s">
@@ -11712,7 +11703,7 @@
       <c r="D121" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="E121" s="6">
+      <c r="E121" s="4">
         <v>45124</v>
       </c>
       <c r="F121" s="5" t="s">
@@ -11721,7 +11712,7 @@
       <c r="G121" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H121" s="7">
+      <c r="H121" s="6">
         <v>0.842</v>
       </c>
       <c r="I121" s="5" t="s">
@@ -11753,7 +11744,7 @@
       <c r="D122" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="E122" s="6">
+      <c r="E122" s="4">
         <v>74683</v>
       </c>
       <c r="F122" s="5" t="s">
@@ -11794,7 +11785,7 @@
       <c r="D123" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E123" s="4">
         <v>241641</v>
       </c>
       <c r="F123" s="5" t="s">
@@ -11844,7 +11835,7 @@
       <c r="G124" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H124" s="7">
+      <c r="H124" s="6">
         <v>0.258</v>
       </c>
       <c r="I124" s="5" t="s">
@@ -11876,7 +11867,7 @@
       <c r="D125" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="E125" s="6">
+      <c r="E125" s="4">
         <v>16101</v>
       </c>
       <c r="F125" s="5" t="s">
@@ -11885,7 +11876,7 @@
       <c r="G125" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H125" s="7">
+      <c r="H125" s="6">
         <v>0.842</v>
       </c>
       <c r="I125" s="5" t="s">
@@ -11917,7 +11908,7 @@
       <c r="D126" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="E126" s="6">
+      <c r="E126" s="4">
         <v>215876</v>
       </c>
       <c r="F126" s="5" t="s">
@@ -11958,7 +11949,7 @@
       <c r="D127" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="E127" s="6">
+      <c r="E127" s="4">
         <v>16135</v>
       </c>
       <c r="F127" s="5" t="s">
@@ -11967,7 +11958,7 @@
       <c r="G127" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H127" s="7">
+      <c r="H127" s="6">
         <v>0.842</v>
       </c>
       <c r="I127" s="5" t="s">
@@ -11999,7 +11990,7 @@
       <c r="D128" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E128" s="6">
+      <c r="E128" s="4">
         <v>221316</v>
       </c>
       <c r="F128" s="5" t="s">
@@ -12040,7 +12031,7 @@
       <c r="D129" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="E129" s="6">
+      <c r="E129" s="4">
         <v>58864</v>
       </c>
       <c r="F129" s="5" t="s">
@@ -12081,7 +12072,7 @@
       <c r="D130" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="E130" s="6">
+      <c r="E130" s="4">
         <v>126710</v>
       </c>
       <c r="F130" s="5" t="s">
@@ -12131,7 +12122,7 @@
       <c r="G131" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H131" s="7">
+      <c r="H131" s="6">
         <v>0.32</v>
       </c>
       <c r="I131" s="5" t="s">
@@ -12163,7 +12154,7 @@
       <c r="D132" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="E132" s="6">
+      <c r="E132" s="4">
         <v>12282</v>
       </c>
       <c r="F132" s="5" t="s">
@@ -12204,7 +12195,7 @@
       <c r="D133" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="E133" s="6">
+      <c r="E133" s="4">
         <v>148928</v>
       </c>
       <c r="F133" s="5" t="s">
@@ -12245,7 +12236,7 @@
       <c r="D134" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="E134" s="6">
+      <c r="E134" s="4">
         <v>48859</v>
       </c>
       <c r="F134" s="5" t="s">
@@ -12254,7 +12245,7 @@
       <c r="G134" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H134" s="7">
+      <c r="H134" s="6">
         <v>0.824</v>
       </c>
       <c r="I134" s="5" t="s">
@@ -12286,7 +12277,7 @@
       <c r="D135" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="E135" s="6">
+      <c r="E135" s="4">
         <v>46552</v>
       </c>
       <c r="F135" s="5" t="s">
@@ -12295,7 +12286,7 @@
       <c r="G135" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H135" s="7">
+      <c r="H135" s="6">
         <v>0.8</v>
       </c>
       <c r="I135" s="5" t="s">
@@ -12327,7 +12318,7 @@
       <c r="D136" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="E136" s="6">
+      <c r="E136" s="4">
         <v>48974</v>
       </c>
       <c r="F136" s="5" t="s">
@@ -12368,7 +12359,7 @@
       <c r="D137" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="E137" s="6">
+      <c r="E137" s="4">
         <v>94523</v>
       </c>
       <c r="F137" s="5" t="s">
@@ -12377,7 +12368,7 @@
       <c r="G137" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H137" s="7">
+      <c r="H137" s="6">
         <v>0.824</v>
       </c>
       <c r="I137" s="5" t="s">
@@ -12409,7 +12400,7 @@
       <c r="D138" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="E138" s="6">
+      <c r="E138" s="4">
         <v>102740</v>
       </c>
       <c r="F138" s="5" t="s">
@@ -12450,7 +12441,7 @@
       <c r="D139" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="E139" s="6">
+      <c r="E139" s="4">
         <v>300716</v>
       </c>
       <c r="F139" s="5" t="s">
@@ -12459,7 +12450,7 @@
       <c r="G139" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H139" s="7">
+      <c r="H139" s="6">
         <v>0.8</v>
       </c>
       <c r="I139" s="5" t="s">
@@ -12491,7 +12482,7 @@
       <c r="D140" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="E140" s="6">
+      <c r="E140" s="4">
         <v>60134</v>
       </c>
       <c r="F140" s="5" t="s">
@@ -12532,7 +12523,7 @@
       <c r="D141" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="E141" s="6">
+      <c r="E141" s="4">
         <v>284730</v>
       </c>
       <c r="F141" s="5" t="s">
@@ -12541,7 +12532,7 @@
       <c r="G141" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H141" s="7">
+      <c r="H141" s="6">
         <v>0.556</v>
       </c>
       <c r="I141" s="5" t="s">
@@ -12573,7 +12564,7 @@
       <c r="D142" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="E142" s="6">
+      <c r="E142" s="4">
         <v>168157</v>
       </c>
       <c r="F142" s="5" t="s">
@@ -12582,7 +12573,7 @@
       <c r="G142" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H142" s="7">
+      <c r="H142" s="6">
         <v>0.833</v>
       </c>
       <c r="I142" s="5" t="s">
@@ -12614,7 +12605,7 @@
       <c r="D143" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="E143" s="6">
+      <c r="E143" s="4">
         <v>144781</v>
       </c>
       <c r="F143" s="5" t="s">
@@ -12655,7 +12646,7 @@
       <c r="D144" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="E144" s="6">
+      <c r="E144" s="4">
         <v>21725</v>
       </c>
       <c r="F144" s="5" t="s">
@@ -12696,7 +12687,7 @@
       <c r="D145" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="E145" s="6">
+      <c r="E145" s="4">
         <v>159622</v>
       </c>
       <c r="F145" s="5" t="s">
@@ -12705,7 +12696,7 @@
       <c r="G145" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H145" s="7">
+      <c r="H145" s="6">
         <v>0.833</v>
       </c>
       <c r="I145" s="5" t="s">
@@ -12737,7 +12728,7 @@
       <c r="D146" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="E146" s="6">
+      <c r="E146" s="4">
         <v>50387</v>
       </c>
       <c r="F146" s="5" t="s">
@@ -12746,7 +12737,7 @@
       <c r="G146" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H146" s="7">
+      <c r="H146" s="6">
         <v>0.824</v>
       </c>
       <c r="I146" s="5" t="s">
@@ -12778,7 +12769,7 @@
       <c r="D147" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="E147" s="6">
+      <c r="E147" s="4">
         <v>234803</v>
       </c>
       <c r="F147" s="5" t="s">
@@ -12787,7 +12778,7 @@
       <c r="G147" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H147" s="7">
+      <c r="H147" s="6">
         <v>0.857</v>
       </c>
       <c r="I147" s="5" t="s">
@@ -12819,7 +12810,7 @@
       <c r="D148" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="E148" s="6">
+      <c r="E148" s="4">
         <v>40014</v>
       </c>
       <c r="F148" s="5" t="s">
@@ -12828,7 +12819,7 @@
       <c r="G148" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H148" s="7">
+      <c r="H148" s="6">
         <v>0.714</v>
       </c>
       <c r="I148" s="5" t="s">
@@ -12860,7 +12851,7 @@
       <c r="D149" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="E149" s="6">
+      <c r="E149" s="4">
         <v>43250</v>
       </c>
       <c r="F149" s="5" t="s">
@@ -12869,7 +12860,7 @@
       <c r="G149" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H149" s="7">
+      <c r="H149" s="6">
         <v>0.692</v>
       </c>
       <c r="I149" s="5" t="s">
@@ -12901,7 +12892,7 @@
       <c r="D150" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="E150" s="6">
+      <c r="E150" s="4">
         <v>136645</v>
       </c>
       <c r="F150" s="5" t="s">
@@ -12910,7 +12901,7 @@
       <c r="G150" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H150" s="7">
+      <c r="H150" s="6">
         <v>0.556</v>
       </c>
       <c r="I150" s="5" t="s">
@@ -12942,7 +12933,7 @@
       <c r="D151" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="E151" s="6">
+      <c r="E151" s="4">
         <v>56543</v>
       </c>
       <c r="F151" s="5" t="s">
@@ -12983,7 +12974,7 @@
       <c r="D152" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="E152" s="6">
+      <c r="E152" s="4">
         <v>139208</v>
       </c>
       <c r="F152" s="5" t="s">
@@ -12992,7 +12983,7 @@
       <c r="G152" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H152" s="7">
+      <c r="H152" s="6">
         <v>0.857</v>
       </c>
       <c r="I152" s="5" t="s">
@@ -13024,7 +13015,7 @@
       <c r="D153" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="E153" s="6">
+      <c r="E153" s="4">
         <v>258254</v>
       </c>
       <c r="F153" s="5" t="s">
@@ -13033,7 +13024,7 @@
       <c r="G153" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H153" s="7">
+      <c r="H153" s="6">
         <v>0.8</v>
       </c>
       <c r="I153" s="5" t="s">
@@ -13065,7 +13056,7 @@
       <c r="D154" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="E154" s="6">
+      <c r="E154" s="4">
         <v>45026</v>
       </c>
       <c r="F154" s="5" t="s">
@@ -13106,7 +13097,7 @@
       <c r="D155" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="E155" s="6">
+      <c r="E155" s="4">
         <v>46252</v>
       </c>
       <c r="F155" s="5" t="s">
@@ -13115,7 +13106,7 @@
       <c r="G155" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H155" s="7">
+      <c r="H155" s="6">
         <v>0.053</v>
       </c>
       <c r="I155" s="5" t="s">
@@ -13147,7 +13138,7 @@
       <c r="D156" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="E156" s="6">
+      <c r="E156" s="4">
         <v>7825</v>
       </c>
       <c r="F156" s="5" t="s">
@@ -13188,7 +13179,7 @@
       <c r="D157" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="E157" s="6">
+      <c r="E157" s="4">
         <v>121483</v>
       </c>
       <c r="F157" s="5" t="s">
@@ -13229,7 +13220,7 @@
       <c r="D158" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="E158" s="6">
+      <c r="E158" s="4">
         <v>12589</v>
       </c>
       <c r="F158" s="5" t="s">
@@ -13238,7 +13229,7 @@
       <c r="G158" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H158" s="7">
+      <c r="H158" s="6">
         <v>0.8</v>
       </c>
       <c r="I158" s="5" t="s">
@@ -13270,7 +13261,7 @@
       <c r="D159" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="E159" s="6">
+      <c r="E159" s="4">
         <v>59377</v>
       </c>
       <c r="F159" s="5" t="s">
@@ -13311,7 +13302,7 @@
       <c r="D160" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="E160" s="6">
+      <c r="E160" s="4">
         <v>15570</v>
       </c>
       <c r="F160" s="5" t="s">
@@ -13352,7 +13343,7 @@
       <c r="D161" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="E161" s="6">
+      <c r="E161" s="4">
         <v>47015</v>
       </c>
       <c r="F161" s="5" t="s">
@@ -13361,7 +13352,7 @@
       <c r="G161" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H161" s="7">
+      <c r="H161" s="6">
         <v>0.824</v>
       </c>
       <c r="I161" s="5" t="s">
@@ -13393,7 +13384,7 @@
       <c r="D162" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="E162" s="6">
+      <c r="E162" s="4">
         <v>258626</v>
       </c>
       <c r="F162" s="5" t="s">
@@ -13402,7 +13393,7 @@
       <c r="G162" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H162" s="7">
+      <c r="H162" s="6">
         <v>0.842</v>
       </c>
       <c r="I162" s="5" t="s">
@@ -13434,7 +13425,7 @@
       <c r="D163" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="E163" s="6">
+      <c r="E163" s="4">
         <v>59027</v>
       </c>
       <c r="F163" s="5" t="s">
@@ -13475,7 +13466,7 @@
       <c r="D164" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="E164" s="6">
+      <c r="E164" s="4">
         <v>240306</v>
       </c>
       <c r="F164" s="5" t="s">
@@ -13516,7 +13507,7 @@
       <c r="D165" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="E165" s="6">
+      <c r="E165" s="4">
         <v>263918</v>
       </c>
       <c r="F165" s="5" t="s">
@@ -13557,7 +13548,7 @@
       <c r="D166" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="E166" s="6">
+      <c r="E166" s="4">
         <v>89297</v>
       </c>
       <c r="F166" s="5" t="s">
@@ -13598,7 +13589,7 @@
       <c r="D167" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="E167" s="6">
+      <c r="E167" s="4">
         <v>194638</v>
       </c>
       <c r="F167" s="5" t="s">
@@ -13639,7 +13630,7 @@
       <c r="D168" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="E168" s="6">
+      <c r="E168" s="4">
         <v>69633</v>
       </c>
       <c r="F168" s="5" t="s">
@@ -13648,7 +13639,7 @@
       <c r="G168" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H168" s="7">
+      <c r="H168" s="6">
         <v>0.692</v>
       </c>
       <c r="I168" s="5" t="s">
@@ -13680,7 +13671,7 @@
       <c r="D169" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="E169" s="6">
+      <c r="E169" s="4">
         <v>119296</v>
       </c>
       <c r="F169" s="5" t="s">
@@ -13689,7 +13680,7 @@
       <c r="G169" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H169" s="7">
+      <c r="H169" s="6">
         <v>0.857</v>
       </c>
       <c r="I169" s="5" t="s">
@@ -13721,7 +13712,7 @@
       <c r="D170" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="E170" s="6">
+      <c r="E170" s="4">
         <v>182581</v>
       </c>
       <c r="F170" s="5" t="s">
@@ -13762,7 +13753,7 @@
       <c r="D171" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="E171" s="6">
+      <c r="E171" s="4">
         <v>141050</v>
       </c>
       <c r="F171" s="5" t="s">
@@ -13803,7 +13794,7 @@
       <c r="D172" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="E172" s="6">
+      <c r="E172" s="4">
         <v>57818</v>
       </c>
       <c r="F172" s="5" t="s">
@@ -13844,7 +13835,7 @@
       <c r="D173" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="E173" s="6">
+      <c r="E173" s="4">
         <v>7825</v>
       </c>
       <c r="F173" s="5" t="s">
@@ -13853,7 +13844,7 @@
       <c r="G173" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H173" s="7">
+      <c r="H173" s="6">
         <v>0.842</v>
       </c>
       <c r="I173" s="5" t="s">
@@ -13885,7 +13876,7 @@
       <c r="D174" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="E174" s="6">
+      <c r="E174" s="4">
         <v>57071</v>
       </c>
       <c r="F174" s="5" t="s">
@@ -13926,7 +13917,7 @@
       <c r="D175" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="E175" s="6">
+      <c r="E175" s="4">
         <v>432773</v>
       </c>
       <c r="F175" s="5" t="s">
@@ -13935,7 +13926,7 @@
       <c r="G175" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H175" s="7">
+      <c r="H175" s="6">
         <v>0.098</v>
       </c>
       <c r="I175" s="5" t="s">
@@ -13967,7 +13958,7 @@
       <c r="D176" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="E176" s="6">
+      <c r="E176" s="4">
         <v>122043</v>
       </c>
       <c r="F176" s="5" t="s">
@@ -14008,7 +13999,7 @@
       <c r="D177" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="E177" s="6">
+      <c r="E177" s="4">
         <v>265127</v>
       </c>
       <c r="F177" s="5" t="s">
@@ -14017,7 +14008,7 @@
       <c r="G177" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H177" s="7">
+      <c r="H177" s="6">
         <v>0.556</v>
       </c>
       <c r="I177" s="5" t="s">
@@ -14049,7 +14040,7 @@
       <c r="D178" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="E178" s="6">
+      <c r="E178" s="4">
         <v>212718</v>
       </c>
       <c r="F178" s="5" t="s">
@@ -14058,7 +14049,7 @@
       <c r="G178" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H178" s="7">
+      <c r="H178" s="6">
         <v>0.556</v>
       </c>
       <c r="I178" s="5" t="s">
@@ -14090,7 +14081,7 @@
       <c r="D179" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="E179" s="6">
+      <c r="E179" s="4">
         <v>125781</v>
       </c>
       <c r="F179" s="5" t="s">
@@ -14131,7 +14122,7 @@
       <c r="D180" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="E180" s="6">
+      <c r="E180" s="4">
         <v>287579</v>
       </c>
       <c r="F180" s="5" t="s">
@@ -14172,7 +14163,7 @@
       <c r="D181" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="E181" s="6">
+      <c r="E181" s="4">
         <v>147520</v>
       </c>
       <c r="F181" s="5" t="s">
@@ -14181,7 +14172,7 @@
       <c r="G181" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H181" s="7">
+      <c r="H181" s="6">
         <v>0.824</v>
       </c>
       <c r="I181" s="5" t="s">
@@ -14213,7 +14204,7 @@
       <c r="D182" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="E182" s="6">
+      <c r="E182" s="4">
         <v>111455</v>
       </c>
       <c r="F182" s="5" t="s">
@@ -14222,7 +14213,7 @@
       <c r="G182" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H182" s="7">
+      <c r="H182" s="6">
         <v>0.533</v>
       </c>
       <c r="I182" s="5" t="s">
@@ -14254,7 +14245,7 @@
       <c r="D183" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="E183" s="6">
+      <c r="E183" s="4">
         <v>29241</v>
       </c>
       <c r="F183" s="5" t="s">
@@ -14295,7 +14286,7 @@
       <c r="D184" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="E184" s="6">
+      <c r="E184" s="4">
         <v>120072</v>
       </c>
       <c r="F184" s="5" t="s">
@@ -14304,7 +14295,7 @@
       <c r="G184" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H184" s="7">
+      <c r="H184" s="6">
         <v>0.706</v>
       </c>
       <c r="I184" s="5" t="s">
@@ -14336,7 +14327,7 @@
       <c r="D185" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="E185" s="6">
+      <c r="E185" s="4">
         <v>116686</v>
       </c>
       <c r="F185" s="5" t="s">
@@ -14377,7 +14368,7 @@
       <c r="D186" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="E186" s="6">
+      <c r="E186" s="4">
         <v>155689</v>
       </c>
       <c r="F186" s="5" t="s">
@@ -14418,7 +14409,7 @@
       <c r="D187" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="E187" s="6">
+      <c r="E187" s="4">
         <v>200056</v>
       </c>
       <c r="F187" s="5" t="s">
@@ -14459,7 +14450,7 @@
       <c r="D188" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="E188" s="6">
+      <c r="E188" s="4">
         <v>182574</v>
       </c>
       <c r="F188" s="5" t="s">
@@ -14500,7 +14491,7 @@
       <c r="D189" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="E189" s="6">
+      <c r="E189" s="4">
         <v>121985</v>
       </c>
       <c r="F189" s="5" t="s">
@@ -14541,7 +14532,7 @@
       <c r="D190" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="E190" s="6">
+      <c r="E190" s="4">
         <v>111038</v>
       </c>
       <c r="F190" s="5" t="s">
@@ -14550,7 +14541,7 @@
       <c r="G190" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H190" s="7">
+      <c r="H190" s="6">
         <v>0.833</v>
       </c>
       <c r="I190" s="5" t="s">
@@ -14582,7 +14573,7 @@
       <c r="D191" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="E191" s="6">
+      <c r="E191" s="4">
         <v>17350</v>
       </c>
       <c r="F191" s="5" t="s">
@@ -14591,7 +14582,7 @@
       <c r="G191" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H191" s="7">
+      <c r="H191" s="6">
         <v>0.556</v>
       </c>
       <c r="I191" s="5" t="s">
@@ -14623,7 +14614,7 @@
       <c r="D192" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="E192" s="6">
+      <c r="E192" s="4">
         <v>39333</v>
       </c>
       <c r="F192" s="5" t="s">
@@ -14632,7 +14623,7 @@
       <c r="G192" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H192" s="7">
+      <c r="H192" s="6">
         <v>0.842</v>
       </c>
       <c r="I192" s="5" t="s">
@@ -14664,7 +14655,7 @@
       <c r="D193" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="E193" s="6">
+      <c r="E193" s="4">
         <v>33947</v>
       </c>
       <c r="F193" s="5" t="s">
@@ -14673,7 +14664,7 @@
       <c r="G193" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H193" s="7">
+      <c r="H193" s="6">
         <v>0.733</v>
       </c>
       <c r="I193" s="5" t="s">
@@ -14705,7 +14696,7 @@
       <c r="D194" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="E194" s="6">
+      <c r="E194" s="4">
         <v>61253</v>
       </c>
       <c r="F194" s="5" t="s">
@@ -14746,7 +14737,7 @@
       <c r="D195" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="E195" s="6">
+      <c r="E195" s="4">
         <v>127032</v>
       </c>
       <c r="F195" s="5" t="s">
@@ -14755,7 +14746,7 @@
       <c r="G195" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H195" s="7">
+      <c r="H195" s="6">
         <v>0.692</v>
       </c>
       <c r="I195" s="5" t="s">
@@ -14787,7 +14778,7 @@
       <c r="D196" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="E196" s="6">
+      <c r="E196" s="4">
         <v>53622</v>
       </c>
       <c r="F196" s="5" t="s">
@@ -14828,7 +14819,7 @@
       <c r="D197" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="E197" s="6">
+      <c r="E197" s="4">
         <v>27240</v>
       </c>
       <c r="F197" s="5" t="s">
@@ -14837,7 +14828,7 @@
       <c r="G197" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H197" s="7">
+      <c r="H197" s="6">
         <v>0.556</v>
       </c>
       <c r="I197" s="5" t="s">
@@ -14869,7 +14860,7 @@
       <c r="D198" s="5" t="s">
         <v>657</v>
       </c>
-      <c r="E198" s="6">
+      <c r="E198" s="4">
         <v>105899</v>
       </c>
       <c r="F198" s="5" t="s">
@@ -14878,7 +14869,7 @@
       <c r="G198" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H198" s="7">
+      <c r="H198" s="6">
         <v>0.824</v>
       </c>
       <c r="I198" s="5" t="s">
@@ -14910,7 +14901,7 @@
       <c r="D199" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="E199" s="6">
+      <c r="E199" s="4">
         <v>17184</v>
       </c>
       <c r="F199" s="5" t="s">
@@ -14949,7 +14940,7 @@
       <c r="D200" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="E200" s="6">
+      <c r="E200" s="4">
         <v>225083</v>
       </c>
       <c r="F200" s="5" t="s">
@@ -14958,7 +14949,7 @@
       <c r="G200" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H200" s="7">
+      <c r="H200" s="6">
         <v>0.824</v>
       </c>
       <c r="I200" s="5" t="s">
@@ -14990,7 +14981,7 @@
       <c r="D201" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E201" s="6">
+      <c r="E201" s="4">
         <v>76163</v>
       </c>
       <c r="F201" s="5" t="s">
@@ -14999,7 +14990,7 @@
       <c r="G201" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H201" s="7">
+      <c r="H201" s="6">
         <v>0.824</v>
       </c>
       <c r="I201" s="5" t="s">
@@ -15031,7 +15022,7 @@
       <c r="D202" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="E202" s="6">
+      <c r="E202" s="4">
         <v>147487</v>
       </c>
       <c r="F202" s="5" t="s">
@@ -15072,7 +15063,7 @@
       <c r="D203" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="E203" s="6">
+      <c r="E203" s="4">
         <v>33923</v>
       </c>
       <c r="F203" s="5" t="s">
@@ -15081,7 +15072,7 @@
       <c r="G203" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H203" s="7">
+      <c r="H203" s="6">
         <v>0.842</v>
       </c>
       <c r="I203" s="5" t="s">
@@ -15113,7 +15104,7 @@
       <c r="D204" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="E204" s="6">
+      <c r="E204" s="4">
         <v>134425</v>
       </c>
       <c r="F204" s="5" t="s">
@@ -15154,7 +15145,7 @@
       <c r="D205" s="5" t="s">
         <v>677</v>
       </c>
-      <c r="E205" s="6">
+      <c r="E205" s="4">
         <v>190393</v>
       </c>
       <c r="F205" s="5" t="s">
@@ -15163,7 +15154,7 @@
       <c r="G205" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H205" s="7">
+      <c r="H205" s="6">
         <v>0.733</v>
       </c>
       <c r="I205" s="5" t="s">
@@ -15195,7 +15186,7 @@
       <c r="D206" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="E206" s="6">
+      <c r="E206" s="4">
         <v>4360</v>
       </c>
       <c r="F206" s="5" t="s">
@@ -15204,7 +15195,7 @@
       <c r="G206" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H206" s="7">
+      <c r="H206" s="6">
         <v>0.733</v>
       </c>
       <c r="I206" s="5" t="s">
@@ -15236,7 +15227,7 @@
       <c r="D207" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="E207" s="6">
+      <c r="E207" s="4">
         <v>34495</v>
       </c>
       <c r="F207" s="5" t="s">
@@ -15245,7 +15236,7 @@
       <c r="G207" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H207" s="7">
+      <c r="H207" s="6">
         <v>0.842</v>
       </c>
       <c r="I207" s="5" t="s">
@@ -15277,7 +15268,7 @@
       <c r="D208" s="5" t="s">
         <v>686</v>
       </c>
-      <c r="E208" s="6">
+      <c r="E208" s="4">
         <v>174504</v>
       </c>
       <c r="F208" s="5" t="s">
@@ -15286,7 +15277,7 @@
       <c r="G208" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H208" s="7">
+      <c r="H208" s="6">
         <v>0.824</v>
       </c>
       <c r="I208" s="5" t="s">
@@ -15318,7 +15309,7 @@
       <c r="D209" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="E209" s="6">
+      <c r="E209" s="4">
         <v>64339</v>
       </c>
       <c r="F209" s="5" t="s">
@@ -15327,7 +15318,7 @@
       <c r="G209" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H209" s="7">
+      <c r="H209" s="6">
         <v>0.824</v>
       </c>
       <c r="I209" s="5" t="s">
@@ -15359,7 +15350,7 @@
       <c r="D210" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="E210" s="6">
+      <c r="E210" s="4">
         <v>56416</v>
       </c>
       <c r="F210" s="5" t="s">
@@ -15400,7 +15391,7 @@
       <c r="D211" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="E211" s="6">
+      <c r="E211" s="4">
         <v>69184</v>
       </c>
       <c r="F211" s="5" t="s">
@@ -15441,7 +15432,7 @@
       <c r="D212" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="E212" s="6">
+      <c r="E212" s="4">
         <v>93740</v>
       </c>
       <c r="F212" s="5" t="s">
@@ -15482,7 +15473,7 @@
       <c r="D213" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="E213" s="6">
+      <c r="E213" s="4">
         <v>37666</v>
       </c>
       <c r="F213" s="5" t="s">
@@ -15491,7 +15482,7 @@
       <c r="G213" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H213" s="7">
+      <c r="H213" s="6">
         <v>0.733</v>
       </c>
       <c r="I213" s="5" t="s">
@@ -15523,7 +15514,7 @@
       <c r="D214" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="E214" s="6">
+      <c r="E214" s="4">
         <v>296622</v>
       </c>
       <c r="F214" s="5" t="s">
@@ -15564,7 +15555,7 @@
       <c r="D215" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="E215" s="6">
+      <c r="E215" s="4">
         <v>113358</v>
       </c>
       <c r="F215" s="5" t="s">
@@ -15573,7 +15564,7 @@
       <c r="G215" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H215" s="7">
+      <c r="H215" s="6">
         <v>0.833</v>
       </c>
       <c r="I215" s="5" t="s">
@@ -15605,7 +15596,7 @@
       <c r="D216" s="5" t="s">
         <v>711</v>
       </c>
-      <c r="E216" s="6">
+      <c r="E216" s="4">
         <v>213605</v>
       </c>
       <c r="F216" s="5" t="s">
@@ -15646,7 +15637,7 @@
       <c r="D217" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="E217" s="6">
+      <c r="E217" s="4">
         <v>29364</v>
       </c>
       <c r="F217" s="5" t="s">
@@ -15655,7 +15646,7 @@
       <c r="G217" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H217" s="7">
+      <c r="H217" s="6">
         <v>0.8</v>
       </c>
       <c r="I217" s="5" t="s">
@@ -15687,7 +15678,7 @@
       <c r="D218" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="E218" s="6">
+      <c r="E218" s="4">
         <v>236693</v>
       </c>
       <c r="F218" s="5" t="s">
@@ -15696,7 +15687,7 @@
       <c r="G218" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H218" s="7">
+      <c r="H218" s="6">
         <v>0.556</v>
       </c>
       <c r="I218" s="5" t="s">
@@ -15728,7 +15719,7 @@
       <c r="D219" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="E219" s="6">
+      <c r="E219" s="4">
         <v>129554</v>
       </c>
       <c r="F219" s="5" t="s">
@@ -15769,7 +15760,7 @@
       <c r="D220" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="E220" s="6">
+      <c r="E220" s="4">
         <v>38593</v>
       </c>
       <c r="F220" s="5" t="s">
@@ -15810,7 +15801,7 @@
       <c r="D221" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="E221" s="6">
+      <c r="E221" s="4">
         <v>82105</v>
       </c>
       <c r="F221" s="5" t="s">
@@ -15819,7 +15810,7 @@
       <c r="G221" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H221" s="7">
+      <c r="H221" s="6">
         <v>0.857</v>
       </c>
       <c r="I221" s="5" t="s">
@@ -15851,7 +15842,7 @@
       <c r="D222" s="5" t="s">
         <v>729</v>
       </c>
-      <c r="E222" s="6">
+      <c r="E222" s="4">
         <v>371998</v>
       </c>
       <c r="F222" s="5" t="s">
@@ -15860,7 +15851,7 @@
       <c r="G222" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H222" s="7">
+      <c r="H222" s="6">
         <v>0.25</v>
       </c>
       <c r="I222" s="5" t="s">
@@ -15892,7 +15883,7 @@
       <c r="D223" s="5" t="s">
         <v>732</v>
       </c>
-      <c r="E223" s="6">
+      <c r="E223" s="4">
         <v>257448</v>
       </c>
       <c r="F223" s="5" t="s">
@@ -15933,7 +15924,7 @@
       <c r="D224" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="E224" s="6">
+      <c r="E224" s="4">
         <v>36025</v>
       </c>
       <c r="F224" s="5" t="s">
@@ -15942,7 +15933,7 @@
       <c r="G224" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H224" s="7">
+      <c r="H224" s="6">
         <v>0.8</v>
       </c>
       <c r="I224" s="5" t="s">
@@ -15974,7 +15965,7 @@
       <c r="D225" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="E225" s="6">
+      <c r="E225" s="4">
         <v>70243</v>
       </c>
       <c r="F225" s="5" t="s">
@@ -16015,7 +16006,7 @@
       <c r="D226" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="E226" s="6">
+      <c r="E226" s="4">
         <v>148751</v>
       </c>
       <c r="F226" s="5" t="s">
@@ -16056,7 +16047,7 @@
       <c r="D227" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="E227" s="6">
+      <c r="E227" s="4">
         <v>34572</v>
       </c>
       <c r="F227" s="5" t="s">
@@ -16065,7 +16056,7 @@
       <c r="G227" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H227" s="7">
+      <c r="H227" s="6">
         <v>0.842</v>
       </c>
       <c r="I227" s="5" t="s">
@@ -16097,7 +16088,7 @@
       <c r="D228" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="E228" s="6">
+      <c r="E228" s="4">
         <v>196948</v>
       </c>
       <c r="F228" s="5" t="s">
@@ -16106,7 +16097,7 @@
       <c r="G228" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H228" s="7">
+      <c r="H228" s="6">
         <v>0.824</v>
       </c>
       <c r="I228" s="5" t="s">
@@ -16138,7 +16129,7 @@
       <c r="D229" s="5" t="s">
         <v>750</v>
       </c>
-      <c r="E229" s="6">
+      <c r="E229" s="4">
         <v>215599</v>
       </c>
       <c r="F229" s="5" t="s">
@@ -16179,7 +16170,7 @@
       <c r="D230" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="E230" s="6">
+      <c r="E230" s="4">
         <v>186590</v>
       </c>
       <c r="F230" s="5" t="s">
@@ -16220,7 +16211,7 @@
       <c r="D231" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="E231" s="6">
+      <c r="E231" s="4">
         <v>36688</v>
       </c>
       <c r="F231" s="5" t="s">
@@ -16261,7 +16252,7 @@
       <c r="D232" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="E232" s="6">
+      <c r="E232" s="4">
         <v>34322</v>
       </c>
       <c r="F232" s="5" t="s">
@@ -16302,7 +16293,7 @@
       <c r="D233" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="E233" s="6">
+      <c r="E233" s="4">
         <v>15452</v>
       </c>
       <c r="F233" s="5" t="s">
@@ -16343,7 +16334,7 @@
       <c r="D234" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="E234" s="6">
+      <c r="E234" s="4">
         <v>52893</v>
       </c>
       <c r="F234" s="5" t="s">
@@ -16352,7 +16343,7 @@
       <c r="G234" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H234" s="7">
+      <c r="H234" s="6">
         <v>0.556</v>
       </c>
       <c r="I234" s="5" t="s">
@@ -16384,7 +16375,7 @@
       <c r="D235" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="E235" s="6">
+      <c r="E235" s="4">
         <v>102427</v>
       </c>
       <c r="F235" s="5" t="s">
@@ -16425,7 +16416,7 @@
       <c r="D236" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="E236" s="6">
+      <c r="E236" s="4">
         <v>192765</v>
       </c>
       <c r="F236" s="5" t="s">
@@ -16434,7 +16425,7 @@
       <c r="G236" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H236" s="7">
+      <c r="H236" s="6">
         <v>0.692</v>
       </c>
       <c r="I236" s="5" t="s">
@@ -16466,7 +16457,7 @@
       <c r="D237" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="E237" s="6">
+      <c r="E237" s="4">
         <v>100131</v>
       </c>
       <c r="F237" s="5" t="s">
@@ -16507,7 +16498,7 @@
       <c r="D238" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="E238" s="6">
+      <c r="E238" s="4">
         <v>15362</v>
       </c>
       <c r="F238" s="5" t="s">
@@ -16546,7 +16537,7 @@
       <c r="D239" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="E239" s="6">
+      <c r="E239" s="4">
         <v>17491</v>
       </c>
       <c r="F239" s="5" t="s">
@@ -16555,7 +16546,7 @@
       <c r="G239" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H239" s="7">
+      <c r="H239" s="6">
         <v>0.556</v>
       </c>
       <c r="I239" s="5" t="s">
@@ -16587,7 +16578,7 @@
       <c r="D240" s="5" t="s">
         <v>783</v>
       </c>
-      <c r="E240" s="6">
+      <c r="E240" s="4">
         <v>93128</v>
       </c>
       <c r="F240" s="5" t="s">
@@ -16628,7 +16619,7 @@
       <c r="D241" s="5" t="s">
         <v>786</v>
       </c>
-      <c r="E241" s="6">
+      <c r="E241" s="4">
         <v>225693</v>
       </c>
       <c r="F241" s="5" t="s">
@@ -16637,7 +16628,7 @@
       <c r="G241" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H241" s="7">
+      <c r="H241" s="6">
         <v>0.8</v>
       </c>
       <c r="I241" s="5" t="s">
@@ -16669,7 +16660,7 @@
       <c r="D242" s="5" t="s">
         <v>789</v>
       </c>
-      <c r="E242" s="6">
+      <c r="E242" s="4">
         <v>88262</v>
       </c>
       <c r="F242" s="5" t="s">
@@ -16678,7 +16669,7 @@
       <c r="G242" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H242" s="7">
+      <c r="H242" s="6">
         <v>0.8</v>
       </c>
       <c r="I242" s="5" t="s">
@@ -16710,7 +16701,7 @@
       <c r="D243" s="5" t="s">
         <v>792</v>
       </c>
-      <c r="E243" s="6">
+      <c r="E243" s="4">
         <v>34593</v>
       </c>
       <c r="F243" s="5" t="s">
@@ -16751,7 +16742,7 @@
       <c r="D244" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="E244" s="6">
+      <c r="E244" s="4">
         <v>187530</v>
       </c>
       <c r="F244" s="5" t="s">
@@ -16760,7 +16751,7 @@
       <c r="G244" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H244" s="7">
+      <c r="H244" s="6">
         <v>0.714</v>
       </c>
       <c r="I244" s="5" t="s">
@@ -16792,7 +16783,7 @@
       <c r="D245" s="5" t="s">
         <v>798</v>
       </c>
-      <c r="E245" s="6">
+      <c r="E245" s="4">
         <v>184573</v>
       </c>
       <c r="F245" s="5" t="s">
@@ -16833,7 +16824,7 @@
       <c r="D246" s="5" t="s">
         <v>801</v>
       </c>
-      <c r="E246" s="6">
+      <c r="E246" s="4">
         <v>26128</v>
       </c>
       <c r="F246" s="5" t="s">
@@ -16842,7 +16833,7 @@
       <c r="G246" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H246" s="7">
+      <c r="H246" s="6">
         <v>0.824</v>
       </c>
       <c r="I246" s="5" t="s">
@@ -16874,7 +16865,7 @@
       <c r="D247" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="E247" s="6">
+      <c r="E247" s="4">
         <v>193469</v>
       </c>
       <c r="F247" s="5" t="s">
@@ -16883,7 +16874,7 @@
       <c r="G247" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H247" s="7">
+      <c r="H247" s="6">
         <v>0.714</v>
       </c>
       <c r="I247" s="5" t="s">
@@ -16902,7 +16893,7 @@
         <v>805</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="18.75" hidden="1">
       <c r="A248" s="4">
         <v>2018</v>
       </c>
@@ -16915,7 +16906,7 @@
       <c r="D248" s="5" t="s">
         <v>807</v>
       </c>
-      <c r="E248" s="6">
+      <c r="E248" s="4">
         <v>4042</v>
       </c>
       <c r="F248" s="5" t="s">
@@ -16956,7 +16947,7 @@
       <c r="D249" s="5" t="s">
         <v>810</v>
       </c>
-      <c r="E249" s="6">
+      <c r="E249" s="4">
         <v>12518</v>
       </c>
       <c r="F249" s="5" t="s">
@@ -16965,7 +16956,7 @@
       <c r="G249" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H249" s="7">
+      <c r="H249" s="6">
         <v>0.714</v>
       </c>
       <c r="I249" s="5" t="s">
@@ -16997,7 +16988,7 @@
       <c r="D250" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="E250" s="6">
+      <c r="E250" s="4">
         <v>249994</v>
       </c>
       <c r="F250" s="5" t="s">
@@ -17038,7 +17029,7 @@
       <c r="D251" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="E251" s="6">
+      <c r="E251" s="4">
         <v>45671</v>
       </c>
       <c r="F251" s="5" t="s">
@@ -17047,7 +17038,7 @@
       <c r="G251" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H251" s="7">
+      <c r="H251" s="6">
         <v>0.842</v>
       </c>
       <c r="I251" s="5" t="s">
@@ -17079,7 +17070,7 @@
       <c r="D252" s="5" t="s">
         <v>819</v>
       </c>
-      <c r="E252" s="6">
+      <c r="E252" s="4">
         <v>27511</v>
       </c>
       <c r="F252" s="5" t="s">
@@ -17088,7 +17079,7 @@
       <c r="G252" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H252" s="7">
+      <c r="H252" s="6">
         <v>0.824</v>
       </c>
       <c r="I252" s="5" t="s">
@@ -17120,7 +17111,7 @@
       <c r="D253" s="5" t="s">
         <v>822</v>
       </c>
-      <c r="E253" s="6">
+      <c r="E253" s="4">
         <v>163086</v>
       </c>
       <c r="F253" s="5" t="s">
@@ -17161,7 +17152,7 @@
       <c r="D254" s="5" t="s">
         <v>825</v>
       </c>
-      <c r="E254" s="6">
+      <c r="E254" s="4">
         <v>344695</v>
       </c>
       <c r="F254" s="5" t="s">
@@ -17202,7 +17193,7 @@
       <c r="D255" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="E255" s="6">
+      <c r="E255" s="4">
         <v>26399</v>
       </c>
       <c r="F255" s="5" t="s">
@@ -17243,7 +17234,7 @@
       <c r="D256" s="5" t="s">
         <v>831</v>
       </c>
-      <c r="E256" s="6">
+      <c r="E256" s="4">
         <v>283130</v>
       </c>
       <c r="F256" s="5" t="s">
@@ -17284,7 +17275,7 @@
       <c r="D257" s="5" t="s">
         <v>834</v>
       </c>
-      <c r="E257" s="6">
+      <c r="E257" s="4">
         <v>48987</v>
       </c>
       <c r="F257" s="5" t="s">
@@ -17323,7 +17314,7 @@
       <c r="D258" s="5" t="s">
         <v>837</v>
       </c>
-      <c r="E258" s="6">
+      <c r="E258" s="4">
         <v>5404</v>
       </c>
       <c r="F258" s="5" t="s">
@@ -17364,7 +17355,7 @@
       <c r="D259" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="E259" s="6">
+      <c r="E259" s="4">
         <v>77966</v>
       </c>
       <c r="F259" s="5" t="s">
@@ -17373,7 +17364,7 @@
       <c r="G259" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H259" s="7">
+      <c r="H259" s="6">
         <v>0.842</v>
       </c>
       <c r="I259" s="5" t="s">
@@ -17405,7 +17396,7 @@
       <c r="D260" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="E260" s="6">
+      <c r="E260" s="4">
         <v>230784</v>
       </c>
       <c r="F260" s="5" t="s">
@@ -17446,7 +17437,7 @@
       <c r="D261" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="E261" s="6">
+      <c r="E261" s="4">
         <v>60410</v>
       </c>
       <c r="F261" s="5" t="s">
@@ -17487,7 +17478,7 @@
       <c r="D262" s="5" t="s">
         <v>849</v>
       </c>
-      <c r="E262" s="6">
+      <c r="E262" s="4">
         <v>60889</v>
       </c>
       <c r="F262" s="5" t="s">
@@ -17496,7 +17487,7 @@
       <c r="G262" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H262" s="7">
+      <c r="H262" s="6">
         <v>0.842</v>
       </c>
       <c r="I262" s="5" t="s">
@@ -17528,7 +17519,7 @@
       <c r="D263" s="5" t="s">
         <v>852</v>
       </c>
-      <c r="E263" s="6">
+      <c r="E263" s="4">
         <v>182381</v>
       </c>
       <c r="F263" s="5" t="s">
@@ -17569,7 +17560,7 @@
       <c r="D264" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="E264" s="6">
+      <c r="E264" s="4">
         <v>661171</v>
       </c>
       <c r="F264" s="5" t="s">
@@ -17578,7 +17569,7 @@
       <c r="G264" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H264" s="7">
+      <c r="H264" s="6">
         <v>0.824</v>
       </c>
       <c r="I264" s="5" t="s">
@@ -17610,7 +17601,7 @@
       <c r="D265" s="5" t="s">
         <v>858</v>
       </c>
-      <c r="E265" s="6">
+      <c r="E265" s="4">
         <v>207929</v>
       </c>
       <c r="F265" s="5" t="s">
@@ -17619,7 +17610,7 @@
       <c r="G265" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H265" s="7">
+      <c r="H265" s="6">
         <v>0.692</v>
       </c>
       <c r="I265" s="5" t="s">
@@ -17651,7 +17642,7 @@
       <c r="D266" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E266" s="6">
+      <c r="E266" s="4">
         <v>15956</v>
       </c>
       <c r="F266" s="5" t="s">
@@ -17660,7 +17651,7 @@
       <c r="G266" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H266" s="7">
+      <c r="H266" s="6">
         <v>0.824</v>
       </c>
       <c r="I266" s="5" t="s">
@@ -17692,7 +17683,7 @@
       <c r="D267" s="5" t="s">
         <v>863</v>
       </c>
-      <c r="E267" s="6">
+      <c r="E267" s="4">
         <v>91845</v>
       </c>
       <c r="F267" s="5" t="s">
@@ -17731,7 +17722,7 @@
       <c r="D268" s="5" t="s">
         <v>866</v>
       </c>
-      <c r="E268" s="6">
+      <c r="E268" s="4">
         <v>35518</v>
       </c>
       <c r="F268" s="5" t="s">
@@ -17772,7 +17763,7 @@
       <c r="D269" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="E269" s="6">
+      <c r="E269" s="4">
         <v>249126</v>
       </c>
       <c r="F269" s="5" t="s">
@@ -17781,7 +17772,7 @@
       <c r="G269" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H269" s="7">
+      <c r="H269" s="6">
         <v>0.692</v>
       </c>
       <c r="I269" s="5" t="s">
@@ -17813,7 +17804,7 @@
       <c r="D270" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="E270" s="6">
+      <c r="E270" s="4">
         <v>126633</v>
       </c>
       <c r="F270" s="5" t="s">
@@ -17822,7 +17813,7 @@
       <c r="G270" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H270" s="7">
+      <c r="H270" s="6">
         <v>0.16</v>
       </c>
       <c r="I270" s="5" t="s">
@@ -17854,7 +17845,7 @@
       <c r="D271" s="5" t="s">
         <v>875</v>
       </c>
-      <c r="E271" s="6">
+      <c r="E271" s="4">
         <v>185024</v>
       </c>
       <c r="F271" s="5" t="s">
@@ -17895,7 +17886,7 @@
       <c r="D272" s="5" t="s">
         <v>878</v>
       </c>
-      <c r="E272" s="6">
+      <c r="E272" s="4">
         <v>302215</v>
       </c>
       <c r="F272" s="5" t="s">
@@ -17936,7 +17927,7 @@
       <c r="D273" s="5" t="s">
         <v>881</v>
       </c>
-      <c r="E273" s="6">
+      <c r="E273" s="4">
         <v>38388</v>
       </c>
       <c r="F273" s="5" t="s">
@@ -17945,7 +17936,7 @@
       <c r="G273" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H273" s="7">
+      <c r="H273" s="6">
         <v>0.714</v>
       </c>
       <c r="I273" s="5" t="s">
@@ -17977,7 +17968,7 @@
       <c r="D274" s="5" t="s">
         <v>884</v>
       </c>
-      <c r="E274" s="6">
+      <c r="E274" s="4">
         <v>243878</v>
       </c>
       <c r="F274" s="5" t="s">
@@ -17986,7 +17977,7 @@
       <c r="G274" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H274" s="7">
+      <c r="H274" s="6">
         <v>0.556</v>
       </c>
       <c r="I274" s="5" t="s">
@@ -18018,7 +18009,7 @@
       <c r="D275" s="5" t="s">
         <v>887</v>
       </c>
-      <c r="E275" s="6">
+      <c r="E275" s="4">
         <v>44068</v>
       </c>
       <c r="F275" s="5" t="s">
@@ -18059,7 +18050,7 @@
       <c r="D276" s="5" t="s">
         <v>890</v>
       </c>
-      <c r="E276" s="6">
+      <c r="E276" s="4">
         <v>91970</v>
       </c>
       <c r="F276" s="5" t="s">
@@ -18068,7 +18059,7 @@
       <c r="G276" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H276" s="7">
+      <c r="H276" s="6">
         <v>0.842</v>
       </c>
       <c r="I276" s="5" t="s">
@@ -18100,7 +18091,7 @@
       <c r="D277" s="5" t="s">
         <v>893</v>
       </c>
-      <c r="E277" s="6">
+      <c r="E277" s="4">
         <v>70097</v>
       </c>
       <c r="F277" s="5" t="s">
@@ -18141,7 +18132,7 @@
       <c r="D278" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="E278" s="6">
+      <c r="E278" s="4">
         <v>53418</v>
       </c>
       <c r="F278" s="5" t="s">
@@ -18182,7 +18173,7 @@
       <c r="D279" s="5" t="s">
         <v>899</v>
       </c>
-      <c r="E279" s="6">
+      <c r="E279" s="4">
         <v>380415</v>
       </c>
       <c r="F279" s="5" t="s">
@@ -18191,7 +18182,7 @@
       <c r="G279" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H279" s="7">
+      <c r="H279" s="6">
         <v>0.833</v>
       </c>
       <c r="I279" s="5" t="s">
@@ -18223,7 +18214,7 @@
       <c r="D280" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="E280" s="6">
+      <c r="E280" s="4">
         <v>183383</v>
       </c>
       <c r="F280" s="5" t="s">
@@ -18232,7 +18223,7 @@
       <c r="G280" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H280" s="7">
+      <c r="H280" s="6">
         <v>0.833</v>
       </c>
       <c r="I280" s="5" t="s">
@@ -18264,7 +18255,7 @@
       <c r="D281" s="5" t="s">
         <v>905</v>
       </c>
-      <c r="E281" s="6">
+      <c r="E281" s="4">
         <v>111078</v>
       </c>
       <c r="F281" s="5" t="s">
@@ -18305,7 +18296,7 @@
       <c r="D282" s="5" t="s">
         <v>908</v>
       </c>
-      <c r="E282" s="6">
+      <c r="E282" s="4">
         <v>57229</v>
       </c>
       <c r="F282" s="5" t="s">
@@ -18314,7 +18305,7 @@
       <c r="G282" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H282" s="7">
+      <c r="H282" s="6">
         <v>0.857</v>
       </c>
       <c r="I282" s="5" t="s">
@@ -18346,7 +18337,7 @@
       <c r="D283" s="5" t="s">
         <v>911</v>
       </c>
-      <c r="E283" s="6">
+      <c r="E283" s="4">
         <v>81785</v>
       </c>
       <c r="F283" s="5" t="s">
@@ -18387,7 +18378,7 @@
       <c r="D284" s="5" t="s">
         <v>914</v>
       </c>
-      <c r="E284" s="6">
+      <c r="E284" s="4">
         <v>84535</v>
       </c>
       <c r="F284" s="5" t="s">
@@ -18396,7 +18387,7 @@
       <c r="G284" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H284" s="7">
+      <c r="H284" s="6">
         <v>0.824</v>
       </c>
       <c r="I284" s="5" t="s">
@@ -18428,7 +18419,7 @@
       <c r="D285" s="5" t="s">
         <v>917</v>
       </c>
-      <c r="E285" s="6">
+      <c r="E285" s="4">
         <v>165579</v>
       </c>
       <c r="F285" s="5" t="s">
@@ -18437,7 +18428,7 @@
       <c r="G285" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H285" s="7">
+      <c r="H285" s="6">
         <v>0.824</v>
       </c>
       <c r="I285" s="5" t="s">
@@ -18469,7 +18460,7 @@
       <c r="D286" s="5" t="s">
         <v>920</v>
       </c>
-      <c r="E286" s="6">
+      <c r="E286" s="4">
         <v>167931</v>
       </c>
       <c r="F286" s="5" t="s">
@@ -18478,7 +18469,7 @@
       <c r="G286" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H286" s="7">
+      <c r="H286" s="6">
         <v>0.824</v>
       </c>
       <c r="I286" s="5" t="s">
@@ -18510,7 +18501,7 @@
       <c r="D287" s="5" t="s">
         <v>923</v>
       </c>
-      <c r="E287" s="6">
+      <c r="E287" s="4">
         <v>88682</v>
       </c>
       <c r="F287" s="5" t="s">
@@ -18519,7 +18510,7 @@
       <c r="G287" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H287" s="7">
+      <c r="H287" s="6">
         <v>0.842</v>
       </c>
       <c r="I287" s="5" t="s">
@@ -18551,7 +18542,7 @@
       <c r="D288" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="E288" s="6">
+      <c r="E288" s="4">
         <v>133964</v>
       </c>
       <c r="F288" s="5" t="s">
@@ -18592,7 +18583,7 @@
       <c r="D289" s="5" t="s">
         <v>929</v>
       </c>
-      <c r="E289" s="6">
+      <c r="E289" s="4">
         <v>1422277</v>
       </c>
       <c r="F289" s="5" t="s">
@@ -18633,7 +18624,7 @@
       <c r="D290" s="5" t="s">
         <v>932</v>
       </c>
-      <c r="E290" s="6">
+      <c r="E290" s="4">
         <v>243714</v>
       </c>
       <c r="F290" s="5" t="s">
@@ -18642,7 +18633,7 @@
       <c r="G290" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H290" s="7">
+      <c r="H290" s="6">
         <v>0.733</v>
       </c>
       <c r="I290" s="5" t="s">
@@ -18674,7 +18665,7 @@
       <c r="D291" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="E291" s="6">
+      <c r="E291" s="4">
         <v>86202</v>
       </c>
       <c r="F291" s="5" t="s">
@@ -18683,7 +18674,7 @@
       <c r="G291" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H291" s="7">
+      <c r="H291" s="6">
         <v>0.824</v>
       </c>
       <c r="I291" s="5" t="s">
@@ -18715,7 +18706,7 @@
       <c r="D292" s="5" t="s">
         <v>938</v>
       </c>
-      <c r="E292" s="6">
+      <c r="E292" s="4">
         <v>65278</v>
       </c>
       <c r="F292" s="5" t="s">
@@ -18756,7 +18747,7 @@
       <c r="D293" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="E293" s="6">
+      <c r="E293" s="4">
         <v>157849</v>
       </c>
       <c r="F293" s="5" t="s">
@@ -18765,7 +18756,7 @@
       <c r="G293" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H293" s="7">
+      <c r="H293" s="6">
         <v>0.833</v>
       </c>
       <c r="I293" s="5" t="s">
@@ -18797,7 +18788,7 @@
       <c r="D294" s="5" t="s">
         <v>944</v>
       </c>
-      <c r="E294" s="6">
+      <c r="E294" s="4">
         <v>106987</v>
       </c>
       <c r="F294" s="5" t="s">
@@ -18838,7 +18829,7 @@
       <c r="D295" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="E295" s="6">
+      <c r="E295" s="4">
         <v>224088</v>
       </c>
       <c r="F295" s="5" t="s">
@@ -18847,7 +18838,7 @@
       <c r="G295" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H295" s="7">
+      <c r="H295" s="6">
         <v>0.8</v>
       </c>
       <c r="I295" s="5" t="s">
@@ -18879,7 +18870,7 @@
       <c r="D296" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="E296" s="6">
+      <c r="E296" s="4">
         <v>128223</v>
       </c>
       <c r="F296" s="5" t="s">
@@ -18888,7 +18879,7 @@
       <c r="G296" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H296" s="7">
+      <c r="H296" s="6">
         <v>0.824</v>
       </c>
       <c r="I296" s="5" t="s">
@@ -18920,7 +18911,7 @@
       <c r="D297" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="E297" s="6">
+      <c r="E297" s="4">
         <v>39152</v>
       </c>
       <c r="F297" s="5" t="s">
@@ -18961,7 +18952,7 @@
       <c r="D298" s="5" t="s">
         <v>956</v>
       </c>
-      <c r="E298" s="6">
+      <c r="E298" s="4">
         <v>50362</v>
       </c>
       <c r="F298" s="5" t="s">
@@ -19002,7 +18993,7 @@
       <c r="D299" s="5" t="s">
         <v>959</v>
       </c>
-      <c r="E299" s="6">
+      <c r="E299" s="4">
         <v>265153</v>
       </c>
       <c r="F299" s="5" t="s">
@@ -19043,7 +19034,7 @@
       <c r="D300" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="E300" s="6">
+      <c r="E300" s="4">
         <v>56331</v>
       </c>
       <c r="F300" s="5" t="s">
@@ -19084,7 +19075,7 @@
       <c r="D301" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="E301" s="6">
+      <c r="E301" s="4">
         <v>31552</v>
       </c>
       <c r="F301" s="5" t="s">
@@ -19093,7 +19084,7 @@
       <c r="G301" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H301" s="7">
+      <c r="H301" s="6">
         <v>0.8</v>
       </c>
       <c r="I301" s="5" t="s">
@@ -19125,7 +19116,7 @@
       <c r="D302" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="E302" s="6">
+      <c r="E302" s="4">
         <v>24576</v>
       </c>
       <c r="F302" s="5" t="s">
@@ -19134,7 +19125,7 @@
       <c r="G302" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H302" s="7">
+      <c r="H302" s="6">
         <v>0.706</v>
       </c>
       <c r="I302" s="5" t="s">
@@ -19166,7 +19157,7 @@
       <c r="D303" s="5" t="s">
         <v>971</v>
       </c>
-      <c r="E303" s="6">
+      <c r="E303" s="4">
         <v>69015</v>
       </c>
       <c r="F303" s="5" t="s">
@@ -19207,7 +19198,7 @@
       <c r="D304" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="E304" s="6">
+      <c r="E304" s="4">
         <v>99343</v>
       </c>
       <c r="F304" s="5" t="s">
@@ -19235,7 +19226,7 @@
         <v>973</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="18.75" hidden="1">
       <c r="A305" s="4">
         <v>2018</v>
       </c>
@@ -19248,7 +19239,7 @@
       <c r="D305" s="5" t="s">
         <v>975</v>
       </c>
-      <c r="E305" s="6">
+      <c r="E305" s="4">
         <v>288253</v>
       </c>
       <c r="F305" s="5" t="s">
@@ -19289,7 +19280,7 @@
       <c r="D306" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="E306" s="6">
+      <c r="E306" s="4">
         <v>315779</v>
       </c>
       <c r="F306" s="5" t="s">
@@ -19330,7 +19321,7 @@
       <c r="D307" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="E307" s="6">
+      <c r="E307" s="4">
         <v>256178</v>
       </c>
       <c r="F307" s="5" t="s">
@@ -19339,7 +19330,7 @@
       <c r="G307" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H307" s="7">
+      <c r="H307" s="6">
         <v>0.857</v>
       </c>
       <c r="I307" s="5" t="s">
@@ -19371,7 +19362,7 @@
       <c r="D308" s="5" t="s">
         <v>983</v>
       </c>
-      <c r="E308" s="6">
+      <c r="E308" s="4">
         <v>355501</v>
       </c>
       <c r="F308" s="5" t="s">
@@ -19412,7 +19403,7 @@
       <c r="D309" s="5" t="s">
         <v>986</v>
       </c>
-      <c r="E309" s="6">
+      <c r="E309" s="4">
         <v>74842</v>
       </c>
       <c r="F309" s="5" t="s">
@@ -19453,7 +19444,7 @@
       <c r="D310" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="E310" s="6">
+      <c r="E310" s="4">
         <v>145707</v>
       </c>
       <c r="F310" s="5" t="s">
@@ -19494,7 +19485,7 @@
       <c r="D311" s="5" t="s">
         <v>990</v>
       </c>
-      <c r="E311" s="6">
+      <c r="E311" s="4">
         <v>69683</v>
       </c>
       <c r="F311" s="5" t="s">
@@ -19535,7 +19526,7 @@
       <c r="D312" s="5" t="s">
         <v>993</v>
       </c>
-      <c r="E312" s="6">
+      <c r="E312" s="4">
         <v>182618</v>
       </c>
       <c r="F312" s="5" t="s">
@@ -19544,7 +19535,7 @@
       <c r="G312" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H312" s="7">
+      <c r="H312" s="6">
         <v>0.824</v>
       </c>
       <c r="I312" s="5" t="s">
@@ -19576,7 +19567,7 @@
       <c r="D313" s="5" t="s">
         <v>996</v>
       </c>
-      <c r="E313" s="6">
+      <c r="E313" s="4">
         <v>172181</v>
       </c>
       <c r="F313" s="5" t="s">
@@ -19617,7 +19608,7 @@
       <c r="D314" s="5" t="s">
         <v>999</v>
       </c>
-      <c r="E314" s="6">
+      <c r="E314" s="4">
         <v>25523</v>
       </c>
       <c r="F314" s="5" t="s">
@@ -19658,7 +19649,7 @@
       <c r="D315" s="5" t="s">
         <v>1002</v>
       </c>
-      <c r="E315" s="6">
+      <c r="E315" s="4">
         <v>46110</v>
       </c>
       <c r="F315" s="5" t="s">
@@ -19667,7 +19658,7 @@
       <c r="G315" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H315" s="7">
+      <c r="H315" s="6">
         <v>0.824</v>
       </c>
       <c r="I315" s="5" t="s">
@@ -19699,7 +19690,7 @@
       <c r="D316" s="5" t="s">
         <v>1005</v>
       </c>
-      <c r="E316" s="6">
+      <c r="E316" s="4">
         <v>50337</v>
       </c>
       <c r="F316" s="5" t="s">
@@ -19708,7 +19699,7 @@
       <c r="G316" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H316" s="7">
+      <c r="H316" s="6">
         <v>0.824</v>
       </c>
       <c r="I316" s="5" t="s">
@@ -19740,7 +19731,7 @@
       <c r="D317" s="5" t="s">
         <v>1008</v>
       </c>
-      <c r="E317" s="6">
+      <c r="E317" s="4">
         <v>32749</v>
       </c>
       <c r="F317" s="5" t="s">
@@ -19749,7 +19740,7 @@
       <c r="G317" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H317" s="7">
+      <c r="H317" s="6">
         <v>0.706</v>
       </c>
       <c r="I317" s="5" t="s">
@@ -19781,7 +19772,7 @@
       <c r="D318" s="5" t="s">
         <v>1011</v>
       </c>
-      <c r="E318" s="6">
+      <c r="E318" s="4">
         <v>131327</v>
       </c>
       <c r="F318" s="5" t="s">
@@ -19790,7 +19781,7 @@
       <c r="G318" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H318" s="7">
+      <c r="H318" s="6">
         <v>0.8</v>
       </c>
       <c r="I318" s="5" t="s">
@@ -19822,7 +19813,7 @@
       <c r="D319" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="E319" s="6">
+      <c r="E319" s="4">
         <v>122946</v>
       </c>
       <c r="F319" s="5" t="s">
@@ -19831,7 +19822,7 @@
       <c r="G319" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H319" s="7">
+      <c r="H319" s="6">
         <v>0.824</v>
       </c>
       <c r="I319" s="5" t="s">
@@ -19863,7 +19854,7 @@
       <c r="D320" s="5" t="s">
         <v>1017</v>
       </c>
-      <c r="E320" s="6">
+      <c r="E320" s="4">
         <v>228444</v>
       </c>
       <c r="F320" s="5" t="s">
@@ -19904,7 +19895,7 @@
       <c r="D321" s="5" t="s">
         <v>1020</v>
       </c>
-      <c r="E321" s="6">
+      <c r="E321" s="4">
         <v>121404</v>
       </c>
       <c r="F321" s="5" t="s">
@@ -19913,7 +19904,7 @@
       <c r="G321" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H321" s="7">
+      <c r="H321" s="6">
         <v>0.714</v>
       </c>
       <c r="I321" s="5" t="s">
@@ -19945,7 +19936,7 @@
       <c r="D322" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="E322" s="6">
+      <c r="E322" s="4">
         <v>27394</v>
       </c>
       <c r="F322" s="5" t="s">
@@ -19954,7 +19945,7 @@
       <c r="G322" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H322" s="7">
+      <c r="H322" s="6">
         <v>0.824</v>
       </c>
       <c r="I322" s="5" t="s">
@@ -19986,7 +19977,7 @@
       <c r="D323" s="5" t="s">
         <v>1026</v>
       </c>
-      <c r="E323" s="6">
+      <c r="E323" s="4">
         <v>54928</v>
       </c>
       <c r="F323" s="5" t="s">
@@ -20027,7 +20018,7 @@
       <c r="D324" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="E324" s="6">
+      <c r="E324" s="4">
         <v>116747</v>
       </c>
       <c r="F324" s="5" t="s">
@@ -20036,7 +20027,7 @@
       <c r="G324" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H324" s="7">
+      <c r="H324" s="6">
         <v>0.8</v>
       </c>
       <c r="I324" s="5" t="s">
@@ -20068,7 +20059,7 @@
       <c r="D325" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="E325" s="6">
+      <c r="E325" s="4">
         <v>13230</v>
       </c>
       <c r="F325" s="5" t="s">
@@ -20077,7 +20068,7 @@
       <c r="G325" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H325" s="7">
+      <c r="H325" s="6">
         <v>0.824</v>
       </c>
       <c r="I325" s="5" t="s">
@@ -20109,7 +20100,7 @@
       <c r="D326" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="E326" s="6">
+      <c r="E326" s="4">
         <v>94529</v>
       </c>
       <c r="F326" s="5" t="s">
@@ -20150,7 +20141,7 @@
       <c r="D327" s="5" t="s">
         <v>1038</v>
       </c>
-      <c r="E327" s="6">
+      <c r="E327" s="4">
         <v>33969</v>
       </c>
       <c r="F327" s="5" t="s">
@@ -20189,7 +20180,7 @@
       <c r="D328" s="5" t="s">
         <v>1041</v>
       </c>
-      <c r="E328" s="6">
+      <c r="E328" s="4">
         <v>38782</v>
       </c>
       <c r="F328" s="5" t="s">
@@ -20230,7 +20221,7 @@
       <c r="D329" s="5" t="s">
         <v>1044</v>
       </c>
-      <c r="E329" s="6">
+      <c r="E329" s="4">
         <v>160222</v>
       </c>
       <c r="F329" s="5" t="s">
@@ -20239,7 +20230,7 @@
       <c r="G329" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H329" s="7">
+      <c r="H329" s="6">
         <v>0.833</v>
       </c>
       <c r="I329" s="5" t="s">
@@ -20271,7 +20262,7 @@
       <c r="D330" s="5" t="s">
         <v>1047</v>
       </c>
-      <c r="E330" s="6">
+      <c r="E330" s="4">
         <v>171411</v>
       </c>
       <c r="F330" s="5" t="s">
@@ -20280,7 +20271,7 @@
       <c r="G330" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H330" s="7">
+      <c r="H330" s="6">
         <v>0.706</v>
       </c>
       <c r="I330" s="5" t="s">
@@ -20312,7 +20303,7 @@
       <c r="D331" s="5" t="s">
         <v>1050</v>
       </c>
-      <c r="E331" s="6">
+      <c r="E331" s="4">
         <v>205938</v>
       </c>
       <c r="F331" s="5" t="s">
@@ -20353,7 +20344,7 @@
       <c r="D332" s="5" t="s">
         <v>1053</v>
       </c>
-      <c r="E332" s="6">
+      <c r="E332" s="4">
         <v>181136</v>
       </c>
       <c r="F332" s="5" t="s">
@@ -20394,7 +20385,7 @@
       <c r="D333" s="5" t="s">
         <v>1056</v>
       </c>
-      <c r="E333" s="6">
+      <c r="E333" s="4">
         <v>173859</v>
       </c>
       <c r="F333" s="5" t="s">
@@ -20403,7 +20394,7 @@
       <c r="G333" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H333" s="7">
+      <c r="H333" s="6">
         <v>0.824</v>
       </c>
       <c r="I333" s="5" t="s">
@@ -20422,7 +20413,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="18.75" hidden="1">
+    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="18.75">
       <c r="A334" s="4">
         <v>2018</v>
       </c>
@@ -20435,11 +20426,11 @@
       <c r="D334" s="5" t="s">
         <v>1059</v>
       </c>
-      <c r="E334" s="6">
+      <c r="E334" s="4">
         <v>112465</v>
       </c>
       <c r="F334" s="5" t="s">
-        <v>588</v>
+        <v>16</v>
       </c>
       <c r="G334" s="5" t="s">
         <v>17</v>
@@ -20476,7 +20467,7 @@
       <c r="D335" s="5" t="s">
         <v>1062</v>
       </c>
-      <c r="E335" s="6">
+      <c r="E335" s="4">
         <v>99922</v>
       </c>
       <c r="F335" s="5" t="s">
@@ -20517,7 +20508,7 @@
       <c r="D336" s="5" t="s">
         <v>1065</v>
       </c>
-      <c r="E336" s="6">
+      <c r="E336" s="4">
         <v>80444</v>
       </c>
       <c r="F336" s="5" t="s">
@@ -20558,7 +20549,7 @@
       <c r="D337" s="5" t="s">
         <v>1068</v>
       </c>
-      <c r="E337" s="6">
+      <c r="E337" s="4">
         <v>244275</v>
       </c>
       <c r="F337" s="5" t="s">
@@ -20599,7 +20590,7 @@
       <c r="D338" s="5" t="s">
         <v>1071</v>
       </c>
-      <c r="E338" s="6">
+      <c r="E338" s="4">
         <v>57051</v>
       </c>
       <c r="F338" s="5" t="s">
@@ -20608,7 +20599,7 @@
       <c r="G338" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H338" s="7">
+      <c r="H338" s="6">
         <v>0.733</v>
       </c>
       <c r="I338" s="5" t="s">
@@ -20640,7 +20631,7 @@
       <c r="D339" s="5" t="s">
         <v>1074</v>
       </c>
-      <c r="E339" s="6">
+      <c r="E339" s="4">
         <v>258923</v>
       </c>
       <c r="F339" s="5" t="s">
@@ -20681,7 +20672,7 @@
       <c r="D340" s="5" t="s">
         <v>1077</v>
       </c>
-      <c r="E340" s="6">
+      <c r="E340" s="4">
         <v>182877</v>
       </c>
       <c r="F340" s="5" t="s">
@@ -20722,7 +20713,7 @@
       <c r="D341" s="5" t="s">
         <v>1080</v>
       </c>
-      <c r="E341" s="6">
+      <c r="E341" s="4">
         <v>46001</v>
       </c>
       <c r="F341" s="5" t="s">
@@ -20731,7 +20722,7 @@
       <c r="G341" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H341" s="7">
+      <c r="H341" s="6">
         <v>0.692</v>
       </c>
       <c r="I341" s="5" t="s">
@@ -20763,7 +20754,7 @@
       <c r="D342" s="5" t="s">
         <v>1083</v>
       </c>
-      <c r="E342" s="6">
+      <c r="E342" s="4">
         <v>42735</v>
       </c>
       <c r="F342" s="5" t="s">
@@ -20772,7 +20763,7 @@
       <c r="G342" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H342" s="7">
+      <c r="H342" s="6">
         <v>0.833</v>
       </c>
       <c r="I342" s="5" t="s">
@@ -20804,7 +20795,7 @@
       <c r="D343" s="5" t="s">
         <v>1086</v>
       </c>
-      <c r="E343" s="6">
+      <c r="E343" s="4">
         <v>43512</v>
       </c>
       <c r="F343" s="5" t="s">
@@ -20845,7 +20836,7 @@
       <c r="D344" s="5" t="s">
         <v>1089</v>
       </c>
-      <c r="E344" s="6">
+      <c r="E344" s="4">
         <v>14086</v>
       </c>
       <c r="F344" s="5" t="s">
@@ -20886,7 +20877,7 @@
       <c r="D345" s="5" t="s">
         <v>1092</v>
       </c>
-      <c r="E345" s="6">
+      <c r="E345" s="4">
         <v>59866</v>
       </c>
       <c r="F345" s="5" t="s">
@@ -20895,7 +20886,7 @@
       <c r="G345" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H345" s="7">
+      <c r="H345" s="6">
         <v>0.824</v>
       </c>
       <c r="I345" s="5" t="s">
@@ -20927,7 +20918,7 @@
       <c r="D346" s="5" t="s">
         <v>1095</v>
       </c>
-      <c r="E346" s="6">
+      <c r="E346" s="4">
         <v>55336</v>
       </c>
       <c r="F346" s="5" t="s">
@@ -20968,7 +20959,7 @@
       <c r="D347" s="5" t="s">
         <v>1098</v>
       </c>
-      <c r="E347" s="6">
+      <c r="E347" s="4">
         <v>74229</v>
       </c>
       <c r="F347" s="5" t="s">
@@ -21009,7 +21000,7 @@
       <c r="D348" s="5" t="s">
         <v>1101</v>
       </c>
-      <c r="E348" s="6">
+      <c r="E348" s="4">
         <v>264956</v>
       </c>
       <c r="F348" s="5" t="s">
@@ -21050,7 +21041,7 @@
       <c r="D349" s="5" t="s">
         <v>1104</v>
       </c>
-      <c r="E349" s="6">
+      <c r="E349" s="4">
         <v>170527</v>
       </c>
       <c r="F349" s="5" t="s">
@@ -21091,7 +21082,7 @@
       <c r="D350" s="5" t="s">
         <v>1107</v>
       </c>
-      <c r="E350" s="6">
+      <c r="E350" s="4">
         <v>277137</v>
       </c>
       <c r="F350" s="5" t="s">
@@ -21132,7 +21123,7 @@
       <c r="D351" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E351" s="6">
+      <c r="E351" s="4">
         <v>19368</v>
       </c>
       <c r="F351" s="5" t="s">
@@ -21141,7 +21132,7 @@
       <c r="G351" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H351" s="7">
+      <c r="H351" s="6">
         <v>0.692</v>
       </c>
       <c r="I351" s="5" t="s">
@@ -21173,7 +21164,7 @@
       <c r="D352" s="5" t="s">
         <v>1112</v>
       </c>
-      <c r="E352" s="6">
+      <c r="E352" s="4">
         <v>33544</v>
       </c>
       <c r="F352" s="5" t="s">
@@ -21212,7 +21203,7 @@
       <c r="D353" s="5" t="s">
         <v>1115</v>
       </c>
-      <c r="E353" s="6">
+      <c r="E353" s="4">
         <v>46741</v>
       </c>
       <c r="F353" s="5" t="s">
@@ -21221,7 +21212,7 @@
       <c r="G353" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H353" s="7">
+      <c r="H353" s="6">
         <v>0.824</v>
       </c>
       <c r="I353" s="5" t="s">
@@ -21253,7 +21244,7 @@
       <c r="D354" s="5" t="s">
         <v>1118</v>
       </c>
-      <c r="E354" s="6">
+      <c r="E354" s="4">
         <v>9593</v>
       </c>
       <c r="F354" s="5" t="s">
@@ -21262,7 +21253,7 @@
       <c r="G354" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H354" s="7">
+      <c r="H354" s="6">
         <v>0.833</v>
       </c>
       <c r="I354" s="5" t="s">
@@ -21294,7 +21285,7 @@
       <c r="D355" s="5" t="s">
         <v>1121</v>
       </c>
-      <c r="E355" s="6">
+      <c r="E355" s="4">
         <v>196792</v>
       </c>
       <c r="F355" s="5" t="s">
@@ -21335,7 +21326,7 @@
       <c r="D356" s="5" t="s">
         <v>1124</v>
       </c>
-      <c r="E356" s="6">
+      <c r="E356" s="4">
         <v>134999</v>
       </c>
       <c r="F356" s="5" t="s">
@@ -21376,7 +21367,7 @@
       <c r="D357" s="5" t="s">
         <v>1127</v>
       </c>
-      <c r="E357" s="6">
+      <c r="E357" s="4">
         <v>255957</v>
       </c>
       <c r="F357" s="5" t="s">
@@ -21385,7 +21376,7 @@
       <c r="G357" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H357" s="7">
+      <c r="H357" s="6">
         <v>0.706</v>
       </c>
       <c r="I357" s="5" t="s">
@@ -21417,7 +21408,7 @@
       <c r="D358" s="5" t="s">
         <v>1130</v>
       </c>
-      <c r="E358" s="6">
+      <c r="E358" s="4">
         <v>193082</v>
       </c>
       <c r="F358" s="5" t="s">
@@ -21426,7 +21417,7 @@
       <c r="G358" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H358" s="7">
+      <c r="H358" s="6">
         <v>0.824</v>
       </c>
       <c r="I358" s="5" t="s">
@@ -21458,7 +21449,7 @@
       <c r="D359" s="5" t="s">
         <v>1133</v>
       </c>
-      <c r="E359" s="6">
+      <c r="E359" s="4">
         <v>143424</v>
       </c>
       <c r="F359" s="5" t="s">
@@ -21467,7 +21458,7 @@
       <c r="G359" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H359" s="7">
+      <c r="H359" s="6">
         <v>0.857</v>
       </c>
       <c r="I359" s="5" t="s">
@@ -21499,7 +21490,7 @@
       <c r="D360" s="5" t="s">
         <v>1136</v>
       </c>
-      <c r="E360" s="6">
+      <c r="E360" s="4">
         <v>125165</v>
       </c>
       <c r="F360" s="5" t="s">
@@ -21540,7 +21531,7 @@
       <c r="D361" s="5" t="s">
         <v>1139</v>
       </c>
-      <c r="E361" s="6">
+      <c r="E361" s="4">
         <v>82070</v>
       </c>
       <c r="F361" s="5" t="s">
@@ -21581,7 +21572,7 @@
       <c r="D362" s="5" t="s">
         <v>1142</v>
       </c>
-      <c r="E362" s="6">
+      <c r="E362" s="4">
         <v>85148</v>
       </c>
       <c r="F362" s="5" t="s">
@@ -21622,7 +21613,7 @@
       <c r="D363" s="5" t="s">
         <v>1145</v>
       </c>
-      <c r="E363" s="6">
+      <c r="E363" s="4">
         <v>70934</v>
       </c>
       <c r="F363" s="5" t="s">
@@ -21631,7 +21622,7 @@
       <c r="G363" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H363" s="7">
+      <c r="H363" s="6">
         <v>0.824</v>
       </c>
       <c r="I363" s="5" t="s">
@@ -21663,7 +21654,7 @@
       <c r="D364" s="5" t="s">
         <v>1148</v>
       </c>
-      <c r="E364" s="6">
+      <c r="E364" s="4">
         <v>9644</v>
       </c>
       <c r="F364" s="5" t="s">
@@ -21704,7 +21695,7 @@
       <c r="D365" s="5" t="s">
         <v>1151</v>
       </c>
-      <c r="E365" s="6">
+      <c r="E365" s="4">
         <v>53536</v>
       </c>
       <c r="F365" s="5" t="s">
@@ -21713,7 +21704,7 @@
       <c r="G365" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H365" s="7">
+      <c r="H365" s="6">
         <v>0.842</v>
       </c>
       <c r="I365" s="5" t="s">
@@ -21745,7 +21736,7 @@
       <c r="D366" s="5" t="s">
         <v>1154</v>
       </c>
-      <c r="E366" s="6">
+      <c r="E366" s="4">
         <v>426620</v>
       </c>
       <c r="F366" s="5" t="s">
@@ -21786,7 +21777,7 @@
       <c r="D367" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="E367" s="6">
+      <c r="E367" s="4">
         <v>249565</v>
       </c>
       <c r="F367" s="5" t="s">
@@ -21795,7 +21786,7 @@
       <c r="G367" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H367" s="7">
+      <c r="H367" s="6">
         <v>0.8</v>
       </c>
       <c r="I367" s="5" t="s">
@@ -21827,7 +21818,7 @@
       <c r="D368" s="5" t="s">
         <v>1160</v>
       </c>
-      <c r="E368" s="6">
+      <c r="E368" s="4">
         <v>60542</v>
       </c>
       <c r="F368" s="5" t="s">
@@ -21868,7 +21859,7 @@
       <c r="D369" s="5" t="s">
         <v>1163</v>
       </c>
-      <c r="E369" s="6">
+      <c r="E369" s="4">
         <v>84992</v>
       </c>
       <c r="F369" s="5" t="s">
@@ -21877,7 +21868,7 @@
       <c r="G369" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H369" s="7">
+      <c r="H369" s="6">
         <v>0.8</v>
       </c>
       <c r="I369" s="5" t="s">
@@ -21909,7 +21900,7 @@
       <c r="D370" s="5" t="s">
         <v>866</v>
       </c>
-      <c r="E370" s="6">
+      <c r="E370" s="4">
         <v>35518</v>
       </c>
       <c r="F370" s="5" t="s">
@@ -21918,7 +21909,7 @@
       <c r="G370" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H370" s="7">
+      <c r="H370" s="6">
         <v>0.824</v>
       </c>
       <c r="I370" s="5" t="s">
@@ -21950,7 +21941,7 @@
       <c r="D371" s="5" t="s">
         <v>1168</v>
       </c>
-      <c r="E371" s="6">
+      <c r="E371" s="4">
         <v>418560</v>
       </c>
       <c r="F371" s="5" t="s">
@@ -21991,7 +21982,7 @@
       <c r="D372" s="5" t="s">
         <v>1171</v>
       </c>
-      <c r="E372" s="6">
+      <c r="E372" s="4">
         <v>7602</v>
       </c>
       <c r="F372" s="5" t="s">
@@ -22032,7 +22023,7 @@
       <c r="D373" s="5" t="s">
         <v>1174</v>
       </c>
-      <c r="E373" s="6">
+      <c r="E373" s="4">
         <v>174694</v>
       </c>
       <c r="F373" s="5" t="s">
@@ -22041,7 +22032,7 @@
       <c r="G373" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H373" s="7">
+      <c r="H373" s="6">
         <v>0.8</v>
       </c>
       <c r="I373" s="5" t="s">
@@ -22073,7 +22064,7 @@
       <c r="D374" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="E374" s="6">
+      <c r="E374" s="4">
         <v>76924</v>
       </c>
       <c r="F374" s="5" t="s">
@@ -22114,7 +22105,7 @@
       <c r="D375" s="5" t="s">
         <v>1179</v>
       </c>
-      <c r="E375" s="6">
+      <c r="E375" s="4">
         <v>126656</v>
       </c>
       <c r="F375" s="5" t="s">
@@ -22155,7 +22146,7 @@
       <c r="D376" s="5" t="s">
         <v>1182</v>
       </c>
-      <c r="E376" s="6">
+      <c r="E376" s="4">
         <v>26669</v>
       </c>
       <c r="F376" s="5" t="s">
@@ -22164,7 +22155,7 @@
       <c r="G376" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H376" s="7">
+      <c r="H376" s="6">
         <v>0.857</v>
       </c>
       <c r="I376" s="5" t="s">
@@ -22196,7 +22187,7 @@
       <c r="D377" s="5" t="s">
         <v>1185</v>
       </c>
-      <c r="E377" s="6">
+      <c r="E377" s="4">
         <v>286297</v>
       </c>
       <c r="F377" s="5" t="s">
@@ -22237,7 +22228,7 @@
       <c r="D378" s="5" t="s">
         <v>1188</v>
       </c>
-      <c r="E378" s="6">
+      <c r="E378" s="4">
         <v>39381</v>
       </c>
       <c r="F378" s="5" t="s">
@@ -22278,7 +22269,7 @@
       <c r="D379" s="5" t="s">
         <v>1191</v>
       </c>
-      <c r="E379" s="6">
+      <c r="E379" s="4">
         <v>213672</v>
       </c>
       <c r="F379" s="5" t="s">
@@ -22287,7 +22278,7 @@
       <c r="G379" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H379" s="7">
+      <c r="H379" s="6">
         <v>0.8</v>
       </c>
       <c r="I379" s="5" t="s">
@@ -22319,7 +22310,7 @@
       <c r="D380" s="5" t="s">
         <v>1194</v>
       </c>
-      <c r="E380" s="6">
+      <c r="E380" s="4">
         <v>101328</v>
       </c>
       <c r="F380" s="5" t="s">
@@ -22328,7 +22319,7 @@
       <c r="G380" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H380" s="7">
+      <c r="H380" s="6">
         <v>0.8</v>
       </c>
       <c r="I380" s="5" t="s">
@@ -22360,7 +22351,7 @@
       <c r="D381" s="5" t="s">
         <v>1197</v>
       </c>
-      <c r="E381" s="6">
+      <c r="E381" s="4">
         <v>42710</v>
       </c>
       <c r="F381" s="5" t="s">
@@ -22369,7 +22360,7 @@
       <c r="G381" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H381" s="7">
+      <c r="H381" s="6">
         <v>0.692</v>
       </c>
       <c r="I381" s="5" t="s">
@@ -22401,7 +22392,7 @@
       <c r="D382" s="5" t="s">
         <v>1200</v>
       </c>
-      <c r="E382" s="6">
+      <c r="E382" s="4">
         <v>206843</v>
       </c>
       <c r="F382" s="5" t="s">
@@ -22440,7 +22431,7 @@
       <c r="D383" s="5" t="s">
         <v>1203</v>
       </c>
-      <c r="E383" s="6">
+      <c r="E383" s="4">
         <v>354362</v>
       </c>
       <c r="F383" s="5" t="s">
@@ -22449,7 +22440,7 @@
       <c r="G383" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H383" s="7">
+      <c r="H383" s="6">
         <v>0.842</v>
       </c>
       <c r="I383" s="5" t="s">
@@ -22481,7 +22472,7 @@
       <c r="D384" s="5" t="s">
         <v>1206</v>
       </c>
-      <c r="E384" s="6">
+      <c r="E384" s="4">
         <v>33793</v>
       </c>
       <c r="F384" s="5" t="s">
@@ -22490,7 +22481,7 @@
       <c r="G384" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H384" s="7">
+      <c r="H384" s="6">
         <v>0.842</v>
       </c>
       <c r="I384" s="5" t="s">
@@ -22522,7 +22513,7 @@
       <c r="D385" s="5" t="s">
         <v>1209</v>
       </c>
-      <c r="E385" s="6">
+      <c r="E385" s="4">
         <v>332798</v>
       </c>
       <c r="F385" s="5" t="s">
@@ -22531,7 +22522,7 @@
       <c r="G385" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H385" s="7">
+      <c r="H385" s="6">
         <v>0.556</v>
       </c>
       <c r="I385" s="5" t="s">
@@ -22563,7 +22554,7 @@
       <c r="D386" s="5" t="s">
         <v>1212</v>
       </c>
-      <c r="E386" s="6">
+      <c r="E386" s="4">
         <v>238752</v>
       </c>
       <c r="F386" s="5" t="s">
@@ -22572,7 +22563,7 @@
       <c r="G386" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H386" s="7">
+      <c r="H386" s="6">
         <v>0.8</v>
       </c>
       <c r="I386" s="5" t="s">
@@ -22604,7 +22595,7 @@
       <c r="D387" s="5" t="s">
         <v>1215</v>
       </c>
-      <c r="E387" s="6">
+      <c r="E387" s="4">
         <v>145538</v>
       </c>
       <c r="F387" s="5" t="s">
@@ -22613,7 +22604,7 @@
       <c r="G387" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H387" s="7">
+      <c r="H387" s="6">
         <v>0.824</v>
       </c>
       <c r="I387" s="5" t="s">
@@ -22645,7 +22636,7 @@
       <c r="D388" s="5" t="s">
         <v>1218</v>
       </c>
-      <c r="E388" s="6">
+      <c r="E388" s="4">
         <v>37713</v>
       </c>
       <c r="F388" s="5" t="s">
@@ -22654,7 +22645,7 @@
       <c r="G388" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H388" s="7">
+      <c r="H388" s="6">
         <v>0.19</v>
       </c>
       <c r="I388" s="5" t="s">
@@ -22686,7 +22677,7 @@
       <c r="D389" s="5" t="s">
         <v>1221</v>
       </c>
-      <c r="E389" s="6">
+      <c r="E389" s="4">
         <v>22202</v>
       </c>
       <c r="F389" s="5" t="s">
@@ -22727,7 +22718,7 @@
       <c r="D390" s="5" t="s">
         <v>1224</v>
       </c>
-      <c r="E390" s="6">
+      <c r="E390" s="4">
         <v>55735</v>
       </c>
       <c r="F390" s="5" t="s">
@@ -22768,7 +22759,7 @@
       <c r="D391" s="5" t="s">
         <v>1227</v>
       </c>
-      <c r="E391" s="6">
+      <c r="E391" s="4">
         <v>213368</v>
       </c>
       <c r="F391" s="5" t="s">
@@ -22809,7 +22800,7 @@
       <c r="D392" s="5" t="s">
         <v>1230</v>
       </c>
-      <c r="E392" s="6">
+      <c r="E392" s="4">
         <v>122153</v>
       </c>
       <c r="F392" s="5" t="s">
@@ -22850,7 +22841,7 @@
       <c r="D393" s="5" t="s">
         <v>1233</v>
       </c>
-      <c r="E393" s="6">
+      <c r="E393" s="4">
         <v>250845</v>
       </c>
       <c r="F393" s="5" t="s">
@@ -22891,7 +22882,7 @@
       <c r="D394" s="5" t="s">
         <v>1236</v>
       </c>
-      <c r="E394" s="6">
+      <c r="E394" s="4">
         <v>35208</v>
       </c>
       <c r="F394" s="5" t="s">
@@ -22932,7 +22923,7 @@
       <c r="D395" s="5" t="s">
         <v>1239</v>
       </c>
-      <c r="E395" s="6">
+      <c r="E395" s="4">
         <v>129674</v>
       </c>
       <c r="F395" s="5" t="s">
@@ -22973,7 +22964,7 @@
       <c r="D396" s="5" t="s">
         <v>1242</v>
       </c>
-      <c r="E396" s="6">
+      <c r="E396" s="4">
         <v>126664</v>
       </c>
       <c r="F396" s="5" t="s">
@@ -22982,7 +22973,7 @@
       <c r="G396" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H396" s="7">
+      <c r="H396" s="6">
         <v>0.857</v>
       </c>
       <c r="I396" s="5" t="s">
@@ -23014,7 +23005,7 @@
       <c r="D397" s="5" t="s">
         <v>1245</v>
       </c>
-      <c r="E397" s="6">
+      <c r="E397" s="4">
         <v>292772</v>
       </c>
       <c r="F397" s="5" t="s">
@@ -23023,7 +23014,7 @@
       <c r="G397" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H397" s="7">
+      <c r="H397" s="6">
         <v>0.714</v>
       </c>
       <c r="I397" s="5" t="s">
@@ -23055,7 +23046,7 @@
       <c r="D398" s="5" t="s">
         <v>1248</v>
       </c>
-      <c r="E398" s="6">
+      <c r="E398" s="4">
         <v>95810</v>
       </c>
       <c r="F398" s="5" t="s">
@@ -23064,7 +23055,7 @@
       <c r="G398" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H398" s="7">
+      <c r="H398" s="6">
         <v>0.692</v>
       </c>
       <c r="I398" s="5" t="s">
@@ -23096,7 +23087,7 @@
       <c r="D399" s="5" t="s">
         <v>1251</v>
       </c>
-      <c r="E399" s="6">
+      <c r="E399" s="4">
         <v>176553</v>
       </c>
       <c r="F399" s="5" t="s">
@@ -23137,7 +23128,7 @@
       <c r="D400" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="E400" s="6">
+      <c r="E400" s="4">
         <v>447661</v>
       </c>
       <c r="F400" s="5" t="s">
@@ -23146,7 +23137,7 @@
       <c r="G400" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H400" s="7">
+      <c r="H400" s="6">
         <v>0.824</v>
       </c>
       <c r="I400" s="5" t="s">
@@ -23178,7 +23169,7 @@
       <c r="D401" s="5" t="s">
         <v>1257</v>
       </c>
-      <c r="E401" s="6">
+      <c r="E401" s="4">
         <v>15363</v>
       </c>
       <c r="F401" s="5" t="s">
@@ -23217,7 +23208,7 @@
       <c r="D402" s="5" t="s">
         <v>1260</v>
       </c>
-      <c r="E402" s="6">
+      <c r="E402" s="4">
         <v>16635</v>
       </c>
       <c r="F402" s="5" t="s">
@@ -23258,7 +23249,7 @@
       <c r="D403" s="5" t="s">
         <v>1263</v>
       </c>
-      <c r="E403" s="6">
+      <c r="E403" s="4">
         <v>42678</v>
       </c>
       <c r="F403" s="5" t="s">
@@ -23299,7 +23290,7 @@
       <c r="D404" s="5" t="s">
         <v>1266</v>
       </c>
-      <c r="E404" s="6">
+      <c r="E404" s="4">
         <v>216181</v>
       </c>
       <c r="F404" s="5" t="s">
@@ -23308,7 +23299,7 @@
       <c r="G404" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H404" s="7">
+      <c r="H404" s="6">
         <v>0.8</v>
       </c>
       <c r="I404" s="5" t="s">
@@ -23340,7 +23331,7 @@
       <c r="D405" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="E405" s="6">
+      <c r="E405" s="4">
         <v>129096</v>
       </c>
       <c r="F405" s="5" t="s">
@@ -23381,7 +23372,7 @@
       <c r="D406" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E406" s="6">
+      <c r="E406" s="4">
         <v>281963</v>
       </c>
       <c r="F406" s="5" t="s">
@@ -23420,7 +23411,7 @@
       <c r="D407" s="5" t="s">
         <v>1274</v>
       </c>
-      <c r="E407" s="6">
+      <c r="E407" s="4">
         <v>53077</v>
       </c>
       <c r="F407" s="5" t="s">
@@ -23429,7 +23420,7 @@
       <c r="G407" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H407" s="7">
+      <c r="H407" s="6">
         <v>0.714</v>
       </c>
       <c r="I407" s="5" t="s">
@@ -23461,7 +23452,7 @@
       <c r="D408" s="5" t="s">
         <v>1277</v>
       </c>
-      <c r="E408" s="6">
+      <c r="E408" s="4">
         <v>198648</v>
       </c>
       <c r="F408" s="5" t="s">
@@ -23500,7 +23491,7 @@
       <c r="D409" s="5" t="s">
         <v>1280</v>
       </c>
-      <c r="E409" s="6">
+      <c r="E409" s="4">
         <v>286384</v>
       </c>
       <c r="F409" s="5" t="s">
@@ -23541,7 +23532,7 @@
       <c r="D410" s="5" t="s">
         <v>1283</v>
       </c>
-      <c r="E410" s="6">
+      <c r="E410" s="4">
         <v>1667</v>
       </c>
       <c r="F410" s="5" t="s">
@@ -23550,7 +23541,7 @@
       <c r="G410" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H410" s="7">
+      <c r="H410" s="6">
         <v>0.8</v>
       </c>
       <c r="I410" s="5" t="s">
@@ -23582,7 +23573,7 @@
       <c r="D411" s="5" t="s">
         <v>1286</v>
       </c>
-      <c r="E411" s="6">
+      <c r="E411" s="4">
         <v>338670</v>
       </c>
       <c r="F411" s="5" t="s">
@@ -23591,7 +23582,7 @@
       <c r="G411" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H411" s="7">
+      <c r="H411" s="6">
         <v>0.824</v>
       </c>
       <c r="I411" s="5" t="s">
@@ -23623,7 +23614,7 @@
       <c r="D412" s="5" t="s">
         <v>1289</v>
       </c>
-      <c r="E412" s="6">
+      <c r="E412" s="4">
         <v>71206</v>
       </c>
       <c r="F412" s="5" t="s">
@@ -23632,7 +23623,7 @@
       <c r="G412" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H412" s="7">
+      <c r="H412" s="6">
         <v>0.556</v>
       </c>
       <c r="I412" s="5" t="s">
@@ -23664,7 +23655,7 @@
       <c r="D413" s="5" t="s">
         <v>1292</v>
       </c>
-      <c r="E413" s="6">
+      <c r="E413" s="4">
         <v>127202</v>
       </c>
       <c r="F413" s="5" t="s">
@@ -23673,7 +23664,7 @@
       <c r="G413" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H413" s="7">
+      <c r="H413" s="6">
         <v>0.833</v>
       </c>
       <c r="I413" s="5" t="s">
@@ -23705,7 +23696,7 @@
       <c r="D414" s="5" t="s">
         <v>1295</v>
       </c>
-      <c r="E414" s="6">
+      <c r="E414" s="4">
         <v>13271</v>
       </c>
       <c r="F414" s="5" t="s">
@@ -23714,7 +23705,7 @@
       <c r="G414" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H414" s="7">
+      <c r="H414" s="6">
         <v>0.833</v>
       </c>
       <c r="I414" s="5" t="s">
@@ -23746,7 +23737,7 @@
       <c r="D415" s="5" t="s">
         <v>1298</v>
       </c>
-      <c r="E415" s="6">
+      <c r="E415" s="4">
         <v>3979</v>
       </c>
       <c r="F415" s="5" t="s">
@@ -23787,7 +23778,7 @@
       <c r="D416" s="5" t="s">
         <v>1301</v>
       </c>
-      <c r="E416" s="6">
+      <c r="E416" s="4">
         <v>27941</v>
       </c>
       <c r="F416" s="5" t="s">
@@ -23796,7 +23787,7 @@
       <c r="G416" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H416" s="7">
+      <c r="H416" s="6">
         <v>0.8</v>
       </c>
       <c r="I416" s="5" t="s">
@@ -23828,7 +23819,7 @@
       <c r="D417" s="5" t="s">
         <v>1304</v>
       </c>
-      <c r="E417" s="6">
+      <c r="E417" s="4">
         <v>140776</v>
       </c>
       <c r="F417" s="5" t="s">
@@ -23869,7 +23860,7 @@
       <c r="D418" s="5" t="s">
         <v>1307</v>
       </c>
-      <c r="E418" s="6">
+      <c r="E418" s="4">
         <v>256718</v>
       </c>
       <c r="F418" s="5" t="s">
@@ -23910,7 +23901,7 @@
       <c r="D419" s="5" t="s">
         <v>1310</v>
       </c>
-      <c r="E419" s="6">
+      <c r="E419" s="4">
         <v>107010</v>
       </c>
       <c r="F419" s="5" t="s">
@@ -23951,7 +23942,7 @@
       <c r="D420" s="5" t="s">
         <v>1313</v>
       </c>
-      <c r="E420" s="6">
+      <c r="E420" s="4">
         <v>33648</v>
       </c>
       <c r="F420" s="5" t="s">
@@ -23992,7 +23983,7 @@
       <c r="D421" s="5" t="s">
         <v>1316</v>
       </c>
-      <c r="E421" s="6">
+      <c r="E421" s="4">
         <v>42714</v>
       </c>
       <c r="F421" s="5" t="s">
@@ -24001,7 +23992,7 @@
       <c r="G421" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H421" s="7">
+      <c r="H421" s="6">
         <v>0.714</v>
       </c>
       <c r="I421" s="5" t="s">
@@ -24033,7 +24024,7 @@
       <c r="D422" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E422" s="6">
+      <c r="E422" s="4">
         <v>229004</v>
       </c>
       <c r="F422" s="5" t="s">
@@ -24042,7 +24033,7 @@
       <c r="G422" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H422" s="7">
+      <c r="H422" s="6">
         <v>0.8</v>
       </c>
       <c r="I422" s="5" t="s">
@@ -24074,7 +24065,7 @@
       <c r="D423" s="5" t="s">
         <v>1320</v>
       </c>
-      <c r="E423" s="6">
+      <c r="E423" s="4">
         <v>258015</v>
       </c>
       <c r="F423" s="5" t="s">
@@ -24083,7 +24074,7 @@
       <c r="G423" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H423" s="7">
+      <c r="H423" s="6">
         <v>0.824</v>
       </c>
       <c r="I423" s="5" t="s">
@@ -24115,7 +24106,7 @@
       <c r="D424" s="5" t="s">
         <v>1323</v>
       </c>
-      <c r="E424" s="6">
+      <c r="E424" s="4">
         <v>139396</v>
       </c>
       <c r="F424" s="5" t="s">
@@ -24156,7 +24147,7 @@
       <c r="D425" s="5" t="s">
         <v>1326</v>
       </c>
-      <c r="E425" s="6">
+      <c r="E425" s="4">
         <v>124870</v>
       </c>
       <c r="F425" s="5" t="s">
@@ -24165,7 +24156,7 @@
       <c r="G425" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H425" s="7">
+      <c r="H425" s="6">
         <v>0.556</v>
       </c>
       <c r="I425" s="5" t="s">
@@ -24197,7 +24188,7 @@
       <c r="D426" s="5" t="s">
         <v>1329</v>
       </c>
-      <c r="E426" s="6">
+      <c r="E426" s="4">
         <v>83466</v>
       </c>
       <c r="F426" s="5" t="s">
@@ -24206,7 +24197,7 @@
       <c r="G426" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H426" s="7">
+      <c r="H426" s="6">
         <v>0.824</v>
       </c>
       <c r="I426" s="5" t="s">
@@ -24225,7 +24216,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="18.75" hidden="1">
       <c r="A427" s="4">
         <v>2018</v>
       </c>
@@ -24238,7 +24229,7 @@
       <c r="D427" s="5" t="s">
         <v>1332</v>
       </c>
-      <c r="E427" s="6">
+      <c r="E427" s="4">
         <v>100399</v>
       </c>
       <c r="F427" s="5" t="s">
@@ -24279,7 +24270,7 @@
       <c r="D428" s="5" t="s">
         <v>1336</v>
       </c>
-      <c r="E428" s="6">
+      <c r="E428" s="4">
         <v>51471</v>
       </c>
       <c r="F428" s="5" t="s">
@@ -24320,7 +24311,7 @@
       <c r="D429" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E429" s="6">
+      <c r="E429" s="4">
         <v>181767</v>
       </c>
       <c r="F429" s="5" t="s">
@@ -24361,7 +24352,7 @@
       <c r="D430" s="5" t="s">
         <v>1266</v>
       </c>
-      <c r="E430" s="6">
+      <c r="E430" s="4">
         <v>13091</v>
       </c>
       <c r="F430" s="5" t="s">
@@ -24402,7 +24393,7 @@
       <c r="D431" s="5" t="s">
         <v>1341</v>
       </c>
-      <c r="E431" s="6">
+      <c r="E431" s="4">
         <v>40074</v>
       </c>
       <c r="F431" s="5" t="s">
@@ -24443,7 +24434,7 @@
       <c r="D432" s="5" t="s">
         <v>1344</v>
       </c>
-      <c r="E432" s="6">
+      <c r="E432" s="4">
         <v>161869</v>
       </c>
       <c r="F432" s="5" t="s">
@@ -24452,7 +24443,7 @@
       <c r="G432" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H432" s="7">
+      <c r="H432" s="6">
         <v>0.8</v>
       </c>
       <c r="I432" s="5" t="s">
@@ -24484,7 +24475,7 @@
       <c r="D433" s="5" t="s">
         <v>1347</v>
       </c>
-      <c r="E433" s="6">
+      <c r="E433" s="4">
         <v>119228</v>
       </c>
       <c r="F433" s="5" t="s">
@@ -24493,7 +24484,7 @@
       <c r="G433" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H433" s="7">
+      <c r="H433" s="6">
         <v>0.174</v>
       </c>
       <c r="I433" s="5" t="s">
@@ -24525,7 +24516,7 @@
       <c r="D434" s="5" t="s">
         <v>1350</v>
       </c>
-      <c r="E434" s="6">
+      <c r="E434" s="4">
         <v>110074</v>
       </c>
       <c r="F434" s="5" t="s">
@@ -24566,7 +24557,7 @@
       <c r="D435" s="5" t="s">
         <v>1353</v>
       </c>
-      <c r="E435" s="6">
+      <c r="E435" s="4">
         <v>170986</v>
       </c>
       <c r="F435" s="5" t="s">
@@ -24607,7 +24598,7 @@
       <c r="D436" s="5" t="s">
         <v>1356</v>
       </c>
-      <c r="E436" s="6">
+      <c r="E436" s="4">
         <v>31952</v>
       </c>
       <c r="F436" s="5" t="s">
@@ -24616,7 +24607,7 @@
       <c r="G436" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H436" s="7">
+      <c r="H436" s="6">
         <v>0.714</v>
       </c>
       <c r="I436" s="5" t="s">
@@ -24648,7 +24639,7 @@
       <c r="D437" s="5" t="s">
         <v>1359</v>
       </c>
-      <c r="E437" s="6">
+      <c r="E437" s="4">
         <v>149807</v>
       </c>
       <c r="F437" s="5" t="s">
@@ -24657,7 +24648,7 @@
       <c r="G437" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H437" s="7">
+      <c r="H437" s="6">
         <v>0.824</v>
       </c>
       <c r="I437" s="5" t="s">
@@ -24689,7 +24680,7 @@
       <c r="D438" s="5" t="s">
         <v>1362</v>
       </c>
-      <c r="E438" s="6">
+      <c r="E438" s="4">
         <v>45611</v>
       </c>
       <c r="F438" s="5" t="s">
@@ -24698,7 +24689,7 @@
       <c r="G438" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H438" s="7">
+      <c r="H438" s="6">
         <v>0.8</v>
       </c>
       <c r="I438" s="5" t="s">
@@ -24730,7 +24721,7 @@
       <c r="D439" s="5" t="s">
         <v>1365</v>
       </c>
-      <c r="E439" s="6">
+      <c r="E439" s="4">
         <v>157539</v>
       </c>
       <c r="F439" s="5" t="s">
@@ -24739,7 +24730,7 @@
       <c r="G439" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H439" s="7">
+      <c r="H439" s="6">
         <v>0.714</v>
       </c>
       <c r="I439" s="5" t="s">
@@ -24771,7 +24762,7 @@
       <c r="D440" s="5" t="s">
         <v>1368</v>
       </c>
-      <c r="E440" s="6">
+      <c r="E440" s="4">
         <v>257987</v>
       </c>
       <c r="F440" s="5" t="s">
@@ -24812,7 +24803,7 @@
       <c r="D441" s="5" t="s">
         <v>1371</v>
       </c>
-      <c r="E441" s="6">
+      <c r="E441" s="4">
         <v>62415</v>
       </c>
       <c r="F441" s="5" t="s">
@@ -24821,7 +24812,7 @@
       <c r="G441" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H441" s="7">
+      <c r="H441" s="6">
         <v>0.714</v>
       </c>
       <c r="I441" s="5" t="s">
@@ -24853,7 +24844,7 @@
       <c r="D442" s="5" t="s">
         <v>1374</v>
       </c>
-      <c r="E442" s="6">
+      <c r="E442" s="4">
         <v>141660</v>
       </c>
       <c r="F442" s="5" t="s">
@@ -24894,7 +24885,7 @@
       <c r="D443" s="5" t="s">
         <v>1377</v>
       </c>
-      <c r="E443" s="6">
+      <c r="E443" s="4">
         <v>38340</v>
       </c>
       <c r="F443" s="5" t="s">
@@ -24935,7 +24926,7 @@
       <c r="D444" s="5" t="s">
         <v>1380</v>
       </c>
-      <c r="E444" s="6">
+      <c r="E444" s="4">
         <v>56976</v>
       </c>
       <c r="F444" s="5" t="s">
@@ -24976,7 +24967,7 @@
       <c r="D445" s="5" t="s">
         <v>1383</v>
       </c>
-      <c r="E445" s="6">
+      <c r="E445" s="4">
         <v>212899</v>
       </c>
       <c r="F445" s="5" t="s">
@@ -24985,7 +24976,7 @@
       <c r="G445" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H445" s="7">
+      <c r="H445" s="6">
         <v>0.824</v>
       </c>
       <c r="I445" s="5" t="s">
@@ -25017,7 +25008,7 @@
       <c r="D446" s="5" t="s">
         <v>1386</v>
       </c>
-      <c r="E446" s="6">
+      <c r="E446" s="4">
         <v>341647</v>
       </c>
       <c r="F446" s="5" t="s">
@@ -25058,7 +25049,7 @@
       <c r="D447" s="5" t="s">
         <v>1389</v>
       </c>
-      <c r="E447" s="6">
+      <c r="E447" s="4">
         <v>167859</v>
       </c>
       <c r="F447" s="5" t="s">
@@ -25067,7 +25058,7 @@
       <c r="G447" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H447" s="7">
+      <c r="H447" s="6">
         <v>0.842</v>
       </c>
       <c r="I447" s="5" t="s">
@@ -25099,7 +25090,7 @@
       <c r="D448" s="5" t="s">
         <v>1392</v>
       </c>
-      <c r="E448" s="6">
+      <c r="E448" s="4">
         <v>21151</v>
       </c>
       <c r="F448" s="5" t="s">
@@ -25140,7 +25131,7 @@
       <c r="D449" s="5" t="s">
         <v>1395</v>
       </c>
-      <c r="E449" s="6">
+      <c r="E449" s="4">
         <v>131090</v>
       </c>
       <c r="F449" s="5" t="s">
@@ -25181,7 +25172,7 @@
       <c r="D450" s="5" t="s">
         <v>1398</v>
       </c>
-      <c r="E450" s="6">
+      <c r="E450" s="4">
         <v>13023</v>
       </c>
       <c r="F450" s="5" t="s">
@@ -25190,7 +25181,7 @@
       <c r="G450" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H450" s="7">
+      <c r="H450" s="6">
         <v>0.556</v>
       </c>
       <c r="I450" s="5" t="s">
@@ -25222,7 +25213,7 @@
       <c r="D451" s="5" t="s">
         <v>1401</v>
       </c>
-      <c r="E451" s="6">
+      <c r="E451" s="4">
         <v>130765</v>
       </c>
       <c r="F451" s="5" t="s">
@@ -25231,7 +25222,7 @@
       <c r="G451" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H451" s="7">
+      <c r="H451" s="6">
         <v>0.8</v>
       </c>
       <c r="I451" s="5" t="s">
@@ -25263,7 +25254,7 @@
       <c r="D452" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="E452" s="6">
+      <c r="E452" s="4">
         <v>225452</v>
       </c>
       <c r="F452" s="5" t="s">
@@ -25272,7 +25263,7 @@
       <c r="G452" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H452" s="7">
+      <c r="H452" s="6">
         <v>0.8</v>
       </c>
       <c r="I452" s="5" t="s">
@@ -25304,7 +25295,7 @@
       <c r="D453" s="5" t="s">
         <v>1406</v>
       </c>
-      <c r="E453" s="6">
+      <c r="E453" s="4">
         <v>453594</v>
       </c>
       <c r="F453" s="5" t="s">
@@ -25313,7 +25304,7 @@
       <c r="G453" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H453" s="7">
+      <c r="H453" s="6">
         <v>0.8</v>
       </c>
       <c r="I453" s="5" t="s">
@@ -25345,7 +25336,7 @@
       <c r="D454" s="5" t="s">
         <v>1409</v>
       </c>
-      <c r="E454" s="6">
+      <c r="E454" s="4">
         <v>226178</v>
       </c>
       <c r="F454" s="5" t="s">
@@ -25354,7 +25345,7 @@
       <c r="G454" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H454" s="7">
+      <c r="H454" s="6">
         <v>0.824</v>
       </c>
       <c r="I454" s="5" t="s">
@@ -25386,7 +25377,7 @@
       <c r="D455" s="5" t="s">
         <v>1412</v>
       </c>
-      <c r="E455" s="6">
+      <c r="E455" s="4">
         <v>63837</v>
       </c>
       <c r="F455" s="5" t="s">
@@ -25427,7 +25418,7 @@
       <c r="D456" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="E456" s="6">
+      <c r="E456" s="4">
         <v>35564</v>
       </c>
       <c r="F456" s="5" t="s">
@@ -25436,7 +25427,7 @@
       <c r="G456" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H456" s="7">
+      <c r="H456" s="6">
         <v>0.692</v>
       </c>
       <c r="I456" s="5" t="s">
@@ -25468,7 +25459,7 @@
       <c r="D457" s="5" t="s">
         <v>1417</v>
       </c>
-      <c r="E457" s="6">
+      <c r="E457" s="4">
         <v>4391</v>
       </c>
       <c r="F457" s="5" t="s">
@@ -25477,7 +25468,7 @@
       <c r="G457" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H457" s="7">
+      <c r="H457" s="6">
         <v>0.556</v>
       </c>
       <c r="I457" s="5" t="s">
@@ -25509,7 +25500,7 @@
       <c r="D458" s="5" t="s">
         <v>1420</v>
       </c>
-      <c r="E458" s="6">
+      <c r="E458" s="4">
         <v>381834</v>
       </c>
       <c r="F458" s="5" t="s">
@@ -25550,7 +25541,7 @@
       <c r="D459" s="5" t="s">
         <v>1423</v>
       </c>
-      <c r="E459" s="6">
+      <c r="E459" s="4">
         <v>341705</v>
       </c>
       <c r="F459" s="5" t="s">
@@ -25591,7 +25582,7 @@
       <c r="D460" s="5" t="s">
         <v>1426</v>
       </c>
-      <c r="E460" s="6">
+      <c r="E460" s="4">
         <v>39679</v>
       </c>
       <c r="F460" s="5" t="s">
@@ -25632,7 +25623,7 @@
       <c r="D461" s="5" t="s">
         <v>1429</v>
       </c>
-      <c r="E461" s="6">
+      <c r="E461" s="4">
         <v>109256</v>
       </c>
       <c r="F461" s="5" t="s">
@@ -25641,7 +25632,7 @@
       <c r="G461" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H461" s="7">
+      <c r="H461" s="6">
         <v>0.824</v>
       </c>
       <c r="I461" s="5" t="s">
@@ -25673,7 +25664,7 @@
       <c r="D462" s="5" t="s">
         <v>1432</v>
       </c>
-      <c r="E462" s="6">
+      <c r="E462" s="4">
         <v>31095</v>
       </c>
       <c r="F462" s="5" t="s">
@@ -25714,7 +25705,7 @@
       <c r="D463" s="5" t="s">
         <v>1435</v>
       </c>
-      <c r="E463" s="6">
+      <c r="E463" s="4">
         <v>171072</v>
       </c>
       <c r="F463" s="5" t="s">
@@ -25723,7 +25714,7 @@
       <c r="G463" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H463" s="7">
+      <c r="H463" s="6">
         <v>0.714</v>
       </c>
       <c r="I463" s="5" t="s">
@@ -25755,7 +25746,7 @@
       <c r="D464" s="5" t="s">
         <v>1438</v>
       </c>
-      <c r="E464" s="6">
+      <c r="E464" s="4">
         <v>127822</v>
       </c>
       <c r="F464" s="5" t="s">
@@ -25796,7 +25787,7 @@
       <c r="D465" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="E465" s="6">
+      <c r="E465" s="4">
         <v>189453</v>
       </c>
       <c r="F465" s="5" t="s">
@@ -25805,7 +25796,7 @@
       <c r="G465" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H465" s="7">
+      <c r="H465" s="6">
         <v>0.3</v>
       </c>
       <c r="I465" s="5" t="s">
@@ -25837,7 +25828,7 @@
       <c r="D466" s="5" t="s">
         <v>1443</v>
       </c>
-      <c r="E466" s="6">
+      <c r="E466" s="4">
         <v>242086</v>
       </c>
       <c r="F466" s="5" t="s">
@@ -25878,7 +25869,7 @@
       <c r="D467" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="E467" s="6">
+      <c r="E467" s="4">
         <v>7767</v>
       </c>
       <c r="F467" s="5" t="s">
@@ -25919,7 +25910,7 @@
       <c r="D468" s="5" t="s">
         <v>1448</v>
       </c>
-      <c r="E468" s="6">
+      <c r="E468" s="4">
         <v>190804</v>
       </c>
       <c r="F468" s="5" t="s">
@@ -25928,7 +25919,7 @@
       <c r="G468" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H468" s="7">
+      <c r="H468" s="6">
         <v>0.714</v>
       </c>
       <c r="I468" s="5" t="s">
@@ -25960,7 +25951,7 @@
       <c r="D469" s="5" t="s">
         <v>1451</v>
       </c>
-      <c r="E469" s="6">
+      <c r="E469" s="4">
         <v>315969</v>
       </c>
       <c r="F469" s="5" t="s">
@@ -26001,7 +25992,7 @@
       <c r="D470" s="5" t="s">
         <v>1454</v>
       </c>
-      <c r="E470" s="6">
+      <c r="E470" s="4">
         <v>54906</v>
       </c>
       <c r="F470" s="5" t="s">
@@ -26042,7 +26033,7 @@
       <c r="D471" s="5" t="s">
         <v>1457</v>
       </c>
-      <c r="E471" s="6">
+      <c r="E471" s="4">
         <v>157635</v>
       </c>
       <c r="F471" s="5" t="s">
@@ -26083,7 +26074,7 @@
       <c r="D472" s="5" t="s">
         <v>1460</v>
       </c>
-      <c r="E472" s="6">
+      <c r="E472" s="4">
         <v>14192</v>
       </c>
       <c r="F472" s="5" t="s">
@@ -26092,7 +26083,7 @@
       <c r="G472" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H472" s="7">
+      <c r="H472" s="6">
         <v>0.824</v>
       </c>
       <c r="I472" s="5" t="s">
@@ -26124,7 +26115,7 @@
       <c r="D473" s="5" t="s">
         <v>1463</v>
       </c>
-      <c r="E473" s="6">
+      <c r="E473" s="4">
         <v>57834</v>
       </c>
       <c r="F473" s="5" t="s">
@@ -26165,7 +26156,7 @@
       <c r="D474" s="5" t="s">
         <v>1466</v>
       </c>
-      <c r="E474" s="6">
+      <c r="E474" s="4">
         <v>282041</v>
       </c>
       <c r="F474" s="5" t="s">
@@ -26206,7 +26197,7 @@
       <c r="D475" s="5" t="s">
         <v>1469</v>
       </c>
-      <c r="E475" s="6">
+      <c r="E475" s="4">
         <v>406635</v>
       </c>
       <c r="F475" s="5" t="s">
@@ -26247,7 +26238,7 @@
       <c r="D476" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="E476" s="6">
+      <c r="E476" s="4">
         <v>191422</v>
       </c>
       <c r="F476" s="5" t="s">
@@ -26288,7 +26279,7 @@
       <c r="D477" s="5" t="s">
         <v>1475</v>
       </c>
-      <c r="E477" s="6">
+      <c r="E477" s="4">
         <v>15076</v>
       </c>
       <c r="F477" s="5" t="s">
@@ -26329,7 +26320,7 @@
       <c r="D478" s="5" t="s">
         <v>1478</v>
       </c>
-      <c r="E478" s="6">
+      <c r="E478" s="4">
         <v>129788</v>
       </c>
       <c r="F478" s="5" t="s">
@@ -26338,7 +26329,7 @@
       <c r="G478" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H478" s="7">
+      <c r="H478" s="6">
         <v>0.8</v>
       </c>
       <c r="I478" s="5" t="s">
@@ -26370,7 +26361,7 @@
       <c r="D479" s="5" t="s">
         <v>1481</v>
       </c>
-      <c r="E479" s="6">
+      <c r="E479" s="4">
         <v>49802</v>
       </c>
       <c r="F479" s="5" t="s">
@@ -26379,7 +26370,7 @@
       <c r="G479" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H479" s="7">
+      <c r="H479" s="6">
         <v>0.833</v>
       </c>
       <c r="I479" s="5" t="s">
@@ -26398,7 +26389,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="18.75" hidden="1">
+    <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="18.75">
       <c r="A480" s="4">
         <v>2018</v>
       </c>
@@ -26411,16 +26402,16 @@
       <c r="D480" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="E480" s="6">
-        <v>447661</v>
+      <c r="E480" s="4">
+        <v>103381</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>588</v>
+        <v>229</v>
       </c>
       <c r="G480" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H480" s="7">
+      <c r="H480" s="6">
         <v>0.273</v>
       </c>
       <c r="I480" s="5" t="s">
@@ -26452,7 +26443,7 @@
       <c r="D481" s="5" t="s">
         <v>1486</v>
       </c>
-      <c r="E481" s="6">
+      <c r="E481" s="4">
         <v>140032</v>
       </c>
       <c r="F481" s="5" t="s">
@@ -26461,7 +26452,7 @@
       <c r="G481" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H481" s="7">
+      <c r="H481" s="6">
         <v>0.824</v>
       </c>
       <c r="I481" s="5" t="s">
@@ -26493,7 +26484,7 @@
       <c r="D482" s="5" t="s">
         <v>1489</v>
       </c>
-      <c r="E482" s="6">
+      <c r="E482" s="4">
         <v>152176</v>
       </c>
       <c r="F482" s="5" t="s">
@@ -26502,7 +26493,7 @@
       <c r="G482" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H482" s="7">
+      <c r="H482" s="6">
         <v>0.207</v>
       </c>
       <c r="I482" s="5" t="s">
@@ -26534,7 +26525,7 @@
       <c r="D483" s="5" t="s">
         <v>1492</v>
       </c>
-      <c r="E483" s="6">
+      <c r="E483" s="4">
         <v>335209</v>
       </c>
       <c r="F483" s="5" t="s">
@@ -26575,7 +26566,7 @@
       <c r="D484" s="5" t="s">
         <v>1495</v>
       </c>
-      <c r="E484" s="6">
+      <c r="E484" s="4">
         <v>25727</v>
       </c>
       <c r="F484" s="5" t="s">
@@ -26616,7 +26607,7 @@
       <c r="D485" s="5" t="s">
         <v>1498</v>
       </c>
-      <c r="E485" s="6">
+      <c r="E485" s="4">
         <v>434224</v>
       </c>
       <c r="F485" s="5" t="s">
@@ -26657,7 +26648,7 @@
       <c r="D486" s="5" t="s">
         <v>1501</v>
       </c>
-      <c r="E486" s="6">
+      <c r="E486" s="4">
         <v>9594</v>
       </c>
       <c r="F486" s="5" t="s">
@@ -26698,7 +26689,7 @@
       <c r="D487" s="5" t="s">
         <v>1504</v>
       </c>
-      <c r="E487" s="6">
+      <c r="E487" s="4">
         <v>398073</v>
       </c>
       <c r="F487" s="5" t="s">
@@ -26739,7 +26730,7 @@
       <c r="D488" s="5" t="s">
         <v>1507</v>
       </c>
-      <c r="E488" s="6">
+      <c r="E488" s="4">
         <v>52595</v>
       </c>
       <c r="F488" s="5" t="s">
@@ -26778,7 +26769,7 @@
       <c r="D489" s="5" t="s">
         <v>1510</v>
       </c>
-      <c r="E489" s="6">
+      <c r="E489" s="4">
         <v>90681</v>
       </c>
       <c r="F489" s="5" t="s">
@@ -26819,7 +26810,7 @@
       <c r="D490" s="5" t="s">
         <v>1513</v>
       </c>
-      <c r="E490" s="6">
+      <c r="E490" s="4">
         <v>61812</v>
       </c>
       <c r="F490" s="5" t="s">
@@ -26860,7 +26851,7 @@
       <c r="D491" s="5" t="s">
         <v>1516</v>
       </c>
-      <c r="E491" s="6">
+      <c r="E491" s="4">
         <v>64126</v>
       </c>
       <c r="F491" s="5" t="s">
@@ -26869,7 +26860,7 @@
       <c r="G491" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H491" s="7">
+      <c r="H491" s="6">
         <v>0.833</v>
       </c>
       <c r="I491" s="5" t="s">
@@ -26901,7 +26892,7 @@
       <c r="D492" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="E492" s="6">
+      <c r="E492" s="4">
         <v>133964</v>
       </c>
       <c r="F492" s="5" t="s">
@@ -26910,7 +26901,7 @@
       <c r="G492" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H492" s="7">
+      <c r="H492" s="6">
         <v>0.8</v>
       </c>
       <c r="I492" s="5" t="s">
@@ -26942,7 +26933,7 @@
       <c r="D493" s="5" t="s">
         <v>1521</v>
       </c>
-      <c r="E493" s="6">
+      <c r="E493" s="4">
         <v>258004</v>
       </c>
       <c r="F493" s="5" t="s">
@@ -26983,7 +26974,7 @@
       <c r="D494" s="5" t="s">
         <v>1524</v>
       </c>
-      <c r="E494" s="6">
+      <c r="E494" s="4">
         <v>44235</v>
       </c>
       <c r="F494" s="5" t="s">
@@ -26992,7 +26983,7 @@
       <c r="G494" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H494" s="7">
+      <c r="H494" s="6">
         <v>0.556</v>
       </c>
       <c r="I494" s="5" t="s">
@@ -27024,7 +27015,7 @@
       <c r="D495" s="5" t="s">
         <v>1527</v>
       </c>
-      <c r="E495" s="6">
+      <c r="E495" s="4">
         <v>58923</v>
       </c>
       <c r="F495" s="5" t="s">
@@ -27065,7 +27056,7 @@
       <c r="D496" s="5" t="s">
         <v>1530</v>
       </c>
-      <c r="E496" s="6">
+      <c r="E496" s="4">
         <v>41281</v>
       </c>
       <c r="F496" s="5" t="s">
@@ -27074,7 +27065,7 @@
       <c r="G496" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H496" s="7">
+      <c r="H496" s="6">
         <v>0.824</v>
       </c>
       <c r="I496" s="5" t="s">
@@ -27106,7 +27097,7 @@
       <c r="D497" s="5" t="s">
         <v>1298</v>
       </c>
-      <c r="E497" s="6">
+      <c r="E497" s="4">
         <v>27486</v>
       </c>
       <c r="F497" s="5" t="s">
@@ -27147,7 +27138,7 @@
       <c r="D498" s="5" t="s">
         <v>1535</v>
       </c>
-      <c r="E498" s="6">
+      <c r="E498" s="4">
         <v>182722</v>
       </c>
       <c r="F498" s="5" t="s">
@@ -27156,7 +27147,7 @@
       <c r="G498" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H498" s="7">
+      <c r="H498" s="6">
         <v>0.824</v>
       </c>
       <c r="I498" s="5" t="s">
@@ -27188,7 +27179,7 @@
       <c r="D499" s="5" t="s">
         <v>1538</v>
       </c>
-      <c r="E499" s="6">
+      <c r="E499" s="4">
         <v>226012</v>
       </c>
       <c r="F499" s="5" t="s">
@@ -27197,7 +27188,7 @@
       <c r="G499" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H499" s="7">
+      <c r="H499" s="6">
         <v>0.824</v>
       </c>
       <c r="I499" s="5" t="s">
@@ -27229,7 +27220,7 @@
       <c r="D500" s="5" t="s">
         <v>1541</v>
       </c>
-      <c r="E500" s="6">
+      <c r="E500" s="4">
         <v>16816</v>
       </c>
       <c r="F500" s="5" t="s">
@@ -27238,7 +27229,7 @@
       <c r="G500" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H500" s="7">
+      <c r="H500" s="6">
         <v>0.842</v>
       </c>
       <c r="I500" s="5" t="s">
@@ -27270,7 +27261,7 @@
       <c r="D501" s="5" t="s">
         <v>1544</v>
       </c>
-      <c r="E501" s="6">
+      <c r="E501" s="4">
         <v>30690</v>
       </c>
       <c r="F501" s="5" t="s">
@@ -27279,7 +27270,7 @@
       <c r="G501" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H501" s="7">
+      <c r="H501" s="6">
         <v>0.154</v>
       </c>
       <c r="I501" s="5" t="s">
@@ -27311,7 +27302,7 @@
       <c r="D502" s="5" t="s">
         <v>1547</v>
       </c>
-      <c r="E502" s="6">
+      <c r="E502" s="4">
         <v>205562</v>
       </c>
       <c r="F502" s="5" t="s">
@@ -27320,7 +27311,7 @@
       <c r="G502" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H502" s="7">
+      <c r="H502" s="6">
         <v>0.8</v>
       </c>
       <c r="I502" s="5" t="s">
@@ -27352,7 +27343,7 @@
       <c r="D503" s="5" t="s">
         <v>1550</v>
       </c>
-      <c r="E503" s="6">
+      <c r="E503" s="4">
         <v>125019</v>
       </c>
       <c r="F503" s="5" t="s">
@@ -27361,7 +27352,7 @@
       <c r="G503" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H503" s="7">
+      <c r="H503" s="6">
         <v>0.824</v>
       </c>
       <c r="I503" s="5" t="s">
@@ -27393,7 +27384,7 @@
       <c r="D504" s="5" t="s">
         <v>1553</v>
       </c>
-      <c r="E504" s="6">
+      <c r="E504" s="4">
         <v>41355</v>
       </c>
       <c r="F504" s="5" t="s">
@@ -27402,7 +27393,7 @@
       <c r="G504" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H504" s="7">
+      <c r="H504" s="6">
         <v>0.556</v>
       </c>
       <c r="I504" s="5" t="s">
@@ -27434,7 +27425,7 @@
       <c r="D505" s="5" t="s">
         <v>1065</v>
       </c>
-      <c r="E505" s="6">
+      <c r="E505" s="4">
         <v>80444</v>
       </c>
       <c r="F505" s="5" t="s">
@@ -27443,7 +27434,7 @@
       <c r="G505" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H505" s="7">
+      <c r="H505" s="6">
         <v>0.207</v>
       </c>
       <c r="I505" s="5" t="s">
@@ -27475,7 +27466,7 @@
       <c r="D506" s="5" t="s">
         <v>1558</v>
       </c>
-      <c r="E506" s="6">
+      <c r="E506" s="4">
         <v>221025</v>
       </c>
       <c r="F506" s="5" t="s">
@@ -27484,7 +27475,7 @@
       <c r="G506" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H506" s="7">
+      <c r="H506" s="6">
         <v>0.857</v>
       </c>
       <c r="I506" s="5" t="s">
@@ -27516,7 +27507,7 @@
       <c r="D507" s="5" t="s">
         <v>1561</v>
       </c>
-      <c r="E507" s="6">
+      <c r="E507" s="4">
         <v>165007</v>
       </c>
       <c r="F507" s="5" t="s">
@@ -27525,7 +27516,7 @@
       <c r="G507" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H507" s="7">
+      <c r="H507" s="6">
         <v>0.857</v>
       </c>
       <c r="I507" s="5" t="s">
@@ -27557,7 +27548,7 @@
       <c r="D508" s="5" t="s">
         <v>1564</v>
       </c>
-      <c r="E508" s="6">
+      <c r="E508" s="4">
         <v>50174</v>
       </c>
       <c r="F508" s="5" t="s">
@@ -27566,7 +27557,7 @@
       <c r="G508" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H508" s="7">
+      <c r="H508" s="6">
         <v>0.692</v>
       </c>
       <c r="I508" s="5" t="s">
@@ -27585,7 +27576,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="18.75" hidden="1">
+    <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="18.75">
       <c r="A509" s="4">
         <v>2018</v>
       </c>
@@ -27598,11 +27589,11 @@
       <c r="D509" s="5" t="s">
         <v>1567</v>
       </c>
-      <c r="E509" s="6">
+      <c r="E509" s="4">
         <v>214775</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>588</v>
+        <v>16</v>
       </c>
       <c r="G509" s="5" t="s">
         <v>17</v>
@@ -27639,7 +27630,7 @@
       <c r="D510" s="5" t="s">
         <v>1570</v>
       </c>
-      <c r="E510" s="6">
+      <c r="E510" s="4">
         <v>163222</v>
       </c>
       <c r="F510" s="5" t="s">
@@ -27680,7 +27671,7 @@
       <c r="D511" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E511" s="6">
+      <c r="E511" s="4">
         <v>40433</v>
       </c>
       <c r="F511" s="5" t="s">
@@ -27721,7 +27712,7 @@
       <c r="D512" s="5" t="s">
         <v>1575</v>
       </c>
-      <c r="E512" s="6">
+      <c r="E512" s="4">
         <v>77710</v>
       </c>
       <c r="F512" s="5" t="s">
@@ -27730,7 +27721,7 @@
       <c r="G512" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H512" s="7">
+      <c r="H512" s="6">
         <v>0.842</v>
       </c>
       <c r="I512" s="5" t="s">
@@ -27762,7 +27753,7 @@
       <c r="D513" s="5" t="s">
         <v>1578</v>
       </c>
-      <c r="E513" s="6">
+      <c r="E513" s="4">
         <v>27389</v>
       </c>
       <c r="F513" s="5" t="s">
@@ -27803,7 +27794,7 @@
       <c r="D514" s="5" t="s">
         <v>1581</v>
       </c>
-      <c r="E514" s="6">
+      <c r="E514" s="4">
         <v>102017</v>
       </c>
       <c r="F514" s="5" t="s">
@@ -27844,7 +27835,7 @@
       <c r="D515" s="5" t="s">
         <v>1584</v>
       </c>
-      <c r="E515" s="6">
+      <c r="E515" s="4">
         <v>134602</v>
       </c>
       <c r="F515" s="5" t="s">
@@ -27885,7 +27876,7 @@
       <c r="D516" s="5" t="s">
         <v>1587</v>
       </c>
-      <c r="E516" s="6">
+      <c r="E516" s="4">
         <v>58602</v>
       </c>
       <c r="F516" s="5" t="s">
@@ -27894,7 +27885,7 @@
       <c r="G516" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H516" s="7">
+      <c r="H516" s="6">
         <v>0.842</v>
       </c>
       <c r="I516" s="5" t="s">
@@ -27926,7 +27917,7 @@
       <c r="D517" s="5" t="s">
         <v>1590</v>
       </c>
-      <c r="E517" s="6">
+      <c r="E517" s="4">
         <v>15680</v>
       </c>
       <c r="F517" s="5" t="s">
@@ -27954,7 +27945,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="18.75" hidden="1">
       <c r="A518" s="4">
         <v>2018</v>
       </c>
@@ -27967,7 +27958,7 @@
       <c r="D518" s="5" t="s">
         <v>1593</v>
       </c>
-      <c r="E518" s="6">
+      <c r="E518" s="4">
         <v>159668</v>
       </c>
       <c r="F518" s="5" t="s">
@@ -28008,7 +27999,7 @@
       <c r="D519" s="5" t="s">
         <v>1596</v>
       </c>
-      <c r="E519" s="6">
+      <c r="E519" s="4">
         <v>183836</v>
       </c>
       <c r="F519" s="5" t="s">
@@ -28017,7 +28008,7 @@
       <c r="G519" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H519" s="7">
+      <c r="H519" s="6">
         <v>0.824</v>
       </c>
       <c r="I519" s="5" t="s">
@@ -28049,7 +28040,7 @@
       <c r="D520" s="5" t="s">
         <v>1599</v>
       </c>
-      <c r="E520" s="6">
+      <c r="E520" s="4">
         <v>348795</v>
       </c>
       <c r="F520" s="5" t="s">
@@ -28090,7 +28081,7 @@
       <c r="D521" s="5" t="s">
         <v>1602</v>
       </c>
-      <c r="E521" s="6">
+      <c r="E521" s="4">
         <v>38497</v>
       </c>
       <c r="F521" s="5" t="s">
@@ -28099,7 +28090,7 @@
       <c r="G521" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H521" s="7">
+      <c r="H521" s="6">
         <v>0.842</v>
       </c>
       <c r="I521" s="5" t="s">
@@ -28131,7 +28122,7 @@
       <c r="D522" s="5" t="s">
         <v>1605</v>
       </c>
-      <c r="E522" s="6">
+      <c r="E522" s="4">
         <v>43530</v>
       </c>
       <c r="F522" s="5" t="s">
@@ -28140,7 +28131,7 @@
       <c r="G522" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H522" s="7">
+      <c r="H522" s="6">
         <v>0.857</v>
       </c>
       <c r="I522" s="5" t="s">
@@ -28172,7 +28163,7 @@
       <c r="D523" s="5" t="s">
         <v>1608</v>
       </c>
-      <c r="E523" s="6">
+      <c r="E523" s="4">
         <v>129476</v>
       </c>
       <c r="F523" s="5" t="s">
@@ -28181,7 +28172,7 @@
       <c r="G523" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H523" s="7">
+      <c r="H523" s="6">
         <v>0.857</v>
       </c>
       <c r="I523" s="5" t="s">
@@ -28213,7 +28204,7 @@
       <c r="D524" s="5" t="s">
         <v>1611</v>
       </c>
-      <c r="E524" s="6">
+      <c r="E524" s="4">
         <v>287183</v>
       </c>
       <c r="F524" s="5" t="s">
@@ -28254,7 +28245,7 @@
       <c r="D525" s="5" t="s">
         <v>1614</v>
       </c>
-      <c r="E525" s="6">
+      <c r="E525" s="4">
         <v>45320</v>
       </c>
       <c r="F525" s="5" t="s">
@@ -28295,7 +28286,7 @@
       <c r="D526" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E526" s="6">
+      <c r="E526" s="4">
         <v>288230</v>
       </c>
       <c r="F526" s="5" t="s">
@@ -28304,7 +28295,7 @@
       <c r="G526" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H526" s="7">
+      <c r="H526" s="6">
         <v>0.857</v>
       </c>
       <c r="I526" s="5" t="s">
@@ -28336,7 +28327,7 @@
       <c r="D527" s="5" t="s">
         <v>1618</v>
       </c>
-      <c r="E527" s="6">
+      <c r="E527" s="4">
         <v>104466</v>
       </c>
       <c r="F527" s="5" t="s">
@@ -28375,7 +28366,7 @@
       <c r="D528" s="5" t="s">
         <v>1621</v>
       </c>
-      <c r="E528" s="6">
+      <c r="E528" s="4">
         <v>118287</v>
       </c>
       <c r="F528" s="5" t="s">
@@ -28384,7 +28375,7 @@
       <c r="G528" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H528" s="7">
+      <c r="H528" s="6">
         <v>0.8</v>
       </c>
       <c r="I528" s="5" t="s">
@@ -28416,7 +28407,7 @@
       <c r="D529" s="5" t="s">
         <v>1624</v>
       </c>
-      <c r="E529" s="6">
+      <c r="E529" s="4">
         <v>298976</v>
       </c>
       <c r="F529" s="5" t="s">
@@ -28457,7 +28448,7 @@
       <c r="D530" s="5" t="s">
         <v>1627</v>
       </c>
-      <c r="E530" s="6">
+      <c r="E530" s="4">
         <v>18006</v>
       </c>
       <c r="F530" s="5" t="s">
@@ -28466,7 +28457,7 @@
       <c r="G530" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H530" s="7">
+      <c r="H530" s="6">
         <v>0.824</v>
       </c>
       <c r="I530" s="5" t="s">
@@ -28498,7 +28489,7 @@
       <c r="D531" s="5" t="s">
         <v>1115</v>
       </c>
-      <c r="E531" s="6">
+      <c r="E531" s="4">
         <v>35251</v>
       </c>
       <c r="F531" s="5" t="s">
@@ -28507,7 +28498,7 @@
       <c r="G531" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H531" s="7">
+      <c r="H531" s="6">
         <v>0.714</v>
       </c>
       <c r="I531" s="5" t="s">
@@ -28539,7 +28530,7 @@
       <c r="D532" s="5" t="s">
         <v>1632</v>
       </c>
-      <c r="E532" s="6">
+      <c r="E532" s="4">
         <v>197300</v>
       </c>
       <c r="F532" s="5" t="s">
@@ -28548,7 +28539,7 @@
       <c r="G532" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H532" s="7">
+      <c r="H532" s="6">
         <v>0.842</v>
       </c>
       <c r="I532" s="5" t="s">
@@ -28580,7 +28571,7 @@
       <c r="D533" s="5" t="s">
         <v>1635</v>
       </c>
-      <c r="E533" s="6">
+      <c r="E533" s="4">
         <v>184672</v>
       </c>
       <c r="F533" s="5" t="s">
@@ -28589,7 +28580,7 @@
       <c r="G533" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H533" s="7">
+      <c r="H533" s="6">
         <v>0.8</v>
       </c>
       <c r="I533" s="5" t="s">
@@ -28621,7 +28612,7 @@
       <c r="D534" s="5" t="s">
         <v>1638</v>
       </c>
-      <c r="E534" s="6">
+      <c r="E534" s="4">
         <v>19981</v>
       </c>
       <c r="F534" s="5" t="s">
@@ -28630,7 +28621,7 @@
       <c r="G534" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H534" s="7">
+      <c r="H534" s="6">
         <v>0.857</v>
       </c>
       <c r="I534" s="5" t="s">
@@ -28662,7 +28653,7 @@
       <c r="D535" s="5" t="s">
         <v>1641</v>
       </c>
-      <c r="E535" s="6">
+      <c r="E535" s="4">
         <v>315557</v>
       </c>
       <c r="F535" s="5" t="s">
@@ -28703,7 +28694,7 @@
       <c r="D536" s="5" t="s">
         <v>1644</v>
       </c>
-      <c r="E536" s="6">
+      <c r="E536" s="4">
         <v>303116</v>
       </c>
       <c r="F536" s="5" t="s">
@@ -28712,7 +28703,7 @@
       <c r="G536" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H536" s="7">
+      <c r="H536" s="6">
         <v>0.231</v>
       </c>
       <c r="I536" s="5" t="s">
@@ -28744,7 +28735,7 @@
       <c r="D537" s="5" t="s">
         <v>1647</v>
       </c>
-      <c r="E537" s="6">
+      <c r="E537" s="4">
         <v>18829</v>
       </c>
       <c r="F537" s="5" t="s">
@@ -28753,7 +28744,7 @@
       <c r="G537" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H537" s="7">
+      <c r="H537" s="6">
         <v>0.842</v>
       </c>
       <c r="I537" s="5" t="s">
@@ -28785,7 +28776,7 @@
       <c r="D538" s="5" t="s">
         <v>1650</v>
       </c>
-      <c r="E538" s="6">
+      <c r="E538" s="4">
         <v>339808</v>
       </c>
       <c r="F538" s="5" t="s">
@@ -28824,7 +28815,7 @@
       <c r="D539" s="5" t="s">
         <v>1653</v>
       </c>
-      <c r="E539" s="6">
+      <c r="E539" s="4">
         <v>38805</v>
       </c>
       <c r="F539" s="5" t="s">
@@ -28865,7 +28856,7 @@
       <c r="D540" s="5" t="s">
         <v>1656</v>
       </c>
-      <c r="E540" s="6">
+      <c r="E540" s="4">
         <v>230717</v>
       </c>
       <c r="F540" s="5" t="s">
@@ -28874,7 +28865,7 @@
       <c r="G540" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H540" s="7">
+      <c r="H540" s="6">
         <v>0.4</v>
       </c>
       <c r="I540" s="5" t="s">
@@ -28906,7 +28897,7 @@
       <c r="D541" s="5" t="s">
         <v>1659</v>
       </c>
-      <c r="E541" s="6">
+      <c r="E541" s="4">
         <v>75442</v>
       </c>
       <c r="F541" s="5" t="s">
@@ -28947,7 +28938,7 @@
       <c r="D542" s="5" t="s">
         <v>1662</v>
       </c>
-      <c r="E542" s="6">
+      <c r="E542" s="4">
         <v>179184</v>
       </c>
       <c r="F542" s="5" t="s">
@@ -28956,7 +28947,7 @@
       <c r="G542" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H542" s="7">
+      <c r="H542" s="6">
         <v>0.824</v>
       </c>
       <c r="I542" s="5" t="s">
@@ -28988,7 +28979,7 @@
       <c r="D543" s="5" t="s">
         <v>1665</v>
       </c>
-      <c r="E543" s="6">
+      <c r="E543" s="4">
         <v>75287</v>
       </c>
       <c r="F543" s="5" t="s">
@@ -29029,7 +29020,7 @@
       <c r="D544" s="5" t="s">
         <v>1668</v>
       </c>
-      <c r="E544" s="6">
+      <c r="E544" s="4">
         <v>120630</v>
       </c>
       <c r="F544" s="5" t="s">
@@ -29038,7 +29029,7 @@
       <c r="G544" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H544" s="7">
+      <c r="H544" s="6">
         <v>0.714</v>
       </c>
       <c r="I544" s="5" t="s">
@@ -29070,7 +29061,7 @@
       <c r="D545" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="E545" s="6">
+      <c r="E545" s="4">
         <v>241641</v>
       </c>
       <c r="F545" s="5" t="s">
@@ -29111,7 +29102,7 @@
       <c r="D546" s="5" t="s">
         <v>1673</v>
       </c>
-      <c r="E546" s="6">
+      <c r="E546" s="4">
         <v>88490</v>
       </c>
       <c r="F546" s="5" t="s">
@@ -29120,7 +29111,7 @@
       <c r="G546" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H546" s="7">
+      <c r="H546" s="6">
         <v>0.857</v>
       </c>
       <c r="I546" s="5" t="s">
@@ -29152,7 +29143,7 @@
       <c r="D547" s="5" t="s">
         <v>1676</v>
       </c>
-      <c r="E547" s="6">
+      <c r="E547" s="4">
         <v>162959</v>
       </c>
       <c r="F547" s="5" t="s">
@@ -29161,7 +29152,7 @@
       <c r="G547" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H547" s="7">
+      <c r="H547" s="6">
         <v>0.842</v>
       </c>
       <c r="I547" s="5" t="s">
@@ -29193,7 +29184,7 @@
       <c r="D548" s="5" t="s">
         <v>1679</v>
       </c>
-      <c r="E548" s="6">
+      <c r="E548" s="4">
         <v>58576</v>
       </c>
       <c r="F548" s="5" t="s">
@@ -29234,7 +29225,7 @@
       <c r="D549" s="5" t="s">
         <v>1682</v>
       </c>
-      <c r="E549" s="6">
+      <c r="E549" s="4">
         <v>166277</v>
       </c>
       <c r="F549" s="5" t="s">
@@ -29275,7 +29266,7 @@
       <c r="D550" s="5" t="s">
         <v>1685</v>
       </c>
-      <c r="E550" s="6">
+      <c r="E550" s="4">
         <v>165825</v>
       </c>
       <c r="F550" s="5" t="s">
@@ -29316,7 +29307,7 @@
       <c r="D551" s="5" t="s">
         <v>1688</v>
       </c>
-      <c r="E551" s="6">
+      <c r="E551" s="4">
         <v>215679</v>
       </c>
       <c r="F551" s="5" t="s">
@@ -29357,7 +29348,7 @@
       <c r="D552" s="5" t="s">
         <v>1691</v>
       </c>
-      <c r="E552" s="6">
+      <c r="E552" s="4">
         <v>111630</v>
       </c>
       <c r="F552" s="5" t="s">
@@ -29398,7 +29389,7 @@
       <c r="D553" s="5" t="s">
         <v>1694</v>
       </c>
-      <c r="E553" s="6">
+      <c r="E553" s="4">
         <v>206734</v>
       </c>
       <c r="F553" s="5" t="s">
@@ -29407,7 +29398,7 @@
       <c r="G553" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H553" s="7">
+      <c r="H553" s="6">
         <v>0.842</v>
       </c>
       <c r="I553" s="5" t="s">
@@ -29439,7 +29430,7 @@
       <c r="D554" s="5" t="s">
         <v>1697</v>
       </c>
-      <c r="E554" s="6">
+      <c r="E554" s="4">
         <v>102744</v>
       </c>
       <c r="F554" s="5" t="s">
@@ -29448,7 +29439,7 @@
       <c r="G554" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H554" s="7">
+      <c r="H554" s="6">
         <v>0.824</v>
       </c>
       <c r="I554" s="5" t="s">
@@ -29480,7 +29471,7 @@
       <c r="D555" s="5" t="s">
         <v>1700</v>
       </c>
-      <c r="E555" s="6">
+      <c r="E555" s="4">
         <v>148372</v>
       </c>
       <c r="F555" s="5" t="s">
@@ -29489,7 +29480,7 @@
       <c r="G555" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H555" s="7">
+      <c r="H555" s="6">
         <v>0.833</v>
       </c>
       <c r="I555" s="5" t="s">
@@ -29521,7 +29512,7 @@
       <c r="D556" s="5" t="s">
         <v>1703</v>
       </c>
-      <c r="E556" s="6">
+      <c r="E556" s="4">
         <v>252080</v>
       </c>
       <c r="F556" s="5" t="s">
@@ -29530,7 +29521,7 @@
       <c r="G556" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H556" s="7">
+      <c r="H556" s="6">
         <v>0.556</v>
       </c>
       <c r="I556" s="5" t="s">
@@ -29562,7 +29553,7 @@
       <c r="D557" s="5" t="s">
         <v>1706</v>
       </c>
-      <c r="E557" s="6">
+      <c r="E557" s="4">
         <v>2865</v>
       </c>
       <c r="F557" s="5" t="s">
@@ -29571,7 +29562,7 @@
       <c r="G557" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H557" s="7">
+      <c r="H557" s="6">
         <v>0.842</v>
       </c>
       <c r="I557" s="5" t="s">
@@ -29603,7 +29594,7 @@
       <c r="D558" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="E558" s="6">
+      <c r="E558" s="4">
         <v>18644</v>
       </c>
       <c r="F558" s="5" t="s">
@@ -29612,7 +29603,7 @@
       <c r="G558" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H558" s="7">
+      <c r="H558" s="6">
         <v>0.842</v>
       </c>
       <c r="I558" s="5" t="s">
@@ -29644,7 +29635,7 @@
       <c r="D559" s="5" t="s">
         <v>1712</v>
       </c>
-      <c r="E559" s="6">
+      <c r="E559" s="4">
         <v>63531</v>
       </c>
       <c r="F559" s="5" t="s">
@@ -29653,7 +29644,7 @@
       <c r="G559" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H559" s="7">
+      <c r="H559" s="6">
         <v>0.842</v>
       </c>
       <c r="I559" s="5" t="s">
@@ -29685,7 +29676,7 @@
       <c r="D560" s="5" t="s">
         <v>1716</v>
       </c>
-      <c r="E560" s="6">
+      <c r="E560" s="4">
         <v>195906</v>
       </c>
       <c r="F560" s="5" t="s">
@@ -29724,7 +29715,7 @@
       <c r="D561" s="5" t="s">
         <v>1719</v>
       </c>
-      <c r="E561" s="6">
+      <c r="E561" s="4">
         <v>149238</v>
       </c>
       <c r="F561" s="5" t="s">
@@ -29733,7 +29724,7 @@
       <c r="G561" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H561" s="7">
+      <c r="H561" s="6">
         <v>0.824</v>
       </c>
       <c r="I561" s="5" t="s">
@@ -29765,7 +29756,7 @@
       <c r="D562" s="5" t="s">
         <v>1722</v>
       </c>
-      <c r="E562" s="6">
+      <c r="E562" s="4">
         <v>318705</v>
       </c>
       <c r="F562" s="5" t="s">
@@ -29774,7 +29765,7 @@
       <c r="G562" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H562" s="7">
+      <c r="H562" s="6">
         <v>0.824</v>
       </c>
       <c r="I562" s="5" t="s">
@@ -29806,7 +29797,7 @@
       <c r="D563" s="5" t="s">
         <v>1725</v>
       </c>
-      <c r="E563" s="6">
+      <c r="E563" s="4">
         <v>245251</v>
       </c>
       <c r="F563" s="5" t="s">
@@ -29815,7 +29806,7 @@
       <c r="G563" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H563" s="7">
+      <c r="H563" s="6">
         <v>0.824</v>
       </c>
       <c r="I563" s="5" t="s">
@@ -29847,7 +29838,7 @@
       <c r="D564" s="5" t="s">
         <v>1728</v>
       </c>
-      <c r="E564" s="6">
+      <c r="E564" s="4">
         <v>126716</v>
       </c>
       <c r="F564" s="5" t="s">
@@ -29856,7 +29847,7 @@
       <c r="G564" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H564" s="7">
+      <c r="H564" s="6">
         <v>0.857</v>
       </c>
       <c r="I564" s="5" t="s">
@@ -29888,7 +29879,7 @@
       <c r="D565" s="5" t="s">
         <v>1731</v>
       </c>
-      <c r="E565" s="6">
+      <c r="E565" s="4">
         <v>146805</v>
       </c>
       <c r="F565" s="5" t="s">
@@ -29929,7 +29920,7 @@
       <c r="D566" s="5" t="s">
         <v>1734</v>
       </c>
-      <c r="E566" s="6">
+      <c r="E566" s="4">
         <v>139341</v>
       </c>
       <c r="F566" s="5" t="s">
@@ -29938,7 +29929,7 @@
       <c r="G566" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H566" s="7">
+      <c r="H566" s="6">
         <v>0.833</v>
       </c>
       <c r="I566" s="5" t="s">
@@ -29970,7 +29961,7 @@
       <c r="D567" s="5" t="s">
         <v>1737</v>
       </c>
-      <c r="E567" s="6">
+      <c r="E567" s="4">
         <v>45178</v>
       </c>
       <c r="F567" s="5" t="s">
@@ -29979,7 +29970,7 @@
       <c r="G567" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H567" s="7">
+      <c r="H567" s="6">
         <v>0.556</v>
       </c>
       <c r="I567" s="5" t="s">
@@ -30011,7 +30002,7 @@
       <c r="D568" s="5" t="s">
         <v>1740</v>
       </c>
-      <c r="E568" s="6">
+      <c r="E568" s="4">
         <v>89650</v>
       </c>
       <c r="F568" s="5" t="s">
@@ -30020,7 +30011,7 @@
       <c r="G568" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H568" s="7">
+      <c r="H568" s="6">
         <v>0.824</v>
       </c>
       <c r="I568" s="5" t="s">
@@ -30052,7 +30043,7 @@
       <c r="D569" s="5" t="s">
         <v>1743</v>
       </c>
-      <c r="E569" s="6">
+      <c r="E569" s="4">
         <v>258878</v>
       </c>
       <c r="F569" s="5" t="s">
@@ -30061,7 +30052,7 @@
       <c r="G569" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H569" s="7">
+      <c r="H569" s="6">
         <v>0.882</v>
       </c>
       <c r="I569" s="5" t="s">
@@ -30093,7 +30084,7 @@
       <c r="D570" s="5" t="s">
         <v>1746</v>
       </c>
-      <c r="E570" s="6">
+      <c r="E570" s="4">
         <v>44058</v>
       </c>
       <c r="F570" s="5" t="s">
@@ -30102,7 +30093,7 @@
       <c r="G570" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H570" s="7">
+      <c r="H570" s="6">
         <v>0.842</v>
       </c>
       <c r="I570" s="5" t="s">
@@ -30134,7 +30125,7 @@
       <c r="D571" s="5" t="s">
         <v>1749</v>
       </c>
-      <c r="E571" s="6">
+      <c r="E571" s="4">
         <v>231289</v>
       </c>
       <c r="F571" s="5" t="s">
@@ -30175,7 +30166,7 @@
       <c r="D572" s="5" t="s">
         <v>1752</v>
       </c>
-      <c r="E572" s="6">
+      <c r="E572" s="4">
         <v>191891</v>
       </c>
       <c r="F572" s="5" t="s">
@@ -30216,7 +30207,7 @@
       <c r="D573" s="5" t="s">
         <v>1755</v>
       </c>
-      <c r="E573" s="6">
+      <c r="E573" s="4">
         <v>157495</v>
       </c>
       <c r="F573" s="5" t="s">
@@ -30255,7 +30246,7 @@
       <c r="D574" s="5" t="s">
         <v>1758</v>
       </c>
-      <c r="E574" s="6">
+      <c r="E574" s="4">
         <v>344519</v>
       </c>
       <c r="F574" s="5" t="s">
@@ -30264,7 +30255,7 @@
       <c r="G574" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H574" s="7">
+      <c r="H574" s="6">
         <v>0.889</v>
       </c>
       <c r="I574" s="5" t="s">
@@ -30296,7 +30287,7 @@
       <c r="D575" s="5" t="s">
         <v>1761</v>
       </c>
-      <c r="E575" s="6">
+      <c r="E575" s="4">
         <v>258005</v>
       </c>
       <c r="F575" s="5" t="s">
@@ -30305,7 +30296,7 @@
       <c r="G575" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H575" s="7">
+      <c r="H575" s="6">
         <v>0.824</v>
       </c>
       <c r="I575" s="5" t="s">
@@ -30337,7 +30328,7 @@
       <c r="D576" s="5" t="s">
         <v>1764</v>
       </c>
-      <c r="E576" s="6">
+      <c r="E576" s="4">
         <v>203853</v>
       </c>
       <c r="F576" s="5" t="s">
@@ -30378,7 +30369,7 @@
       <c r="D577" s="5" t="s">
         <v>1767</v>
       </c>
-      <c r="E577" s="6">
+      <c r="E577" s="4">
         <v>341680</v>
       </c>
       <c r="F577" s="5" t="s">
@@ -30387,7 +30378,7 @@
       <c r="G577" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H577" s="7">
+      <c r="H577" s="6">
         <v>0.714</v>
       </c>
       <c r="I577" s="5" t="s">
@@ -30419,7 +30410,7 @@
       <c r="D578" s="5" t="s">
         <v>1770</v>
       </c>
-      <c r="E578" s="6">
+      <c r="E578" s="4">
         <v>76061</v>
       </c>
       <c r="F578" s="5" t="s">
@@ -30460,7 +30451,7 @@
       <c r="D579" s="5" t="s">
         <v>1773</v>
       </c>
-      <c r="E579" s="6">
+      <c r="E579" s="4">
         <v>14942</v>
       </c>
       <c r="F579" s="5" t="s">
@@ -30501,7 +30492,7 @@
       <c r="D580" s="5" t="s">
         <v>1776</v>
       </c>
-      <c r="E580" s="6">
+      <c r="E580" s="4">
         <v>121686</v>
       </c>
       <c r="F580" s="5" t="s">
@@ -30510,7 +30501,7 @@
       <c r="G580" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H580" s="7">
+      <c r="H580" s="6">
         <v>0.8</v>
       </c>
       <c r="I580" s="5" t="s">
@@ -30542,7 +30533,7 @@
       <c r="D581" s="5" t="s">
         <v>1779</v>
       </c>
-      <c r="E581" s="6">
+      <c r="E581" s="4">
         <v>339340</v>
       </c>
       <c r="F581" s="5" t="s">
@@ -30583,7 +30574,7 @@
       <c r="D582" s="5" t="s">
         <v>1782</v>
       </c>
-      <c r="E582" s="6">
+      <c r="E582" s="4">
         <v>357147</v>
       </c>
       <c r="F582" s="5" t="s">
@@ -30624,7 +30615,7 @@
       <c r="D583" s="5" t="s">
         <v>1785</v>
       </c>
-      <c r="E583" s="6">
+      <c r="E583" s="4">
         <v>124715</v>
       </c>
       <c r="F583" s="5" t="s">
@@ -30663,7 +30654,7 @@
       <c r="D584" s="5" t="s">
         <v>1788</v>
       </c>
-      <c r="E584" s="6">
+      <c r="E584" s="4">
         <v>156990</v>
       </c>
       <c r="F584" s="5" t="s">
@@ -30672,7 +30663,7 @@
       <c r="G584" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H584" s="7">
+      <c r="H584" s="6">
         <v>0.733</v>
       </c>
       <c r="I584" s="5" t="s">
@@ -30704,7 +30695,7 @@
       <c r="D585" s="5" t="s">
         <v>1791</v>
       </c>
-      <c r="E585" s="6">
+      <c r="E585" s="4">
         <v>342209</v>
       </c>
       <c r="F585" s="5" t="s">
@@ -30745,7 +30736,7 @@
       <c r="D586" s="5" t="s">
         <v>1794</v>
       </c>
-      <c r="E586" s="6">
+      <c r="E586" s="4">
         <v>40995</v>
       </c>
       <c r="F586" s="5" t="s">
@@ -30786,7 +30777,7 @@
       <c r="D587" s="5" t="s">
         <v>1797</v>
       </c>
-      <c r="E587" s="6">
+      <c r="E587" s="4">
         <v>183288</v>
       </c>
       <c r="F587" s="5" t="s">
@@ -30827,7 +30818,7 @@
       <c r="D588" s="5" t="s">
         <v>1800</v>
       </c>
-      <c r="E588" s="6">
+      <c r="E588" s="4">
         <v>388171</v>
       </c>
       <c r="F588" s="5" t="s">
@@ -30836,7 +30827,7 @@
       <c r="G588" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H588" s="7">
+      <c r="H588" s="6">
         <v>0.8</v>
       </c>
       <c r="I588" s="5" t="s">
@@ -30868,7 +30859,7 @@
       <c r="D589" s="5" t="s">
         <v>1803</v>
       </c>
-      <c r="E589" s="6">
+      <c r="E589" s="4">
         <v>15904</v>
       </c>
       <c r="F589" s="5" t="s">
@@ -30877,7 +30868,7 @@
       <c r="G589" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H589" s="7">
+      <c r="H589" s="6">
         <v>0.857</v>
       </c>
       <c r="I589" s="5" t="s">
@@ -30909,7 +30900,7 @@
       <c r="D590" s="5" t="s">
         <v>1806</v>
       </c>
-      <c r="E590" s="6">
+      <c r="E590" s="4">
         <v>152651</v>
       </c>
       <c r="F590" s="5" t="s">
@@ -30918,7 +30909,7 @@
       <c r="G590" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H590" s="7">
+      <c r="H590" s="6">
         <v>0.174</v>
       </c>
       <c r="I590" s="5" t="s">
@@ -30950,7 +30941,7 @@
       <c r="D591" s="5" t="s">
         <v>1809</v>
       </c>
-      <c r="E591" s="6">
+      <c r="E591" s="4">
         <v>480763</v>
       </c>
       <c r="F591" s="5" t="s">
@@ -30959,7 +30950,7 @@
       <c r="G591" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H591" s="7">
+      <c r="H591" s="6">
         <v>0.692</v>
       </c>
       <c r="I591" s="5" t="s">
@@ -30991,7 +30982,7 @@
       <c r="D592" s="5" t="s">
         <v>1812</v>
       </c>
-      <c r="E592" s="6">
+      <c r="E592" s="4">
         <v>45538</v>
       </c>
       <c r="F592" s="5" t="s">
@@ -31032,7 +31023,7 @@
       <c r="D593" s="5" t="s">
         <v>1815</v>
       </c>
-      <c r="E593" s="6">
+      <c r="E593" s="4">
         <v>251896</v>
       </c>
       <c r="F593" s="5" t="s">
@@ -31073,7 +31064,7 @@
       <c r="D594" s="5" t="s">
         <v>1818</v>
       </c>
-      <c r="E594" s="6">
+      <c r="E594" s="4">
         <v>130257</v>
       </c>
       <c r="F594" s="5" t="s">
@@ -31114,7 +31105,7 @@
       <c r="D595" s="5" t="s">
         <v>1821</v>
       </c>
-      <c r="E595" s="6">
+      <c r="E595" s="4">
         <v>123261</v>
       </c>
       <c r="F595" s="5" t="s">
@@ -31155,7 +31146,7 @@
       <c r="D596" s="5" t="s">
         <v>1824</v>
       </c>
-      <c r="E596" s="6">
+      <c r="E596" s="4">
         <v>56601</v>
       </c>
       <c r="F596" s="5" t="s">
@@ -31196,7 +31187,7 @@
       <c r="D597" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="E597" s="6">
+      <c r="E597" s="4">
         <v>93176</v>
       </c>
       <c r="F597" s="5" t="s">
@@ -31237,7 +31228,7 @@
       <c r="D598" s="5" t="s">
         <v>1830</v>
       </c>
-      <c r="E598" s="6">
+      <c r="E598" s="4">
         <v>30290</v>
       </c>
       <c r="F598" s="5" t="s">
@@ -31278,7 +31269,7 @@
       <c r="D599" s="5" t="s">
         <v>1833</v>
       </c>
-      <c r="E599" s="6">
+      <c r="E599" s="4">
         <v>40423</v>
       </c>
       <c r="F599" s="5" t="s">
@@ -31319,7 +31310,7 @@
       <c r="D600" s="5" t="s">
         <v>1836</v>
       </c>
-      <c r="E600" s="6">
+      <c r="E600" s="4">
         <v>146227</v>
       </c>
       <c r="F600" s="5" t="s">
@@ -31328,7 +31319,7 @@
       <c r="G600" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H600" s="7">
+      <c r="H600" s="6">
         <v>0.857</v>
       </c>
       <c r="I600" s="5" t="s">
@@ -31360,7 +31351,7 @@
       <c r="D601" s="5" t="s">
         <v>1839</v>
       </c>
-      <c r="E601" s="6">
+      <c r="E601" s="4">
         <v>17259</v>
       </c>
       <c r="F601" s="5" t="s">
@@ -31369,7 +31360,7 @@
       <c r="G601" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H601" s="7">
+      <c r="H601" s="6">
         <v>0.733</v>
       </c>
       <c r="I601" s="5" t="s">
@@ -31401,7 +31392,7 @@
       <c r="D602" s="5" t="s">
         <v>1842</v>
       </c>
-      <c r="E602" s="6">
+      <c r="E602" s="4">
         <v>26276</v>
       </c>
       <c r="F602" s="5" t="s">
@@ -31410,7 +31401,7 @@
       <c r="G602" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H602" s="7">
+      <c r="H602" s="6">
         <v>0.692</v>
       </c>
       <c r="I602" s="5" t="s">
@@ -31442,7 +31433,7 @@
       <c r="D603" s="5" t="s">
         <v>1845</v>
       </c>
-      <c r="E603" s="6">
+      <c r="E603" s="4">
         <v>68410</v>
       </c>
       <c r="F603" s="5" t="s">
@@ -31451,7 +31442,7 @@
       <c r="G603" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H603" s="7">
+      <c r="H603" s="6">
         <v>0.714</v>
       </c>
       <c r="I603" s="5" t="s">
@@ -31483,7 +31474,7 @@
       <c r="D604" s="5" t="s">
         <v>1848</v>
       </c>
-      <c r="E604" s="6">
+      <c r="E604" s="4">
         <v>22412</v>
       </c>
       <c r="F604" s="5" t="s">
@@ -31492,7 +31483,7 @@
       <c r="G604" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H604" s="7">
+      <c r="H604" s="6">
         <v>0.824</v>
       </c>
       <c r="I604" s="5" t="s">
@@ -31524,7 +31515,7 @@
       <c r="D605" s="5" t="s">
         <v>1851</v>
       </c>
-      <c r="E605" s="6">
+      <c r="E605" s="4">
         <v>134158</v>
       </c>
       <c r="F605" s="5" t="s">
@@ -31565,7 +31556,7 @@
       <c r="D606" s="5" t="s">
         <v>1854</v>
       </c>
-      <c r="E606" s="6">
+      <c r="E606" s="4">
         <v>344598</v>
       </c>
       <c r="F606" s="5" t="s">
@@ -31606,7 +31597,7 @@
       <c r="D607" s="5" t="s">
         <v>1857</v>
       </c>
-      <c r="E607" s="6">
+      <c r="E607" s="4">
         <v>728221</v>
       </c>
       <c r="F607" s="5" t="s">
@@ -31647,7 +31638,7 @@
       <c r="D608" s="5" t="s">
         <v>1860</v>
       </c>
-      <c r="E608" s="6">
+      <c r="E608" s="4">
         <v>56523</v>
       </c>
       <c r="F608" s="5" t="s">
@@ -31688,7 +31679,7 @@
       <c r="D609" s="5" t="s">
         <v>1863</v>
       </c>
-      <c r="E609" s="6">
+      <c r="E609" s="4">
         <v>47082</v>
       </c>
       <c r="F609" s="5" t="s">
@@ -31697,7 +31688,7 @@
       <c r="G609" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H609" s="7">
+      <c r="H609" s="6">
         <v>0.857</v>
       </c>
       <c r="I609" s="5" t="s">
@@ -31729,7 +31720,7 @@
       <c r="D610" s="5" t="s">
         <v>1866</v>
       </c>
-      <c r="E610" s="6">
+      <c r="E610" s="4">
         <v>319745</v>
       </c>
       <c r="F610" s="5" t="s">
@@ -31770,7 +31761,7 @@
       <c r="D611" s="5" t="s">
         <v>1869</v>
       </c>
-      <c r="E611" s="6">
+      <c r="E611" s="4">
         <v>156722</v>
       </c>
       <c r="F611" s="5" t="s">
@@ -31811,7 +31802,7 @@
       <c r="D612" s="5" t="s">
         <v>1872</v>
       </c>
-      <c r="E612" s="6">
+      <c r="E612" s="4">
         <v>263956</v>
       </c>
       <c r="F612" s="5" t="s">
@@ -31852,7 +31843,7 @@
       <c r="D613" s="5" t="s">
         <v>1875</v>
       </c>
-      <c r="E613" s="6">
+      <c r="E613" s="4">
         <v>121842</v>
       </c>
       <c r="F613" s="5" t="s">
@@ -31861,7 +31852,7 @@
       <c r="G613" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H613" s="7">
+      <c r="H613" s="6">
         <v>0.105</v>
       </c>
       <c r="I613" s="5" t="s">
@@ -31893,7 +31884,7 @@
       <c r="D614" s="5" t="s">
         <v>1878</v>
       </c>
-      <c r="E614" s="6">
+      <c r="E614" s="4">
         <v>317482</v>
       </c>
       <c r="F614" s="5" t="s">
@@ -31934,7 +31925,7 @@
       <c r="D615" s="5" t="s">
         <v>1881</v>
       </c>
-      <c r="E615" s="6">
+      <c r="E615" s="4">
         <v>214316</v>
       </c>
       <c r="F615" s="5" t="s">
@@ -31975,7 +31966,7 @@
       <c r="D616" s="5" t="s">
         <v>1884</v>
       </c>
-      <c r="E616" s="6">
+      <c r="E616" s="4">
         <v>55215</v>
       </c>
       <c r="F616" s="5" t="s">
@@ -32016,7 +32007,7 @@
       <c r="D617" s="5" t="s">
         <v>1887</v>
       </c>
-      <c r="E617" s="6">
+      <c r="E617" s="4">
         <v>240551</v>
       </c>
       <c r="F617" s="5" t="s">
@@ -32057,7 +32048,7 @@
       <c r="D618" s="5" t="s">
         <v>1890</v>
       </c>
-      <c r="E618" s="6">
+      <c r="E618" s="4">
         <v>82442</v>
       </c>
       <c r="F618" s="5" t="s">
@@ -32066,7 +32057,7 @@
       <c r="G618" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H618" s="7">
+      <c r="H618" s="6">
         <v>0.824</v>
       </c>
       <c r="I618" s="5" t="s">
@@ -32098,7 +32089,7 @@
       <c r="D619" s="5" t="s">
         <v>1893</v>
       </c>
-      <c r="E619" s="6">
+      <c r="E619" s="4">
         <v>164913</v>
       </c>
       <c r="F619" s="5" t="s">
@@ -32107,7 +32098,7 @@
       <c r="G619" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H619" s="7">
+      <c r="H619" s="6">
         <v>0.4</v>
       </c>
       <c r="I619" s="5" t="s">
@@ -32139,7 +32130,7 @@
       <c r="D620" s="5" t="s">
         <v>1896</v>
       </c>
-      <c r="E620" s="6">
+      <c r="E620" s="4">
         <v>251812</v>
       </c>
       <c r="F620" s="5" t="s">
@@ -32148,7 +32139,7 @@
       <c r="G620" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H620" s="7">
+      <c r="H620" s="6">
         <v>0.706</v>
       </c>
       <c r="I620" s="5" t="s">
@@ -32180,7 +32171,7 @@
       <c r="D621" s="5" t="s">
         <v>1899</v>
       </c>
-      <c r="E621" s="6">
+      <c r="E621" s="4">
         <v>46104</v>
       </c>
       <c r="F621" s="5" t="s">
@@ -32189,7 +32180,7 @@
       <c r="G621" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H621" s="7">
+      <c r="H621" s="6">
         <v>0.8</v>
       </c>
       <c r="I621" s="5" t="s">
@@ -32221,7 +32212,7 @@
       <c r="D622" s="5" t="s">
         <v>1902</v>
       </c>
-      <c r="E622" s="6">
+      <c r="E622" s="4">
         <v>648195</v>
       </c>
       <c r="F622" s="5" t="s">
@@ -32262,7 +32253,7 @@
       <c r="D623" s="5" t="s">
         <v>1905</v>
       </c>
-      <c r="E623" s="6">
+      <c r="E623" s="4">
         <v>19579</v>
       </c>
       <c r="F623" s="5" t="s">
@@ -32271,7 +32262,7 @@
       <c r="G623" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H623" s="7">
+      <c r="H623" s="6">
         <v>0.824</v>
       </c>
       <c r="I623" s="5" t="s">
@@ -32303,7 +32294,7 @@
       <c r="D624" s="5" t="s">
         <v>932</v>
       </c>
-      <c r="E624" s="6">
+      <c r="E624" s="4">
         <v>134294</v>
       </c>
       <c r="F624" s="5" t="s">
@@ -32312,7 +32303,7 @@
       <c r="G624" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H624" s="7">
+      <c r="H624" s="6">
         <v>0.857</v>
       </c>
       <c r="I624" s="5" t="s">
@@ -32344,7 +32335,7 @@
       <c r="D625" s="5" t="s">
         <v>1910</v>
       </c>
-      <c r="E625" s="6">
+      <c r="E625" s="4">
         <v>104505</v>
       </c>
       <c r="F625" s="5" t="s">
@@ -32385,7 +32376,7 @@
       <c r="D626" s="5" t="s">
         <v>1913</v>
       </c>
-      <c r="E626" s="6">
+      <c r="E626" s="4">
         <v>314678</v>
       </c>
       <c r="F626" s="5" t="s">
@@ -32426,7 +32417,7 @@
       <c r="D627" s="5" t="s">
         <v>1916</v>
       </c>
-      <c r="E627" s="6">
+      <c r="E627" s="4">
         <v>39743</v>
       </c>
       <c r="F627" s="5" t="s">
@@ -32435,7 +32426,7 @@
       <c r="G627" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H627" s="7">
+      <c r="H627" s="6">
         <v>0.733</v>
       </c>
       <c r="I627" s="5" t="s">
@@ -32467,7 +32458,7 @@
       <c r="D628" s="5" t="s">
         <v>1919</v>
       </c>
-      <c r="E628" s="6">
+      <c r="E628" s="4">
         <v>20816</v>
       </c>
       <c r="F628" s="5" t="s">
@@ -32476,7 +32467,7 @@
       <c r="G628" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H628" s="7">
+      <c r="H628" s="6">
         <v>0.556</v>
       </c>
       <c r="I628" s="5" t="s">
@@ -32508,7 +32499,7 @@
       <c r="D629" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="E629" s="6">
+      <c r="E629" s="4">
         <v>240306</v>
       </c>
       <c r="F629" s="5" t="s">
@@ -32517,7 +32508,7 @@
       <c r="G629" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H629" s="7">
+      <c r="H629" s="6">
         <v>0.19</v>
       </c>
       <c r="I629" s="5" t="s">
@@ -32549,7 +32540,7 @@
       <c r="D630" s="5" t="s">
         <v>1924</v>
       </c>
-      <c r="E630" s="6">
+      <c r="E630" s="4">
         <v>295400</v>
       </c>
       <c r="F630" s="5" t="s">
@@ -32558,7 +32549,7 @@
       <c r="G630" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H630" s="7">
+      <c r="H630" s="6">
         <v>0.556</v>
       </c>
       <c r="I630" s="5" t="s">
@@ -32590,7 +32581,7 @@
       <c r="D631" s="5" t="s">
         <v>1927</v>
       </c>
-      <c r="E631" s="6">
+      <c r="E631" s="4">
         <v>39642</v>
       </c>
       <c r="F631" s="5" t="s">
@@ -32599,7 +32590,7 @@
       <c r="G631" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H631" s="7">
+      <c r="H631" s="6">
         <v>0.381</v>
       </c>
       <c r="I631" s="5" t="s">
@@ -32631,7 +32622,7 @@
       <c r="D632" s="5" t="s">
         <v>1930</v>
       </c>
-      <c r="E632" s="6">
+      <c r="E632" s="4">
         <v>126719</v>
       </c>
       <c r="F632" s="5" t="s">
@@ -32640,7 +32631,7 @@
       <c r="G632" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H632" s="7">
+      <c r="H632" s="6">
         <v>0.733</v>
       </c>
       <c r="I632" s="5" t="s">
@@ -32672,7 +32663,7 @@
       <c r="D633" s="5" t="s">
         <v>1933</v>
       </c>
-      <c r="E633" s="6">
+      <c r="E633" s="4">
         <v>74089</v>
       </c>
       <c r="F633" s="5" t="s">
@@ -32713,7 +32704,7 @@
       <c r="D634" s="5" t="s">
         <v>1936</v>
       </c>
-      <c r="E634" s="6">
+      <c r="E634" s="4">
         <v>203842</v>
       </c>
       <c r="F634" s="5" t="s">
@@ -32754,7 +32745,7 @@
       <c r="D635" s="5" t="s">
         <v>1939</v>
       </c>
-      <c r="E635" s="6">
+      <c r="E635" s="4">
         <v>73491</v>
       </c>
       <c r="F635" s="5" t="s">
@@ -32763,7 +32754,7 @@
       <c r="G635" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H635" s="7">
+      <c r="H635" s="6">
         <v>0.824</v>
       </c>
       <c r="I635" s="5" t="s">
@@ -32795,7 +32786,7 @@
       <c r="D636" s="5" t="s">
         <v>1942</v>
       </c>
-      <c r="E636" s="6">
+      <c r="E636" s="4">
         <v>257455</v>
       </c>
       <c r="F636" s="5" t="s">
@@ -32836,7 +32827,7 @@
       <c r="D637" s="5" t="s">
         <v>1945</v>
       </c>
-      <c r="E637" s="6">
+      <c r="E637" s="4">
         <v>65347</v>
       </c>
       <c r="F637" s="5" t="s">
@@ -32845,7 +32836,7 @@
       <c r="G637" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H637" s="7">
+      <c r="H637" s="6">
         <v>0.706</v>
       </c>
       <c r="I637" s="5" t="s">
@@ -32877,7 +32868,7 @@
       <c r="D638" s="5" t="s">
         <v>1948</v>
       </c>
-      <c r="E638" s="6">
+      <c r="E638" s="4">
         <v>199369</v>
       </c>
       <c r="F638" s="5" t="s">
@@ -32886,7 +32877,7 @@
       <c r="G638" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H638" s="7">
+      <c r="H638" s="6">
         <v>0.824</v>
       </c>
       <c r="I638" s="5" t="s">
@@ -32918,7 +32909,7 @@
       <c r="D639" s="5" t="s">
         <v>1951</v>
       </c>
-      <c r="E639" s="6">
+      <c r="E639" s="4">
         <v>69838</v>
       </c>
       <c r="F639" s="5" t="s">
@@ -32959,7 +32950,7 @@
       <c r="D640" s="5" t="s">
         <v>1954</v>
       </c>
-      <c r="E640" s="6">
+      <c r="E640" s="4">
         <v>344152</v>
       </c>
       <c r="F640" s="5" t="s">
@@ -32968,7 +32959,7 @@
       <c r="G640" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H640" s="7">
+      <c r="H640" s="6">
         <v>0.8</v>
       </c>
       <c r="I640" s="5" t="s">
@@ -33000,7 +32991,7 @@
       <c r="D641" s="5" t="s">
         <v>1957</v>
       </c>
-      <c r="E641" s="6">
+      <c r="E641" s="4">
         <v>258889</v>
       </c>
       <c r="F641" s="5" t="s">
@@ -33009,7 +33000,7 @@
       <c r="G641" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H641" s="7">
+      <c r="H641" s="6">
         <v>0.857</v>
       </c>
       <c r="I641" s="5" t="s">
@@ -33041,7 +33032,7 @@
       <c r="D642" s="5" t="s">
         <v>1960</v>
       </c>
-      <c r="E642" s="6">
+      <c r="E642" s="4">
         <v>400485</v>
       </c>
       <c r="F642" s="5" t="s">
@@ -33082,7 +33073,7 @@
       <c r="D643" s="5" t="s">
         <v>1963</v>
       </c>
-      <c r="E643" s="6">
+      <c r="E643" s="4">
         <v>52787</v>
       </c>
       <c r="F643" s="5" t="s">
@@ -33123,7 +33114,7 @@
       <c r="D644" s="5" t="s">
         <v>1966</v>
       </c>
-      <c r="E644" s="6">
+      <c r="E644" s="4">
         <v>37287</v>
       </c>
       <c r="F644" s="5" t="s">
@@ -33162,7 +33153,7 @@
       <c r="D645" s="5" t="s">
         <v>1969</v>
       </c>
-      <c r="E645" s="6">
+      <c r="E645" s="4">
         <v>334429</v>
       </c>
       <c r="F645" s="5" t="s">
@@ -33203,7 +33194,7 @@
       <c r="D646" s="5" t="s">
         <v>1972</v>
       </c>
-      <c r="E646" s="6">
+      <c r="E646" s="4">
         <v>67920</v>
       </c>
       <c r="F646" s="5" t="s">
@@ -33212,7 +33203,7 @@
       <c r="G646" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H646" s="7">
+      <c r="H646" s="6">
         <v>0.824</v>
       </c>
       <c r="I646" s="5" t="s">
@@ -33244,7 +33235,7 @@
       <c r="D647" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E647" s="6">
+      <c r="E647" s="4">
         <v>131789</v>
       </c>
       <c r="F647" s="5" t="s">
@@ -33253,7 +33244,7 @@
       <c r="G647" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H647" s="7">
+      <c r="H647" s="6">
         <v>0.824</v>
       </c>
       <c r="I647" s="5" t="s">
@@ -33285,7 +33276,7 @@
       <c r="D648" s="5" t="s">
         <v>1977</v>
       </c>
-      <c r="E648" s="6">
+      <c r="E648" s="4">
         <v>87884</v>
       </c>
       <c r="F648" s="5" t="s">
@@ -33326,7 +33317,7 @@
       <c r="D649" s="5" t="s">
         <v>1980</v>
       </c>
-      <c r="E649" s="6">
+      <c r="E649" s="4">
         <v>44790</v>
       </c>
       <c r="F649" s="5" t="s">
@@ -33335,7 +33326,7 @@
       <c r="G649" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H649" s="7">
+      <c r="H649" s="6">
         <v>0.556</v>
       </c>
       <c r="I649" s="5" t="s">
@@ -33367,7 +33358,7 @@
       <c r="D650" s="5" t="s">
         <v>1983</v>
       </c>
-      <c r="E650" s="6">
+      <c r="E650" s="4">
         <v>224256</v>
       </c>
       <c r="F650" s="5" t="s">
@@ -33408,7 +33399,7 @@
       <c r="D651" s="5" t="s">
         <v>1986</v>
       </c>
-      <c r="E651" s="6">
+      <c r="E651" s="4">
         <v>16600</v>
       </c>
       <c r="F651" s="5" t="s">
@@ -33417,7 +33408,7 @@
       <c r="G651" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H651" s="7">
+      <c r="H651" s="6">
         <v>0.16</v>
       </c>
       <c r="I651" s="5" t="s">
@@ -33449,7 +33440,7 @@
       <c r="D652" s="5" t="s">
         <v>1989</v>
       </c>
-      <c r="E652" s="6">
+      <c r="E652" s="4">
         <v>181547</v>
       </c>
       <c r="F652" s="5" t="s">
@@ -33490,7 +33481,7 @@
       <c r="D653" s="5" t="s">
         <v>1992</v>
       </c>
-      <c r="E653" s="6">
+      <c r="E653" s="4">
         <v>84511</v>
       </c>
       <c r="F653" s="5" t="s">
@@ -33531,7 +33522,7 @@
       <c r="D654" s="5" t="s">
         <v>1995</v>
       </c>
-      <c r="E654" s="6">
+      <c r="E654" s="4">
         <v>145838</v>
       </c>
       <c r="F654" s="5" t="s">
@@ -33540,7 +33531,7 @@
       <c r="G654" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H654" s="7">
+      <c r="H654" s="6">
         <v>0.833</v>
       </c>
       <c r="I654" s="5" t="s">
@@ -33572,7 +33563,7 @@
       <c r="D655" s="5" t="s">
         <v>1998</v>
       </c>
-      <c r="E655" s="6">
+      <c r="E655" s="4">
         <v>100986</v>
       </c>
       <c r="F655" s="5" t="s">
@@ -33613,7 +33604,7 @@
       <c r="D656" s="5" t="s">
         <v>2001</v>
       </c>
-      <c r="E656" s="6">
+      <c r="E656" s="4">
         <v>233113</v>
       </c>
       <c r="F656" s="5" t="s">
@@ -33622,7 +33613,7 @@
       <c r="G656" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H656" s="7">
+      <c r="H656" s="6">
         <v>0.353</v>
       </c>
       <c r="I656" s="5" t="s">
@@ -33654,7 +33645,7 @@
       <c r="D657" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="E657" s="6">
+      <c r="E657" s="4">
         <v>282411</v>
       </c>
       <c r="F657" s="5" t="s">
@@ -33695,7 +33686,7 @@
       <c r="D658" s="5" t="s">
         <v>2006</v>
       </c>
-      <c r="E658" s="6">
+      <c r="E658" s="4">
         <v>392775</v>
       </c>
       <c r="F658" s="5" t="s">
@@ -33736,7 +33727,7 @@
       <c r="D659" s="5" t="s">
         <v>2009</v>
       </c>
-      <c r="E659" s="6">
+      <c r="E659" s="4">
         <v>341051</v>
       </c>
       <c r="F659" s="5" t="s">
@@ -33745,7 +33736,7 @@
       <c r="G659" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H659" s="7">
+      <c r="H659" s="6">
         <v>0.692</v>
       </c>
       <c r="I659" s="5" t="s">
@@ -33777,7 +33768,7 @@
       <c r="D660" s="5" t="s">
         <v>2012</v>
       </c>
-      <c r="E660" s="6">
+      <c r="E660" s="4">
         <v>369319</v>
       </c>
       <c r="F660" s="5" t="s">
@@ -33818,7 +33809,7 @@
       <c r="D661" s="5" t="s">
         <v>2015</v>
       </c>
-      <c r="E661" s="6">
+      <c r="E661" s="4">
         <v>9340</v>
       </c>
       <c r="F661" s="5" t="s">
@@ -33859,7 +33850,7 @@
       <c r="D662" s="5" t="s">
         <v>2018</v>
       </c>
-      <c r="E662" s="6">
+      <c r="E662" s="4">
         <v>44716</v>
       </c>
       <c r="F662" s="5" t="s">
@@ -33868,7 +33859,7 @@
       <c r="G662" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H662" s="7">
+      <c r="H662" s="6">
         <v>0.842</v>
       </c>
       <c r="I662" s="5" t="s">
@@ -33900,7 +33891,7 @@
       <c r="D663" s="5" t="s">
         <v>2021</v>
       </c>
-      <c r="E663" s="6">
+      <c r="E663" s="4">
         <v>342046</v>
       </c>
       <c r="F663" s="5" t="s">
@@ -33941,7 +33932,7 @@
       <c r="D664" s="5" t="s">
         <v>2024</v>
       </c>
-      <c r="E664" s="6">
+      <c r="E664" s="4">
         <v>172142</v>
       </c>
       <c r="F664" s="5" t="s">
@@ -33982,7 +33973,7 @@
       <c r="D665" s="5" t="s">
         <v>2027</v>
       </c>
-      <c r="E665" s="6">
+      <c r="E665" s="4">
         <v>72347</v>
       </c>
       <c r="F665" s="5" t="s">
@@ -34023,7 +34014,7 @@
       <c r="D666" s="5" t="s">
         <v>2031</v>
       </c>
-      <c r="E666" s="6">
+      <c r="E666" s="4">
         <v>3455</v>
       </c>
       <c r="F666" s="5" t="s">
@@ -34064,7 +34055,7 @@
       <c r="D667" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="E667" s="6">
+      <c r="E667" s="4">
         <v>37666</v>
       </c>
       <c r="F667" s="5" t="s">
@@ -34073,7 +34064,7 @@
       <c r="G667" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H667" s="7">
+      <c r="H667" s="6">
         <v>0.2</v>
       </c>
       <c r="I667" s="5" t="s">
@@ -34105,7 +34096,7 @@
       <c r="D668" s="5" t="s">
         <v>2036</v>
       </c>
-      <c r="E668" s="6">
+      <c r="E668" s="4">
         <v>315852</v>
       </c>
       <c r="F668" s="5" t="s">
@@ -34114,7 +34105,7 @@
       <c r="G668" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H668" s="7">
+      <c r="H668" s="6">
         <v>0.533</v>
       </c>
       <c r="I668" s="5" t="s">
@@ -34146,7 +34137,7 @@
       <c r="D669" s="5" t="s">
         <v>2039</v>
       </c>
-      <c r="E669" s="6">
+      <c r="E669" s="4">
         <v>49841</v>
       </c>
       <c r="F669" s="5" t="s">
@@ -34155,7 +34146,7 @@
       <c r="G669" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H669" s="7">
+      <c r="H669" s="6">
         <v>0.357</v>
       </c>
       <c r="I669" s="5" t="s">
@@ -34187,7 +34178,7 @@
       <c r="D670" s="5" t="s">
         <v>2042</v>
       </c>
-      <c r="E670" s="6">
+      <c r="E670" s="4">
         <v>122077</v>
       </c>
       <c r="F670" s="5" t="s">
@@ -34196,7 +34187,7 @@
       <c r="G670" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H670" s="7">
+      <c r="H670" s="6">
         <v>0.429</v>
       </c>
       <c r="I670" s="5" t="s">
@@ -34228,7 +34219,7 @@
       <c r="D671" s="5" t="s">
         <v>2045</v>
       </c>
-      <c r="E671" s="6">
+      <c r="E671" s="4">
         <v>238056</v>
       </c>
       <c r="F671" s="5" t="s">
@@ -34237,7 +34228,7 @@
       <c r="G671" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H671" s="7">
+      <c r="H671" s="6">
         <v>0.556</v>
       </c>
       <c r="I671" s="5" t="s">
@@ -34269,7 +34260,7 @@
       <c r="D672" s="5" t="s">
         <v>2048</v>
       </c>
-      <c r="E672" s="6">
+      <c r="E672" s="4">
         <v>288496</v>
       </c>
       <c r="F672" s="5" t="s">
@@ -34278,7 +34269,7 @@
       <c r="G672" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H672" s="7">
+      <c r="H672" s="6">
         <v>0.8</v>
       </c>
       <c r="I672" s="5" t="s">
@@ -34310,7 +34301,7 @@
       <c r="D673" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="E673" s="6">
+      <c r="E673" s="4">
         <v>223967</v>
       </c>
       <c r="F673" s="5" t="s">
@@ -34351,7 +34342,7 @@
       <c r="D674" s="5" t="s">
         <v>2054</v>
       </c>
-      <c r="E674" s="6">
+      <c r="E674" s="4">
         <v>85177</v>
       </c>
       <c r="F674" s="5" t="s">
@@ -34360,7 +34351,7 @@
       <c r="G674" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H674" s="7">
+      <c r="H674" s="6">
         <v>0.857</v>
       </c>
       <c r="I674" s="5" t="s">
@@ -34392,7 +34383,7 @@
       <c r="D675" s="5" t="s">
         <v>2057</v>
       </c>
-      <c r="E675" s="6">
+      <c r="E675" s="4">
         <v>167243</v>
       </c>
       <c r="F675" s="5" t="s">
@@ -34433,7 +34424,7 @@
       <c r="D676" s="5" t="s">
         <v>2060</v>
       </c>
-      <c r="E676" s="6">
+      <c r="E676" s="4">
         <v>349066</v>
       </c>
       <c r="F676" s="5" t="s">
@@ -34474,7 +34465,7 @@
       <c r="D677" s="5" t="s">
         <v>2063</v>
       </c>
-      <c r="E677" s="6">
+      <c r="E677" s="4">
         <v>670882</v>
       </c>
       <c r="F677" s="5" t="s">
@@ -34515,7 +34506,7 @@
       <c r="D678" s="5" t="s">
         <v>2066</v>
       </c>
-      <c r="E678" s="6">
+      <c r="E678" s="4">
         <v>320913</v>
       </c>
       <c r="F678" s="5" t="s">
@@ -34556,7 +34547,7 @@
       <c r="D679" s="5" t="s">
         <v>2069</v>
       </c>
-      <c r="E679" s="6">
+      <c r="E679" s="4">
         <v>23914</v>
       </c>
       <c r="F679" s="5" t="s">
@@ -34595,7 +34586,7 @@
       <c r="D680" s="5" t="s">
         <v>2072</v>
       </c>
-      <c r="E680" s="6">
+      <c r="E680" s="4">
         <v>222813</v>
       </c>
       <c r="F680" s="5" t="s">
@@ -34604,7 +34595,7 @@
       <c r="G680" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H680" s="7">
+      <c r="H680" s="6">
         <v>0.857</v>
       </c>
       <c r="I680" s="5" t="s">
@@ -34636,7 +34627,7 @@
       <c r="D681" s="5" t="s">
         <v>2075</v>
       </c>
-      <c r="E681" s="6">
+      <c r="E681" s="4">
         <v>242499</v>
       </c>
       <c r="F681" s="5" t="s">
@@ -34645,7 +34636,7 @@
       <c r="G681" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H681" s="7">
+      <c r="H681" s="6">
         <v>0.375</v>
       </c>
       <c r="I681" s="5" t="s">
@@ -34664,7 +34655,7 @@
         <v>2076</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="682" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="682" customHeight="1" ht="18.75" hidden="1">
       <c r="A682" s="4">
         <v>2018</v>
       </c>
@@ -34677,7 +34668,7 @@
       <c r="D682" s="5" t="s">
         <v>2078</v>
       </c>
-      <c r="E682" s="6">
+      <c r="E682" s="4">
         <v>386574</v>
       </c>
       <c r="F682" s="5" t="s">
@@ -34686,7 +34677,7 @@
       <c r="G682" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H682" s="7">
+      <c r="H682" s="6">
         <v>0.615</v>
       </c>
       <c r="I682" s="5" t="s">
@@ -34718,7 +34709,7 @@
       <c r="D683" s="5" t="s">
         <v>2081</v>
       </c>
-      <c r="E683" s="6">
+      <c r="E683" s="4">
         <v>58205</v>
       </c>
       <c r="F683" s="5" t="s">
@@ -34759,7 +34750,7 @@
       <c r="D684" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="E684" s="6">
+      <c r="E684" s="4">
         <v>357397</v>
       </c>
       <c r="F684" s="5" t="s">
@@ -34768,7 +34759,7 @@
       <c r="G684" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H684" s="7">
+      <c r="H684" s="6">
         <v>0.167</v>
       </c>
       <c r="I684" s="5" t="s">
@@ -34800,7 +34791,7 @@
       <c r="D685" s="5" t="s">
         <v>2085</v>
       </c>
-      <c r="E685" s="6">
+      <c r="E685" s="4">
         <v>362844</v>
       </c>
       <c r="F685" s="5" t="s">
@@ -34841,7 +34832,7 @@
       <c r="D686" s="5" t="s">
         <v>2088</v>
       </c>
-      <c r="E686" s="6">
+      <c r="E686" s="4">
         <v>203074</v>
       </c>
       <c r="F686" s="5" t="s">
@@ -34882,7 +34873,7 @@
       <c r="D687" s="5" t="s">
         <v>2091</v>
       </c>
-      <c r="E687" s="6">
+      <c r="E687" s="4">
         <v>238055</v>
       </c>
       <c r="F687" s="5" t="s">
@@ -34891,7 +34882,7 @@
       <c r="G687" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H687" s="7">
+      <c r="H687" s="6">
         <v>0.824</v>
       </c>
       <c r="I687" s="5" t="s">
@@ -34923,7 +34914,7 @@
       <c r="D688" s="5" t="s">
         <v>2094</v>
       </c>
-      <c r="E688" s="6">
+      <c r="E688" s="4">
         <v>226138</v>
       </c>
       <c r="F688" s="5" t="s">
@@ -34932,7 +34923,7 @@
       <c r="G688" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H688" s="7">
+      <c r="H688" s="6">
         <v>0.444</v>
       </c>
       <c r="I688" s="5" t="s">
@@ -34964,7 +34955,7 @@
       <c r="D689" s="5" t="s">
         <v>2097</v>
       </c>
-      <c r="E689" s="6">
+      <c r="E689" s="4">
         <v>75296</v>
       </c>
       <c r="F689" s="5" t="s">
@@ -35005,7 +34996,7 @@
       <c r="D690" s="5" t="s">
         <v>2100</v>
       </c>
-      <c r="E690" s="6">
+      <c r="E690" s="4">
         <v>520624</v>
       </c>
       <c r="F690" s="5" t="s">
@@ -35014,7 +35005,7 @@
       <c r="G690" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H690" s="7">
+      <c r="H690" s="6">
         <v>0.692</v>
       </c>
       <c r="I690" s="5" t="s">
@@ -35046,7 +35037,7 @@
       <c r="D691" s="5" t="s">
         <v>2103</v>
       </c>
-      <c r="E691" s="6">
+      <c r="E691" s="4">
         <v>391905</v>
       </c>
       <c r="F691" s="5" t="s">
@@ -35087,7 +35078,7 @@
       <c r="D692" s="5" t="s">
         <v>2106</v>
       </c>
-      <c r="E692" s="6">
+      <c r="E692" s="4">
         <v>26</v>
       </c>
       <c r="F692" s="5" t="s">
@@ -35128,7 +35119,7 @@
       <c r="D693" s="5" t="s">
         <v>2109</v>
       </c>
-      <c r="E693" s="6">
+      <c r="E693" s="4">
         <v>289075</v>
       </c>
       <c r="F693" s="5" t="s">
@@ -35169,7 +35160,7 @@
       <c r="D694" s="5" t="s">
         <v>2112</v>
       </c>
-      <c r="E694" s="6">
+      <c r="E694" s="4">
         <v>77760</v>
       </c>
       <c r="F694" s="5" t="s">
@@ -35178,7 +35169,7 @@
       <c r="G694" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H694" s="7">
+      <c r="H694" s="6">
         <v>0.692</v>
       </c>
       <c r="I694" s="5" t="s">
